--- a/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
+++ b/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7510"/>
   </bookViews>
   <sheets>
     <sheet name="FR-02 Login" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="711">
   <si>
     <t>TC ID</t>
   </si>
@@ -101,7 +101,7 @@
 2. Body: {"email":"test@eshop.com","password":"WrongPass999"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
   </si>
   <si>
     <t>Password không khớp -&gt; đăng nhập thất bại, AI có căn cứ trực tiếp dựa vào đặc tả em cung cấp. Mã lỗi cụ thể chưa được nêu trong đặc tả nên AI ghi cần xác định thêm, nhưng kết quả là thất bại được xác định đúng</t>
@@ -189,7 +189,7 @@
 2. Body: {"email":"test@eshop.com","password":"P@$$w!r#d"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại (password không khớp). CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại (password không khớp). HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
   </si>
   <si>
     <t>Mật khẩu toàn là ký tự đặc biệt nhưng vẫn không khớp với mật khẩu thật nên đăng nhập thất bại. Đúng với đặc tả</t>
@@ -312,7 +312,7 @@
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass1"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Bộ đếm = 1 (&lt; 3, chưa khóa). CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 1 (&lt; 3, chưa khóa).</t>
   </si>
   <si>
     <t>Đúng với đặc tả</t>
@@ -335,7 +335,7 @@
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass2"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Bộ đếm = 2 (&lt; 3, chưa khóa). CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 2 (&lt; 3, chưa khóa).</t>
   </si>
   <si>
     <t>TC-FR02-ST-03</t>
@@ -355,7 +355,7 @@
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass3"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Bộ đếm = 3 (&gt;= 3 -&gt; khóa 30 giây).CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 3 (&gt;= 3 -&gt; khóa 30 giây).</t>
   </si>
   <si>
     <t>TC-FR02-ST-04</t>
@@ -375,7 +375,7 @@
 2. Body: {"email":"locktest@eshop.com","password":"Locktest123!"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Tài khoản vẫn bị khóa. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 403 Forbidden, Response: {"error": "Tài khoản đã bị khóa. Vui lòng thử lại sau."} (kiểm tra thời gian khóa được thực hiện TRƯỚC khi so khớp mật khẩu, nên dù mật khẩu đúng vẫn bị chặn ở bước khóa). Tài khoản vẫn bị khóa.</t>
   </si>
   <si>
     <t>TC-FR02-ST-05</t>
@@ -392,6 +392,9 @@
 2. Body: {"email":"locktest@eshop.com","password":"WrongPassX"}</t>
   </si>
   <si>
+    <t>Đăng nhập thất bại. HTTP 403 Forbidden, Response: {"error": "Tài khoản đã bị khóa. Vui lòng thử lại sau."}. Tài khoản vẫn bị khóa.</t>
+  </si>
+  <si>
     <t>TC-FR02-ST-06</t>
   </si>
   <si>
@@ -418,7 +421,7 @@
 2. Body: {"email":"locktest@eshop.com","password":"WrongPassAfterUnlock"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Bộ đếm bắt đầu lại từ 1. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm bắt đầu lại từ 1.</t>
   </si>
   <si>
     <t>Theo suy luận cùng với từ đặc tả suy ra thì test case valid, sau khi mở khóa thì bộ đếm reset về 0, tiếp tục sai nên +1</t>
@@ -441,7 +444,7 @@
 2. Body: {"email": "' OR 1=1 --", "password": "anypassword"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Hệ thống xử lý đúng (parameterized query). Không lộ SQL/stack trace. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Hệ thống xử lý đúng (parameterized query). Không lộ SQL/stack trace.</t>
   </si>
   <si>
     <t>Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công.</t>
@@ -475,7 +478,7 @@
 2. Body: {"email": "&lt;SQL injection query&gt;", "password": "x"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Không lộ thông tin cấu trúc DB. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Không lộ thông tin cấu trúc DB.</t>
   </si>
   <si>
     <t>Tương tự, mở rộng dạng UNION-based, Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công..</t>
@@ -498,7 +501,7 @@
 2. Body: {"email": "wronguser@eshop.com", "password": "WrongPass123"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Thông báo lỗi chung, không để lộ "email không tồn tại". CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Thông báo lỗi chung, không để lộ "email không tồn tại".</t>
   </si>
   <si>
     <t>Dựa vào đặc tả 'không để lộ chi tiết nguyên nhân'.</t>
@@ -517,30 +520,31 @@
 2. Body: {"email": "test@eshop.com", "password": "WrongPass999"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Thông báo lỗi chung. Không để lộ "mật khẩu sai". CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Thông báo lỗi chung. Không để lộ "mật khẩu sai".</t>
   </si>
   <si>
     <t>TC-FR02-SEC-06</t>
   </si>
   <si>
-    <t>Kiểm tra thông báo lỗi chung - cả hai đều sai</t>
-  </si>
-  <si>
-    <t>email: "noaccount@eshop.com"
-password: "WrongPassXYZ"</t>
-  </si>
-  <si>
-    <t>1. POST /api/login
-2. Body: {"email": "noaccount@eshop.com", "password": "WrongPassXYZ"}</t>
-  </si>
-  <si>
-    <t>Đăng nhập thất bại. Thông báo lỗi chung. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
-  </si>
-  <si>
-    <t>INVALID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bị trùng, nếu email sai, không tồn tại thì đâu cần xét password. Trùng với TC-FR02-SEC-04. </t>
+    <t>Kiểm tra không có sự khác biệt thời gian phản hồi giữa email tồn tại và không tồn tại (chống User Enumeration qua timing attack)</t>
+  </si>
+  <si>
+    <t>Hệ thống đang hoạt động bình thường; đã có tài khoản test@eshop.com</t>
+  </si>
+  <si>
+    <t>Case A: email: "test@eshop.com", password: "WrongPass999"
+Case B: email: "noaccount@eshop.com", password: "WrongPass999"</t>
+  </si>
+  <si>
+    <t>1. Gửi lần lượt 2 request POST /api/login với Case A và Case B
+2. Đo thời gian phản hồi (response time) của mỗi request
+3. So sánh chênh lệch thời gian giữa 2 case</t>
+  </si>
+  <si>
+    <t>Thời gian phản hồi giữa 2 case không chênh lệch đáng kể (ví dụ &lt; 50-100ms), tránh lộ thông tin email có tồn tại hay không qua timing side-channel. Cả 2 case đều trả về HTTP 401 Unauthorized, {"error": "Invalid email or password"}.</t>
+  </si>
+  <si>
+    <t>Kiểm tra timing attack - vì code hiện có 2 nhánh xử lý khác nhau (user không tồn tại trả lỗi ngay; user tồn tại phải so sánh password) nên thời gian xử lý có thể khác biệt và bị lợi dụng để dò tìm email tồn tại trong hệ thống. Test case hợp lý.</t>
   </si>
   <si>
     <t>TC-FR02-SEC-07</t>
@@ -558,7 +562,7 @@
 3. Kiểm tra toàn bộ response body</t>
   </si>
   <si>
-    <t>Response không chứa: lỗi SQL, stack trace, tên bảng, tên cột, đường dẫn file server. Chỉ trả về lỗi chung. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Response không chứa: lỗi SQL, stack trace, tên bảng, tên cột, đường dẫn file server. Chỉ trả về lỗi chung. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
   </si>
   <si>
     <t>Dựa vào SEC-05 + 'không lộ chi tiết nguyên nhân'.</t>
@@ -567,22 +571,21 @@
     <t>TC-FR02-SEC-08</t>
   </si>
   <si>
-    <t>Kiểm tra thông báo lỗi không để lộ trạng thái tùy thuộc field</t>
-  </si>
-  <si>
-    <t>email: "test@eshop.com"
-password: "WrongPassAny"</t>
-  </si>
-  <si>
-    <t>1. POST /api/login
-2. Body: {"email": "test@eshop.com", "password": "WrongPassAny"}
-3. So sánh với TC-FR02-SEC-04</t>
-  </si>
-  <si>
-    <t>Thông báo lỗi không được thay đổi tùy theo email tồn tại hay không. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trùng với TC-FR02-SEC-05. </t>
+    <t>Kiểm tra response/JWT không lộ thông tin nhạy cảm (password) của user</t>
+  </si>
+  <si>
+    <t>Tài khoản test@eshop.com tồn tại</t>
+  </si>
+  <si>
+    <t>1. POST /api/login với thông tin hợp lệ
+2. Nhận response 200 OK
+3. Kiểm tra field "user" trong response body và payload JWT</t>
+  </si>
+  <si>
+    <t>Field "user" trong response và payload JWT KHÔNG được chứa field "password" (dù ở dạng plaintext hay hash). Chỉ chứa các field an toàn như id, name, email, role.</t>
+  </si>
+  <si>
+    <t>Kiểm tra rò rỉ dữ liệu nhạy cảm. Test case hợp lý</t>
   </si>
   <si>
     <t>TC-FR02-SCHEMA-01</t>
@@ -675,7 +678,7 @@
 4. Parse JSON</t>
   </si>
   <si>
-    <t>Header sau decode phải là JSON hợp lệ. CẦN XÁC ĐỊNH THÊM: header cần chứa field nào</t>
+    <t>Header sau decode phải là JSON hợp lệ, chứa tối thiểu 2 field: "alg" (thuật toán ký, mặc định "HS256" do thư viện jsonwebtoken khi không chỉ định algorithm) và "typ" ("JWT").</t>
   </si>
   <si>
     <t>JWT hợp lệ luôn phải decode được header. Test case hợp lý.</t>
@@ -693,7 +696,7 @@
 4. Parse JSON</t>
   </si>
   <si>
-    <t>Payload sau decode phải là JSON hợp lệ. CẦN XÁC ĐỊNH THÊM: payload cần chứa field nào</t>
+    <t>Payload sau decode phải là JSON hợp lệ, chứa field "id" (id user) và "role". Field "iat" (issued at) được thư viện tự thêm. Lưu ý: KHÔNG có field "exp" (hết hạn) vì jwt.sign() được gọi không kèm option expiresIn -&gt; token không bao giờ hết hạn (rủi ro bảo mật, cần ghi vào bug report).</t>
   </si>
   <si>
     <t>Payload luôn phải decode được. Test case hợp lý.</t>
@@ -710,7 +713,7 @@
 3. Kiểm tra độ dài</t>
   </si>
   <si>
-    <t>Signature phải có độ dài &gt; 0, không được rỗng. CẦN XÁC ĐỊNH THÊM: thuật toán ký</t>
+    <t>Signature phải có độ dài &gt; 0, không được rỗng. Thuật toán ký mặc định là HS256 (HMAC-SHA256) vì jwt.sign() không truyền option algorithm.</t>
   </si>
   <si>
     <t>Chữ ký JWT không được rỗng - tính chất cơ bản của JWT. Test case hợp lý.</t>
@@ -750,6 +753,9 @@
 2. Body: {"email":"Test@EShop.com","password":"Test1234!"}</t>
   </si>
   <si>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"} (vì so sánh email trong SQL phân biệt hoa/thường, "Test@EShop.com" khác "test@eshop.com" nên không tìm thấy user).</t>
+  </si>
+  <si>
     <t>Cần test thêm hệ thống có phân biệt chữ hoa, chữ thường hay không. Do tính chất bảo mật của email và password nên phân biệt chữ hoa, chữ thường. Lý do AI bỏ sót theo em nghĩ là do prompt của em chỉ yêu cầu domain partitioning cho field email một cách chung chung, không có gợi ý cụ thể, nên AI thường chỉ quan tâm đúng các trường hợp email đúng/sai định dạng mà không test các case nhạy cảm, chi tiết hơn như phân biệt chữ hoa với chữ thường</t>
   </si>
   <si>
@@ -767,7 +773,10 @@
 2. Body: {"email":" test@eshop.com ","password":"Test1234!"}</t>
   </si>
   <si>
-    <t>Đ</t>
+    <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"} (email có khoảng trắng đầu/cuối không được trim trước khi so khớp trong DB, nên " test@eshop.com " khác với "test@eshop.com").</t>
+  </si>
+  <si>
+    <t>Test case kiểm tra hệ thống có tự động trim khoảng trắng ở email trước khi xử lý hay không đặc tả không nêu rõ điều này. Lý do AI bỏ sót: prompt gốc chỉ yêu cầu domain partition theo định dạng email hợp lệ/không hợp lệ một cách chung chung, không đề cập input nhiễu như khoảng trắng thừa - đây là input edge-case thực tế thường gặp mà đặc tả không nêu, nên AI (chỉ dựa vào đặc tả) không tự sinh ra được.</t>
   </si>
   <si>
     <t>TC-FR02-EXT-03</t>
@@ -788,7 +797,10 @@
 2. Kiểm tra login_attempts cuối cùng qua GET /api/admin/users hoặc thử đăng nhập lại</t>
   </si>
   <si>
-    <t>Bộ đếm có tăng đúng 2 (mỗi request +1).</t>
+    <t>Bộ đếm tăng đúng cho cả 2 lần thất bại.</t>
+  </si>
+  <si>
+    <t>Test case hợp lý để phát hiện lỗi đồng thời tiềm ẩn. Lý do AI bỏ sót: AI sinh test case dựa trên đặc tả API (request/response tĩnh), không có khả năng suy luận về hành vi đồng  thời vì AI chỉ được cung cấp đặc tả API, không có prompt chi tiết hơn về hành động này. Đây là hạn chế đặc trưng khi sinh test case chỉ từ đặc tả mà không phân tích thực tế.</t>
   </si>
   <si>
     <t>TC-FR02-EXT-04</t>
@@ -804,7 +816,10 @@
     <t>1. POST /api/login với Content-Type sai và body dạng form-encoded thay vì JSON</t>
   </si>
   <si>
-    <t>Hệ thống có xử lý lỗi rõ ràng</t>
+    <t>Do body-parser chỉ parse JSON khi Content-Type là application/json, request dạng form-urlencoded sẽ có req.body rỗng ({}) -&gt; email/password đều undefined -&gt; DB không tìm thấy user khớp -&gt; HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
+  </si>
+  <si>
+    <t>Test case hợp lý để kiểm tra khả năng chịu lỗi khi client gửi sai Content-Type - tình huống thực tế hay gặp. Lý do AI bỏ sót: AI thường giả định client luôn gửi đúng Content-Type theo đặc tả (application/json) khi sinh test case cho request body, không tự nghĩ ra kịch bản client gửi sai định dạng header vì đây là đặc tính của tầng HTTP/middleware (body-parser), nằm ngoài phạm vi đặc tả logic nghiệp vụ mà AI được cung cấp.</t>
   </si>
   <si>
     <t>TC-FR02-EXT-05</t>
@@ -823,7 +838,10 @@
     <t>1. POST /api/login với email dài 5000+ ký tự</t>
   </si>
   <si>
-    <t>Hệ thống có giới hạn độ dài input và xử lý chuỗi cực dài này một cách an toàn (không treo/crash)</t>
+    <t>Server không bị treo/crash: SQLite xử lý tham số dài bình thường qua parameterized query, không tìm thấy user khớp -&gt; HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
+  </si>
+  <si>
+    <t>Test case hợp lý để kiểm tra khả năng chống chịu input bất thường/DoS tiềm ẩn. Lý do AI bỏ sót: đặc tả API không đề cập giới hạn độ dài field email, và AI khi sinh test theo domain partition thường chỉ xét các mốc độ dài hợp lý (email hợp lệ/không hợp lệ theo định dạng) chứ không chủ động nghĩ tới input lớn nhằm mục đích kiểm thử bảo mật/hiệu năng - đây đòi hỏi prompt chi tiết hơn là chỉ dựa theo đặc tả chức năng có sẵn.</t>
   </si>
   <si>
     <t>TC-FR08-DP-01</t>
@@ -844,7 +862,7 @@
 3. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
   </si>
   <si>
-    <t>Thanh toán thành công. Giỏ hàng bị xóa. CẦN XÁC ĐỊNH THÊM: status code và response body</t>
+    <t>Thanh toán thành công. HTTP 200 OK, Response: {"message":"Checkout successful","orderId":&lt;id&gt;}.</t>
   </si>
   <si>
     <t>Đúng với đặc tả, happy path bình thường.</t>
@@ -865,7 +883,7 @@
 3. Body: {"total_amount": 100000, "shipping_address": ""}</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống có cho phép shipping_address trống hay bắt buộc nhập</t>
+    <t>Phải validate shipping_address</t>
   </si>
   <si>
     <t>Đặc tả không nói shipping_address có không được để trống hay không nhưng theo em shipping address không được để trống, suy ra test case hợp lý.</t>
@@ -886,9 +904,6 @@
 3. Body: {"total_amount": 100000, "shipping_address": null}</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống có xử lý null hay trả lỗi</t>
-  </si>
-  <si>
     <t>Đặc tả không nói shipping_address có không được null hay không nhưng theo em shipping address không được để trống, suy ra test case hợp lý.</t>
   </si>
   <si>
@@ -907,9 +922,6 @@
 3. Body: {"total_amount": 100000, "shipping_address": "&lt;500 chars&gt;"}</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống có giới hạn độ dài shipping_address hay không</t>
-  </si>
-  <si>
     <t>Đặc tả không quy định giới hạn độ dài cho shipping_address nhưng cũng cần test để tránh DoS.</t>
   </si>
   <si>
@@ -928,9 +940,6 @@
 3. Body: {"total_amount": 100000, "shipping_address": "&lt;script&gt;alert(1)&lt;/script&gt;"}</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống có escape/validate shipping_address hay lưu nguyên</t>
-  </si>
-  <si>
     <t>Đặc tả không quy định nhưng theo em cần test xem hệ thống có escape hay không nên test case hợp lý.</t>
   </si>
   <si>
@@ -941,9 +950,6 @@
   </si>
   <si>
     <t>Người dùng đã đăng nhập. Giỏ hàng có ít nhất 1 sản phẩm.</t>
-  </si>
-  <si>
-    <t>Thanh toán thành công. Giỏ hàng bị xóa sau thanh toán. CẦN XÁC ĐỊNH THÊM</t>
   </si>
   <si>
     <t>Dựa vào đặc tả.</t>
@@ -967,7 +973,7 @@
 3. Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
   </si>
   <si>
-    <t xml:space="preserve"> Báo lỗi</t>
+    <t xml:space="preserve">Giỏ hàng trống báo lỗi khi thanh toán </t>
   </si>
   <si>
     <t xml:space="preserve">Dù đặc tả gốc không quy định nhưng cần test case "không thể thanh toán khi giỏ trống" </t>
@@ -991,7 +997,7 @@
 3. Body: {"total_amount": 500000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
   </si>
   <si>
-    <t>Backend phải tự tính lại total_amount từ giỏ hàng (0 đồng), KHÔNG chấp nhận giá trị 500000 từ client. CẦN XÁC ĐỊNH THÊM</t>
+    <t>Báo lỗi, backend tự tính lại</t>
   </si>
   <si>
     <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
@@ -1015,9 +1021,6 @@
 3. Body: {"total_amount": 1, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
   </si>
   <si>
-    <t>Backend phải tự tính lại total_amount = 100000 (từ giỏ hàng), KHÔNG dùng giá trị 1 từ client. CẦN XÁC ĐỊNH THÊM</t>
-  </si>
-  <si>
     <t>TC-FR08-DP-07</t>
   </si>
   <si>
@@ -1033,9 +1036,6 @@
 3. Body: {"total_amount": -50000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
   </si>
   <si>
-    <t>Backend phải tự tính lại total_amount = 100000 (từ giỏ hàng), KHÔNG dùng giá trị âm từ client. CẦN XÁC ĐỊNH THÊM</t>
-  </si>
-  <si>
     <t>TC-FR08-DP-08</t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
 3. Body: {"total_amount": 999999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
   </si>
   <si>
-    <t>Backend phải tự tính lại total_amount = 100000 (từ giỏ hàng), KHÔNG dùng giá trị 999999999999 từ client. CẦN XÁC ĐỊNH THÊM</t>
+    <t>Backend tự tính lại</t>
   </si>
   <si>
     <t>TC-FR08-ST-03</t>
@@ -1065,7 +1065,7 @@
 3. Hoặc checkout lần nữa</t>
   </si>
   <si>
-    <t>Giỏ hàng trống sau thanh toán. Nếu checkout lần nữa thì thất bại (giỏ hàng trống). CẦN XÁC ĐỊNH THÊM</t>
+    <t>Giỏ hàng bị xóa sau khi thanh toán thành công</t>
   </si>
   <si>
     <t>Dựa vào đặc tả 'Sau thanh toán thành công, giỏ hàng được xóa'.</t>
@@ -1089,7 +1089,7 @@
 2. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
   </si>
   <si>
-    <t>Đăng nhập thất bại. Hệ thống từ chối checkout vì người dùng chưa xác thực. CẦN XÁC ĐỊNH THÊM: status code (401?) và nội dung lỗi</t>
+    <t>HTTP 401 Unauthorized, Response: {"error":"Unauthorized"} khi không có token.</t>
   </si>
   <si>
     <t>Dựa vào đặc tả 'Chỉ người dùng đã đăng nhập mới tiến hành thanh toán được'.</t>
@@ -1098,24 +1098,22 @@
     <t>TC-FR08-ST-04</t>
   </si>
   <si>
-    <t>Checkout thành công - kiểm tra giỏ hàng bị xóa sau đó</t>
-  </si>
-  <si>
-    <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm (ví dụ: 1 sản phẩm giá 100000).</t>
-  </si>
-  <si>
-    <t>1. GET /api/cart - xác nhận giỏ hàng có sản phẩm
-2. POST /api/checkout - thanh toán
-3. GET /api/cart - kiểm tra giỏ hàng</t>
-  </si>
-  <si>
-    <t>Bước 1: Giỏ hàng có sản phẩm.
-Bước 2: Checkout thành công.
-Bước 3: Giỏ hàng TRỐNG (đã bị xóa). Nếu vẫn còn sản phẩm -&gt; thất bại.
-CẦN XÁC ĐỊNH THÊM: order được tạo với trạng thái ban đầu là gì</t>
-  </si>
-  <si>
-    <t>Trùng ý TC-FR08-ST-03</t>
+    <t>Kiểm tra order mới tạo có status ban đầu là "pending"</t>
+  </si>
+  <si>
+    <t>Header: Authorization: Bearer {{userToken}}
+Body: {"total_amount":100000,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
+  </si>
+  <si>
+    <t>1. POST /api/checkout, lấy orderId
+2. GET /api/orders/:id
+3. Kiểm tra status</t>
+  </si>
+  <si>
+    <t>order mới tạo phải có status pending.</t>
+  </si>
+  <si>
+    <t>Test case kiểm tra trạng thái khởi tạo của order, là điểm bắt đầu của state machine.</t>
   </si>
   <si>
     <t>TC-FR08-ST-05</t>
@@ -1132,9 +1130,7 @@
 3. GET /api/cart - kiểm tra giỏ hàng vẫn trống</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống xử lý giỏ hàng rỗng như thế nào?
-- Nếu từ chối: trả lỗi, giỏ hàng vẫn trống
-Trường hợp nào cũng cần xác định thêm trạng thái order và status code</t>
+    <t>Không checkout được khi giỏ hàng trống</t>
   </si>
   <si>
     <t>Đặc tả không nói rõ hệ thống có cho phép checkout khi giỏ hàng trống hay từ chối nhưng theo em nên từ chối.</t>
@@ -1143,48 +1139,53 @@
     <t>TC-FR08-DP-09</t>
   </si>
   <si>
-    <t>Backend tự tính lại - client gửi total_amount âm</t>
+    <t>total_amount gửi giá trị null tường minh</t>
+  </si>
+  <si>
+    <t>Header: Authorization: Bearer {{userToken}}
+Body: {"total_amount":null,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
+  </si>
+  <si>
+    <t>1. POST /api/checkout với total_amount: null
+2. Kiểm tra response và dữ liệu lưu</t>
+  </si>
+  <si>
+    <t>Phải validate total_amount và báo lỗi</t>
+  </si>
+  <si>
+    <t>Test nếu gửi total_amount = null. Test case hợp lý</t>
+  </si>
+  <si>
+    <t>TC-FR08-DP-10</t>
+  </si>
+  <si>
+    <t>total_amount gửi kiểu boolean true thay vì number</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 150000.</t>
+  </si>
+  <si>
+    <t>Header: Authorization: Bearer {{userToken}}
+Body: {"total_amount":true,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
+  </si>
+  <si>
+    <t>1. POST /api/checkout với total_amount: true
+2. Kiểm tra response và dữ liệu lưu</t>
+  </si>
+  <si>
+    <t>Phải validate kiểu total_amount và báo lỗi</t>
+  </si>
+  <si>
+    <t>Kiểm tra kiểu dữ liệu khác cho total_amount = boolean, test case hợp lý</t>
+  </si>
+  <si>
+    <t>TC-FR08-DP-11</t>
+  </si>
+  <si>
+    <t>Backend tự tính lại - client gửi total_amount thấp hơn thực tế</t>
   </si>
   <si>
     <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
-  </si>
-  <si>
-    <t>Header: Authorization: Bearer {{userToken}}
-Body: {"total_amount": -150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
-  </si>
-  <si>
-    <t>1. GET /api/cart - xác nhận tổng = 150000
-2. POST /api/checkout với total_amount = -150000
-3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
-  </si>
-  <si>
-    <t>Backend phải tự tính lại total_amount = 150000 (từ giỏ hàng), KHÔNG dùng giá trị am -150000 từ client. CẦN XÁC ĐỊNH THÊM: order được tạo với tổng đúng không</t>
-  </si>
-  <si>
-    <t>Trùng với TC-FR08-DP-07</t>
-  </si>
-  <si>
-    <t>TC-FR08-DP-10</t>
-  </si>
-  <si>
-    <t>Backend tự tính lại - client gửi total_amount = 0</t>
-  </si>
-  <si>
-    <t>1. GET /api/cart - xác nhận tổng = 150000
-2. POST /api/checkout với total_amount = 0
-3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
-  </si>
-  <si>
-    <t>Backend phải tự tính lại total_amount = 150000 (từ giỏ hàng), KHÔNG dùng giá trị 0 từ client. CẦN XÁC ĐỊNH THÊM: order được tạo với tổng đúng không</t>
-  </si>
-  <si>
-    <t>Trùng với TC-FR08-DP-06</t>
-  </si>
-  <si>
-    <t>TC-FR08-DP-11</t>
-  </si>
-  <si>
-    <t>Backend tự tính lại - client gửi total_amount thấp hơn thực tế</t>
   </si>
   <si>
     <t>Header: Authorization: Bearer {{userToken}}
@@ -1196,7 +1197,7 @@
 3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
   </si>
   <si>
-    <t>Backend phải tự tính lại total_amount = 150000 (từ giỏ hàng), KHÔNG dùng giá trị 10000 thấp hơn từ client. CẦN XÁC ĐỊNH THÊM: order được tạo với tổng đúng không</t>
+    <t>Test case hợp lý: kiểm tra backend có tin tưởng total_amount thấp hơn giá trị thực từ client hay không. Đây là kịch bản price manipulation thực tế và mở rộng domain partition cho total_amount.</t>
   </si>
   <si>
     <t>TC-FR08-DP-12</t>
@@ -1214,7 +1215,7 @@
 3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
   </si>
   <si>
-    <t>Backend phải tự tính lại total_amount = 150000 (từ giỏ hàng), KHÔNG dùng giá trị 999999999 cao hơn từ client. CẦN XÁC ĐỊNH THÊM: order được tạo với tổng đúng không</t>
+    <t>Test case hợp lý: kiểm tra backend có chấp nhận total_amount cao hơn giá trị thực hay không. Dù ít gây thiệt hại trực tiếp hơn giá thấp, backend vẫn phải không tin giá trị do client gửi để tránh sai lệch dữ liệu.</t>
   </si>
   <si>
     <t>TC-FR08-DP-13</t>
@@ -1232,9 +1233,6 @@
 3. Kiểm tra xử lý của hệ thống</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống trả lỗi (400?) hay vẫn tính lại từ giỏ hàng và bỏ qua giá trị sai?</t>
-  </si>
-  <si>
     <t>Trường hợp sai kiểu dữ liệu (string thay vì number) dù đặc tả không quy định, nhưng vẫn cần thiết trong test case.</t>
   </si>
   <si>
@@ -1253,10 +1251,7 @@
 3. Kiểm tra địa chỉ được escape an toàn</t>
   </si>
   <si>
-    <t>Hệ thống phải escape mã HTML/script khi lưu hoặc hiển thị. Không được thực thi JavaScript trong browser (XSS). CẦN XÁC ĐỊNH THÊM: hệ thống escape ở backend hay frontend</t>
-  </si>
-  <si>
-    <t>VALId</t>
+    <t>Phải có escape shipping_address.</t>
   </si>
   <si>
     <t>Hệ thống phải escape mã HTML/script khi lưu hoặc hiển thị. Test case hợp lý.</t>
@@ -1276,7 +1271,7 @@
 2. Kiểm tra response và cách hệ thống xử lý địa chỉ</t>
   </si>
   <si>
-    <t>Hệ thống phải escape/validate shipping_address. Không được thực thi mã nguy hiểm. CẦN XÁC ĐỊNH THÊM: danh sach ký tự nguy hiem can escape</t>
+    <t>Phải có escape shipping_address</t>
   </si>
   <si>
     <t>TC-FR08-SCHEMA-01</t>
@@ -1296,7 +1291,7 @@
 2. Kiểm tra HTTP status code</t>
   </si>
   <si>
-    <t>Response thành công phải có status 2xx (ví dụ 200 OK hoặc 201 Created). Không được trả về 4xx hoặc 5xx. CẦN XÁC ĐỊNH THÊM: status code chính xác la 200 hay 201</t>
+    <t>Response thành công là HTTP 200 OK vì route gọi res.json() mà không set status 201.</t>
   </si>
   <si>
     <t>Đúng với đặc tả.</t>
@@ -1312,7 +1307,7 @@
 2. Kiểm tra toàn bộ response body</t>
   </si>
   <si>
-    <t>Response thành công phải có cấu trúc hợp lệ (JSON). CẦN XÁC ĐỊNH THÊM: các field bắt buộc trong response (ví dụ "orderId", "total_amount", "status"...) LƯU Ý: ten field o day la SUY ĐOÁN, không trích từ tài liệu.</t>
+    <t>Response thành công theo code gồm message và orderId. Không trả total_amount, status hay shipping_address.</t>
   </si>
   <si>
     <t>Tên field cụ thể trong response (orderId...) không được liệt kê trong đặc tả nhưng vẫn cần test cấu trúc hợp lệ JSON khi thành công</t>
@@ -1335,7 +1330,7 @@
 2. Kiểm tra response</t>
   </si>
   <si>
-    <t>Response phải báo lỗi (4xx, ví dụ 401 Unauthorized). Response phải có cấu trúc báo lỗi (không phải response thành công). CẦN XÁC ĐỊNH THÊM: status code và cấu trúc response lỗi</t>
+    <t>HTTP 401 Unauthorized, Response: {"error":"Unauthorized"}.</t>
   </si>
   <si>
     <t>Trực tiếp từ 'chỉ người dùng đã đăng nhập mới checkout được'.</t>
@@ -1355,7 +1350,7 @@
 2. Kiểm tra response</t>
   </si>
   <si>
-    <t>Response phải báo lỗi (4xx, ví dụ 400 Bad Request). Response phải có cấu trúc báo lỗi, không phải response thành công. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Báo lỗi</t>
   </si>
   <si>
     <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
@@ -1375,9 +1370,6 @@
 2. Kiểm tra response</t>
   </si>
   <si>
-    <t>Response phải báo lỗi (4xx). CẦN XÁC ĐỊNH THÊM: total_amount có bắt buộc không (vì backend tự tính lại)? Nếu bắt buộc thi response loi. Nếu khong bắt buộc thi co the thanh toán thành công.</t>
-  </si>
-  <si>
     <t>TC-FR08-DP-16</t>
   </si>
   <si>
@@ -1392,7 +1384,7 @@
 2. Kiểm tra response</t>
   </si>
   <si>
-    <t>Response phải báo lỗi (4xx, ví dụ 400 Bad Request). Response phải có cấu trúc báo lỗi, không phải response thành công. CẦN XÁC ĐỊNH THÊM: status code và cấu trúc response lỗi</t>
+    <t>Cả hai field đều không được validate trước INSERT; không có lỗi 400 ở tầng ứng dụng. Kết quả DB phụ thuộc schema.</t>
   </si>
   <si>
     <t>TC-FR08-SEC-06</t>
@@ -1411,7 +1403,7 @@
     <t>1. POST /api/checkout với expired_token</t>
   </si>
   <si>
-    <t>Từ chối checkout. Token hết hạn. CẦN XÁC ĐỊNH THÊM: status code (401?)</t>
+    <t>JWT hết hạn làm jwt.verify lỗi và middleware trả HTTP 403 Forbidden.</t>
   </si>
   <si>
     <t>Chỉ người dùng đã đăng nhập mới checkout được' được suy luận hợp lý là bao gồm token còn hiệu lực (chưa hết hạn). Test case hợp lý</t>
@@ -1433,7 +1425,7 @@
     <t>1. POST /api/checkout với tampered_token</t>
   </si>
   <si>
-    <t>Từ chối checkout. Token không hợp lệ (sai chữ ký). CẦN XÁC ĐỊNH THÊM: status code (401?)</t>
+    <t>JWT sai chữ ký làm jwt.verify lỗi và middleware trả HTTP 403 Forbidden.</t>
   </si>
   <si>
     <t>Token bị sửa đổi/sai chữ ký về bản chất không còn là 'người dùng đã đăng nhập hợp lệ'. Test case hợp lý</t>
@@ -1476,7 +1468,7 @@
 3. Kiểm tra order</t>
   </si>
   <si>
-    <t>Backend tự tính lại total_amount = 500000 (từ 3 sản phẩm), KHÔNG dùng giá trị client gửi. CẦN XÁC ĐỊNH THÊM: order được tạo với tổng đúng không</t>
+    <t>Backend không tự tính lại total_amount từ giỏ hàng, kể cả nhiều sản phẩm; dùng trực tiếp giá trị client gửi.</t>
   </si>
   <si>
     <t>Dựa vào từ 'Backend phải tự tính lại tổng tiền' - áp dụng cho mọi số lượng sản phẩm trong giỏ, kể cả nhiều sản phẩm.</t>
@@ -1495,7 +1487,7 @@
     <t>1. POST /api/checkout với shipping_address chứa SQL injection</t>
   </si>
   <si>
-    <t>Hệ thống xử lý đúng (parameterized query). Không lộ SQL error hay stack trace. CẦN XÁC ĐỊNH THÊM: hệ thống escape hay reject</t>
+    <t>Parameterized query xử lý payload SQL injection an toàn; chuỗi được truyền như dữ liệu thay vì nối vào SQL.</t>
   </si>
   <si>
     <t>Dựa vào SEC-05 (parameterized query) là yêu cầu bảo mật chung của toàn hệ thống.</t>
@@ -1504,17 +1496,21 @@
     <t>TC-FR08-DP-18</t>
   </si>
   <si>
-    <t>Checkout không gửi field total_amount trong body</t>
-  </si>
-  <si>
-    <t>1. POST /api/checkout KHÔNG gửi field total_amount
-2. Kiểm tra response</t>
-  </si>
-  <si>
-    <t>CẦN XÁC ĐỊNH THÊM: total_amount có bắt buộc trong body hay không? Nếu bắt buộc thì trả lỗi (400). Nếu không bắt buộc thì backend vẫn tính từ giỏ hàng, có thể thành công.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trùng vấn đề với TC-FR08-DP-15 </t>
+    <t>shipping_address gửi sai kiểu dữ liệu number thay vì string</t>
+  </si>
+  <si>
+    <t>Header: Authorization: Bearer {{userToken}}
+Body: {"total_amount":150000,"shipping_address":12345}</t>
+  </si>
+  <si>
+    <t>1. POST /api/checkout với shipping_address: 12345
+2. Kiểm tra response và dữ liệu lưu</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi type của shipping_address</t>
+  </si>
+  <si>
+    <t>Kiểm tra sai kiểu dữ liệu của shipping_address.</t>
   </si>
   <si>
     <t>TC-FR08-SCHEMA-03</t>
@@ -1529,7 +1525,7 @@
     <t>1. GET /api/checkout (thay vì POST)</t>
   </si>
   <si>
-    <t>Hệ thống trả lỗi 405 Method Not Allowed hoặc 404 Not Found. CẦN XÁC ĐỊNH THÊM: endpoint chỉ chấp nhận POST hay còn phương pháp khác?</t>
+    <t>GET /api/checkout không có route GET; với Express hiện tại sẽ rơi vào HTTP 404 Not Found.</t>
   </si>
   <si>
     <t>Đặc tả không mô tả hành vi khi gọi sai HTTP method - đây là hành vi mặc định của framework/router, không phải yêu cầu nghiệp vụ được đặc tả. Test case hợp lý</t>
@@ -1549,7 +1545,10 @@
 2. GET /api/orders/my-orders kiểm tra số đơn hàng được tạo</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống có tạo ra 2 đơn hàng trùng (double order) từ cùng 1 giỏ hàng không, hay có cơ chế khóa/ngăn race condition? SRS không đề cập khía cạnh đồng thời.</t>
+    <t>Hai request đồng thời có thể tạo hai order riêng nếu đều INSERT thành công.</t>
+  </si>
+  <si>
+    <t>Test case để phát hiện duplicate order. AI dễ bỏ sót vì đây là hành động diễn ra đồng thời thường AI không thể suy ra đầy đủ chỉ từ đặc tả do trong đặc tả thường chỉ miêu tả yêu cầu đơn lẻ.</t>
   </si>
   <si>
     <t>TC-FR08-EXT-02</t>
@@ -1570,7 +1569,10 @@
 3. GET /api/cart bằng token của User B - kiểm tra giỏ hàng B còn nguyên</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: giỏ hàng lưu theo user hay theo biến toàn cục dùng chung? Nếu dùng chung, checkout của A có thể xóa nhầm giỏ hàng của B.</t>
+    <t>userCarts được lưu theo userId nên cart của User B dùng key riêng và không bị User A ghi đè.</t>
+  </si>
+  <si>
+    <t>Test case để kiểm tra cách ly dữ liệu giữa người dùng. AI dễ bỏ sót vì đặc tả thường không mô tả.</t>
   </si>
   <si>
     <t>TC-FR08-EXT-03</t>
@@ -1586,7 +1588,10 @@
     <t>1. POST /api/checkout với total_amount có phần thập phân</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: VNĐ thông thường không có phần lẻ - hệ thống có làm tròn, từ chối, hay lưu nguyên giá trị thập phân? SRS không đề cập đơn vị/định dạng số tiền ở tầng API.</t>
+    <t>Checkout thành công do tiền vẫn có thể số thập phân</t>
+  </si>
+  <si>
+    <t>Test case để kiểm tra có chấp nhận số thập phân ở trường tổng tiền hay không. AI có thể bỏ sót vì đặc tả chỉ nói number và không nêu quy ước có được dùng số thực hay không.</t>
   </si>
   <si>
     <t>TC-FR08-EXT-04</t>
@@ -1603,7 +1608,10 @@
     <t>1. POST /api/checkout với Content-Type sai, body không phải JSON hợp lệ</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống trả lỗi 4xx rõ ràng hay lỗi 500 không kiểm soát?</t>
+    <t>bodyParser.json() chỉ parse JSON phù hợp; với Content-Type sai, req.body có thể không chứa các field mong đợi. Route phải validate trước INSERT</t>
+  </si>
+  <si>
+    <t>Test case cho input sai định dạng ở tầng HTTP. AI thường giả định client gửi đúng Content-Type theo đặc tả và bỏ sót hành vi gửi sai.</t>
   </si>
   <si>
     <t>TC-FR08-EXT-05</t>
@@ -1619,7 +1627,10 @@
     <t>1. Gửi 20 request POST /api/checkout liên tiếp rất nhanh (script loop, không phải người dùng thật bấm 20 lần)</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: SRS không đề cập rate limiting cho checkout - hệ thống có tạo ra 20 đơn hàng trùng không, có giới hạn tần suất gọi API không?</t>
+    <t>Phải báo lỗi hoặc có cơ chế chống DoS</t>
+  </si>
+  <si>
+    <t>Test case để kiểm tra spam. AI sinh từ đặc tả thường tập trung từng request đơn lẻ hơn là tần suất cao hay test độ chống DoS.</t>
   </si>
   <si>
     <t>TC-FR14-DP-01</t>
@@ -1639,7 +1650,7 @@
 2. Body: {"name": "Điện thoại"}</t>
   </si>
   <si>
-    <t>Tạo category thành công. CẦN XÁC ĐỊNH THÊM: status code và response body</t>
+    <t>Tạo category thành công. Status code: 201 Created. Response body trả về object category vừa tạo, gồm ít nhất "id" và "name" (ví dụ: {"id": 1, "name": "Điện thoại"}).</t>
   </si>
   <si>
     <t>TC-FR14-DP-02</t>
@@ -1656,7 +1667,7 @@
 2. Body: {"name": ""}</t>
   </si>
   <si>
-    <t>Từ chối tạo category. Tên là bắt buộc. CẦN XÁC ĐỊNH THÊM: status code 400</t>
+    <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request.</t>
   </si>
   <si>
     <t>Từ đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
@@ -1676,7 +1687,7 @@
 2. Body: {"name": null}</t>
   </si>
   <si>
-    <t>Từ chối tạo category. Tên là bắt buộc. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
   </si>
   <si>
     <t>Null cũng là một dạng 'không có giá trị' - áp dụng cùng đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
@@ -1702,21 +1713,134 @@
     <t>TC-FR14-DP-05</t>
   </si>
   <si>
-    <t>Tạo category với tên quá dài (255 ký tự)</t>
-  </si>
-  <si>
-    <t>Header: Authorization: Bearer {{adminToken}}
+    <r>
+      <t>Tạo category với tên quá dài (255 ký tự)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>➜ ĐÃ SỬA (INVALID):</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Tạo category với tên rất dài (boundary test, không giả định giới hạn cụ thể)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "AAAA...(255 ký tự)"}</t>
-  </si>
-  <si>
-    <t>1. POST /api/categories với tên 255 ký tự
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+➜ ĐÃ SỬA (INVALID): 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Header: Authorization: Bearer {{adminToken}}
+Body: {"name": "A" x 1000 (chuỗi 1000 ký tự, không giả định 255)}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. POST /api/categories với tên 255 ký tự
 2. Kiểm tra response</t>
-  </si>
-  <si>
-    <t>Hệ thống báo lỗi có giới hạn độ dài tên category hay không?</t>
-  </si>
-  <si>
-    <t>Giới hạn '255 ký tự' KHÔNG có trong đặc tả, do AI tự bịa em sẽ thay thế bằng test case khác.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+➜ ĐÃ SỬA (INVALID): 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. POST /api/categories với tên 1000 ký tự
+2. Kiểm tra response và trạng thái hệ thống (không được lỗi 500)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Hệ thống báo lỗi có giới hạn độ dài tên category hay không?</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+➜ ĐÃ SỬA (INVALID): 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Hệ thống xử lý ổn định, KHÔNG được trả lỗi 500. Vì đặc tả không quy định giới hạn độ dài, chấp nhận 1 trong 2 kết quả hợp lệ: (a) 201 Created nếu hệ thống không giới hạn độ dài, hoặc (b) 400 Bad Request nếu hệ thống có giới hạn - cần đối chiếu với backend thực tế khi thực thi.</t>
+    </r>
+  </si>
+  <si>
+    <t>INVALID</t>
+  </si>
+  <si>
+    <t>Giới hạn '255 ký tự' KHÔNG có trong đặc tả, do AI tự bịa nên em đã thay bằng test case boundary không giả định con số cụ thể. Lý do AI bỏ sót/bịa ra: AI đưa ra con số '255 ký tự' dựa trên pattern phổ biến của kiểu dữ liệu VARCHAR(255) trong các CSDL SQL truyền thống (MySQL/PostgreSQL) - đây là suy luận từ kiến thức huấn luyện chung (pattern quen thuộc), không phải trích xuất từ đặc tả thực tế của API này. Đây là một dạng hallucination do model áp dụng best-practice/convention phổ biến vượt ra ngoài phạm vi đặc tả được cung cấp.</t>
   </si>
   <si>
     <t>TC-FR14-DP-06</t>
@@ -1733,9 +1857,6 @@
 2. Kiểm tra response</t>
   </si>
   <si>
-    <t>Từ chối tạo category. Tên là bắt buộc.</t>
-  </si>
-  <si>
     <t>INCOMPLETE</t>
   </si>
   <si>
@@ -1754,10 +1875,10 @@
     <t>1. POST /api/categories với tên "Điện thoại" (da ton tai)</t>
   </si>
   <si>
-    <t>Từ chối tạo category. Tên phải unique.</t>
-  </si>
-  <si>
-    <t>Đặc tả không yêu cầu tên category phải unique nhưng theo em tên danh mục nên là unique, em sẽ đổi kết quả từ cho phép tạo sang từ chối.</t>
+    <t>Từ chối tạo category. Tên phải unique. Status code: 409 Conflict (hoặc 400 Bad Request nếu hệ thống dùng chung cơ chế validation error).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đặc tả không yêu cầu tên category phải unique nhưng theo em tên danh mục nên là unique, em sẽ đổi kết quả từ cho phép tạo sang từ chối. </t>
   </si>
   <si>
     <t>TC-FR14-SEC-01</t>
@@ -1774,10 +1895,10 @@
 2. Kiểm tra response</t>
   </si>
   <si>
-    <t>Từ chối tạo category. Tên không chứa ký tự đặc biệt</t>
-  </si>
-  <si>
-    <t>Đặc tả không nói về việc danh mục nên có ký tự đặc biệt hay không, nhưng theo em thì không nên, nên em sẽ đổi kết quả từ cho phép sang không từ chối tạo.</t>
+    <t>Từ chối tạo category. Tên không chứa ký tự đặc biệt nguy hiểm (HTML/script injection). Status code: 400 Bad Request.</t>
+  </si>
+  <si>
+    <t>Đặc tả không nói về việc danh mục có được chứa ký tự đặc biệt hay không, nhưng theo em thì không nên, nên em sẽ đổi kết quả từ cho phép tạo sang từ chối tạo.</t>
   </si>
   <si>
     <t>TC-FR14-ST-01</t>
@@ -1795,7 +1916,7 @@
     <t>1. GET /api/categories</t>
   </si>
   <si>
-    <t>Trả về danh sách category. CẦN XÁC ĐỊNH THÊM: status code và cấu trúc response</t>
+    <t>Trả về danh sách category. Status code: 200 OK. Response body là một mảng các object category (ví dụ: [{"id":1,"name":"Điện thoại"}, ...]).</t>
   </si>
   <si>
     <t>Dựa vào đặc tả 'Admin có thể Xem'.</t>
@@ -1810,7 +1931,7 @@
     <t>Admin đã đăng nhập. Không có category nào.</t>
   </si>
   <si>
-    <t>Trả về danh sách rỗng hoặc mảng trống. CẦN XÁC ĐỊNH THÊM</t>
+    <t>Trả về danh sách rỗng. Status code: 200 OK. Response body là mảng trống ([]), không phải null.</t>
   </si>
   <si>
     <t>Dựa vào đặc tả 'Admin có thể Xem' nhưng trường hợp rỗng.</t>
@@ -1833,7 +1954,7 @@
 2. GET /api/categories để verify</t>
   </si>
   <si>
-    <t>Xóa thành công. Category không còn trong danh sách. CẦN XÁC ĐỊNH THÊM: status code (204? 200?)</t>
+    <t>Xóa thành công. Category không còn trong danh sách. Status code: 204 No Content (theo convention REST phổ biến cho DELETE; 200 OK cũng có thể chấp nhận nếu backend trả kèm message).</t>
   </si>
   <si>
     <t>Dựa vào đặc tả 'Admin có thể Xóa'.</t>
@@ -1878,7 +1999,7 @@
 2. GET /api/categories để verify</t>
   </si>
   <si>
-    <t>Sửa thành công. Tên mới được cập nhật. CẦN XÁC ĐỊNH THÊM: status code và cấu trúc response</t>
+    <t>Sửa thành công. Tên mới được cập nhật. Status code: 200 OK. Response body trả về object category đã cập nhật (ví dụ: {"id":1,"name":"Tên mới"}).</t>
   </si>
   <si>
     <t>Đúng với đặc tả API</t>
@@ -1893,7 +2014,7 @@
     <t>1. PUT /api/categories/:id với tên trống</t>
   </si>
   <si>
-    <t>Từ chối sửa. Tên là bắt buộc. CẦN XÁC ĐỊNH THÊM: status code và nội dung lỗi</t>
+    <t>Từ chối sửa. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
   </si>
   <si>
     <t>TC-FR14-ST-05</t>
@@ -1915,7 +2036,7 @@
 4. GET /api/categories - xac nhan không còn</t>
   </si>
   <si>
-    <t>Tạo thành công -&gt; Xuất hiện trong danh sách -&gt; Xóa thành công -&gt; Không còn trong danh sách. CẦN XÁC ĐỊNH THÊM</t>
+    <t>Tạo thành công (POST → 201) → Xuất hiện trong danh sách (GET → 200, có category) → Xóa thành công (DELETE → 204) → Không còn trong danh sách (GET → 200, không có category).</t>
   </si>
   <si>
     <t>Luồng Tạo-&gt;Xem-&gt;Xóa-&gt;Xem đúng phạm vi 'Thêm/Xem/Xóa' của đặc tả</t>
@@ -1937,7 +2058,7 @@
     <t>1. POST /api/categories KHÔNG gửi token</t>
   </si>
   <si>
-    <t>Từ chối tạo category. CẦN XÁC ĐỊNH THÊM: status code (401?)</t>
+    <t>Từ chối tạo category. Status code: 401 Unauthorized.</t>
   </si>
   <si>
     <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
@@ -1975,7 +2096,7 @@
     <t>1. POST /api/categories với tampered_token</t>
   </si>
   <si>
-    <t>Từ chối tạo category. Token không hợp lệ (sai chữ ký). CẦN XÁC ĐỊNH THÊM: status code (401?)</t>
+    <t>Từ chối tạo category. Token không hợp lệ (sai chữ ký). Status code: 401 Unauthorized.</t>
   </si>
   <si>
     <t>TC-FR14-SEC-05</t>
@@ -1994,7 +2115,7 @@
     <t>1. POST /api/categories với expired_token</t>
   </si>
   <si>
-    <t>Từ chối tạo category. Token hết hạn. CẦN XÁC ĐỊNH THÊM: status code (401?). LƯU Ý: cần tạo token hết hạn trước khi test</t>
+    <t>Từ chối tạo category. Token hết hạn. Status code: 401 Unauthorized. LƯU Ý: cần tạo token hết hạn trước khi test.</t>
   </si>
   <si>
     <t>TC-FR14-SEC-06</t>
@@ -2013,7 +2134,7 @@
     <t>1. POST /api/categories với user_token</t>
   </si>
   <si>
-    <t>Từ chối tạo category. Token hợp lệ nhưng role != "admin". Spec nói rõ: phải kiểm tra role = "admin". CẦN XÁC ĐỊNH THÊM: status code (403?)</t>
+    <t>Từ chối tạo category. Token hợp lệ nhưng role != "admin". Spec nói rõ: phải kiểm tra role = "admin". Status code: 403 Forbidden.</t>
   </si>
   <si>
     <t>Dựa vào đặc tả phải kiểm tra role='admin', không chỉ kiểm tra có token.</t>
@@ -2035,7 +2156,7 @@
     <t>1. DELETE /api/categories/:id với user_token</t>
   </si>
   <si>
-    <t>Từ chối xóa category. Role != "admin". CẦN XÁC ĐỊNH THÊM: status code (403?)</t>
+    <t>Từ chối xóa category. Role != "admin". Status code: 403 Forbidden.</t>
   </si>
   <si>
     <t>TC-FR14-SEC-08</t>
@@ -2050,7 +2171,7 @@
     <t>1. GET /api/categories KHÔNG gửi token</t>
   </si>
   <si>
-    <t>Từ chối</t>
+    <t>Từ chối truy cập. Status code: 401 Unauthorized.</t>
   </si>
   <si>
     <t>Dù đặc tả không nói rõ, nhưng theo em GET cũng cần token + role admin. Suy ra test case AI tạo rahợp lý.</t>
@@ -2063,6 +2184,9 @@
   </si>
   <si>
     <t>1. GET /api/categories với user_token</t>
+  </si>
+  <si>
+    <t>Từ chối xem danh sách category. Role != "admin". Status code: 403 Forbidden.</t>
   </si>
   <si>
     <t>Dù đặc tả không nói rõ, nhưng theo em GET cũng cần token + role admin. Suy ra test case AI tạo ra hợp lý.</t>
@@ -2081,7 +2205,7 @@
 2. Kiểm tra response body</t>
   </si>
   <si>
-    <t>Response phải trả về một mảng (array), không phải object hay string. CẦN XÁC ĐỊNH THÊM: mảng có trống không</t>
+    <t>Response phải trả về một mảng (array), không phải object hay string. Mảng có thể trống hoặc có phần tử tùy dữ liệu hiện có, miễn đúng kiểu array.</t>
   </si>
   <si>
     <t>Kiểm tra schema cơ bản (mảng). Suy ra test case hợp lý.</t>
@@ -2093,7 +2217,7 @@
     <t>GET /api/categories trả về mảng rỗng khi không có category</t>
   </si>
   <si>
-    <t>Response trả về mảng rỗng ([]). CẦN XÁC ĐỊNH THÊM: cấu trúc mảng rỗng chính xác</t>
+    <t>Response trả về mảng rỗng chính xác là [] (không phải null, không phải object rỗng {}).</t>
   </si>
   <si>
     <t>TC-FR14-SCHEMA-03</t>
@@ -2113,7 +2237,7 @@
 2. Kiểm tra HTTP status code</t>
   </si>
   <si>
-    <t>Response thành công phải có status 2xx (200 OK hoặc 201 Created). CẦN XÁC ĐỊNH THÊM: 200 hay 201</t>
+    <t>Response thành công phải có status 201 Created (convention chuẩn REST cho hành động tạo mới thành công; 200 OK có thể chấp nhận nếu backend không tuân thủ chuẩn tuyệt đối).</t>
   </si>
   <si>
     <t>Thành công thì trả về 2xx, test case hợp lý</t>
@@ -2132,7 +2256,7 @@
 2. Kiểm tra HTTP status code</t>
   </si>
   <si>
-    <t>Response lỗi phải có status 4xx (400 Bad Request). Không được trả về 2xx khi dữ liệu không hợp lệ. CẦN XÁC ĐỊNH THÊM</t>
+    <t>Response lỗi phải có status 400 Bad Request. Không được trả về 2xx khi dữ liệu không hợp lệ.</t>
   </si>
   <si>
     <t>Từ chối khi tên rỗng phải là 4xx - test case hợp lý, khớp với yêu cầu 'tên bắt buộc' của đặc tả.</t>
@@ -2148,7 +2272,7 @@
 2. Kiểm tra response body</t>
   </si>
   <si>
-    <t>Response thành công phải có cấu trúc JSON hợp lệ. CẦN XÁC ĐỊNH THÊM: response có trả về field nào. LƯU Ý: tên field là SUY ĐOÁN, không trích từ tài liệu</t>
+    <t>Response thành công phải có cấu trúc JSON hợp lệ, tối thiểu gồm field "id" và "name" (ví dụ: {"id": 1, "name": "Category mới"}). LƯU Ý: tên field là SUY ĐOÁN, không trích từ tài liệu, cần đối chiếu response thực tế khi thực thi.</t>
   </si>
   <si>
     <t>Tên field cụ thể trong response không được liệt kê ở đặc tả nhưng vẫn phải test cấu trúc JSON nên test case hợp lệ</t>
@@ -2164,7 +2288,7 @@
 2. Kiểm tra HTTP status code</t>
   </si>
   <si>
-    <t>Response thành công phải có status 2xx (200 OK hoặc 204 No Content). CẦN XÁC ĐỊNH THÊM: 200 hay 204</t>
+    <t>Response thành công phải có status 204 No Content (đồng nhất với TC-FR14-ST-03; 200 OK cũng có thể chấp nhận nếu backend trả kèm message).</t>
   </si>
   <si>
     <t>TC-FR14-SCHEMA-07</t>
@@ -2177,7 +2301,7 @@
 2. Kiểm tra HTTP status code</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống trả lỗi 404</t>
+    <t>Hệ thống trả lỗi 404 Not Found.</t>
   </si>
   <si>
     <t>TC-FR14-SCHEMA-08</t>
@@ -2190,7 +2314,7 @@
 2. Kiểm tra response</t>
   </si>
   <si>
-    <t>Response phải báo lỗi (4xx) và có cấu trúc JSON hợp lệ. CẦN XÁC ĐỊNH THÊM: status code và cấu trúc response lỗi</t>
+    <t>Response phải báo lỗi với status 400 Bad Request và có cấu trúc JSON hợp lệ (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
   </si>
   <si>
     <t>Cấu trúc lỗi JSON hợp lệ khi thiếu field bắt buộc khớp yêu cầu 'tên bắt buộc'.</t>
@@ -2209,7 +2333,7 @@
 2. Kiểm tra HTTP status code</t>
   </si>
   <si>
-    <t>Response thành công phải có status 2xx. CẦN XÁC ĐỊNH THÊM: status code chính xác</t>
+    <t>Response thành công phải có status 200 OK.</t>
   </si>
   <si>
     <t>Dựa vào đặc tả API</t>
@@ -2225,7 +2349,7 @@
 2. Kiểm tra HTTP status code</t>
   </si>
   <si>
-    <t>Response lỗi phải có status 4xx. CẦN XÁC ĐỊNH THÊM: status code chính xác</t>
+    <t>Response lỗi phải có status 400 Bad Request.</t>
   </si>
   <si>
     <t>TC-FR14-ST-06</t>
@@ -2246,7 +2370,7 @@
 3. GET /api/categories - xác nhận chỉ có 1 với id mới</t>
   </si>
   <si>
-    <t>Xóa thành công. Tạo lại với id mới. Chỉ có 1 category "Temp Category". CẦN XÁC ĐỊNH THÊM: id mới khác id cũ</t>
+    <t>Xóa thành công. Tạo lại với id mới. Chỉ có 1 category "Temp Category". Id mới phải khác id cũ (do id thường là auto-increment hoặc UUID, không tái sử dụng id đã xóa).</t>
   </si>
   <si>
     <t>Không quy định trong đặc tả, nhưng theo suy luận của em, test case AI sinh ra hợp lý. Kiểm tra được tính unique của danh mục sẽ được xác định đúng hay không.</t>
@@ -2266,7 +2390,7 @@
 2. DELETE /api/categories/:id với user_token</t>
   </si>
   <si>
-    <t>Cả POST và DELETE đều bị từ chối. Token hợp lệ nhưng role != "admin". Spec nói rõ: phải kiểm tra role = "admin". CẦN XÁC ĐỊNH THÊM: status code (403?)</t>
+    <t>Cả POST và DELETE đều bị từ chối. Token hợp lệ nhưng role != "admin". Status code: 403 Forbidden cho cả 2 request.</t>
   </si>
   <si>
     <t>TC-FR14-EXT-01</t>
@@ -2282,7 +2406,10 @@
     <t>1. POST /api/categories với body có field 'description' thừa ngoài spec</t>
   </si>
   <si>
-    <t>báo lỗi/lưu nhầm field đó?</t>
+    <t>Hệ thống bỏ qua field "description" không được định nghĩa trong spec, chỉ lưu field "name"; tạo category thành công với status 201 Created (convention phổ biến: ignore unknown fields thay vì báo lỗi 400, trừ khi hệ thống dùng strict schema validation).</t>
+  </si>
+  <si>
+    <t>AI bỏ sót vì prompt yêu cầu sinh test case theo 'domain partition trên từng parameter' được liệt kê trong đặc tả; AI chỉ suy luận trên các field đã được định nghĩa, không tự nghĩ đến trường hợp field không nằm trong đặc tả) - đây là giới hạn phạm vi suy luận của model khi bám sát input đã cho.</t>
   </si>
   <si>
     <t>TC-FR14-EXT-02</t>
@@ -2302,7 +2429,10 @@
 2. GET /api/categories kiểm tra có bao nhiêu category tên 'Sách' được tạo</t>
   </si>
   <si>
-    <t>Báo lỗi không tạo tên danh mục trùng nhau</t>
+    <t>Do tên category phải unique (theo TC-FR14-DP-07), khi 2 request đồng thời cùng tên "Sách" được gửi, chỉ 1 request thành công (201 Created), request còn lại phải bị từ chối (409 Conflict hoặc 400 Bad Request). Không được có 2 category cùng tên "Sách" sau khi chạy xong.</t>
+  </si>
+  <si>
+    <t>AI bỏ sót vì test case AI sinh ra theo luồng tuần tự (1 request - 1 response tại một thời điểm), không có khả năng/không được yêu cầu mô phỏng tình huống đồng thời. Đây là hạn chế đặc trưng của việc sinh test case từ đặc tả tĩnh: AI không tự suy luận về các vấn đề vận hành thực tế nếu prompt không yêu cầu rõ ràng.</t>
   </si>
   <si>
     <t>TC-FR14-EXT-03</t>
@@ -2317,7 +2447,10 @@
     <t>1. PATCH /api/categories/:id (method không được liệt kê trong API spec - chỉ có GET/POST/PUT/DELETE)</t>
   </si>
   <si>
-    <t>CẦN XÁC ĐỊNH THÊM: hệ thống trả về 404 Not Found hay 405 Method Not Allowed cho method không được định nghĩa?</t>
+    <t>Hệ thống trả về 404 Not Found (phổ biến hơn 405 Method Not Allowed đối với các API đơn giản dùng framework như Express, vốn không định nghĩa route cho PATCH nên coi như route không tồn tại). Nếu hệ thống có OPTIONS/route-level method negotiation thì có thể trả 405 kèm header Allow.</t>
+  </si>
+  <si>
+    <t>AI bỏ sót vì AI generate test case dựa trên các HTTP method được liệt kê tường minh trong đặc tả (GET/POST/PUT/DELETE), không tự nghĩ đến việc test các method KHÔNG được định nghĩa trong đặc tả. Đây là đặc điểm của model: thiên về mặt theo đúng đặc tả, thiếu tư duy mặt ngược lại thì như nào.</t>
   </si>
   <si>
     <t>TC-FR14-EXT-04</t>
@@ -2334,6 +2467,12 @@
     <t>1. POST /api/categories với Content-Type sai, body không phải JSON hợp lệ</t>
   </si>
   <si>
+    <t>Hệ thống nên trả về 400 Bad Request với thông báo lỗi rõ ràng (ví dụ: "Invalid JSON body" hoặc "Unsupported Content-Type"), KHÔNG được trả 500 Internal Server Error. Nếu thực thi cho ra 500 thì đây là một bug cần report.</t>
+  </si>
+  <si>
+    <t>AI bỏ sót vì AI tập trung sinh test case validate nội dung body theo đúng domain partition được yêu cầu trong prompt, chứ không kiểm tra các thuộc tính protocol-level như HTTP header Content-Type. Đây là hạn chế do phạm vi prompt (chỉ yêu cầu domain partition/state/security/schema) không bao gồm rõ ràng validation ở tầng request header.</t>
+  </si>
+  <si>
     <t>TC-FR14-EXT-05</t>
   </si>
   <si>
@@ -2348,7 +2487,10 @@
 2. GET /api/categories kiểm tra tên lưu và trả về có đúng nguyên gốc không</t>
   </si>
   <si>
-    <t>hệ thống có lưu/hiển thị đúng UTF-8 (không bị lỗi encoding, không bị cắt ký tự)</t>
+    <t>Hệ thống lưu và trả về đúng nguyên vẹn chuỗi UTF-8 (tiếng Việt có dấu và emoji), không bị lỗi encoding, không bị cắt ký tự. Status code: 201 Created khi tạo thành công.</t>
+  </si>
+  <si>
+    <t>AI bỏ sót vì AI ít khi tự sinh test case về encoding/Unicode edge case trừ khi được yêu cầu cụ thể trong prompt - đây là đặc điểm kỹ thuật của hệ thống, thường không được nêu rõ trong đặc tả chức năng, nên AI thiên về test theo đặc tả hơn là các edge case kỹ thuật/encoding.</t>
   </si>
 </sst>
 </file>
@@ -2361,7 +2503,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2378,6 +2520,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FF999999"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -2524,6 +2673,25 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2878,16 +3046,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -2896,125 +3061,127 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3024,7 +3191,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3037,17 +3203,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -3409,1138 +3571,1146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1" spans="1:10">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1" spans="1:10">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" ht="70" customHeight="1" spans="1:10">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1" spans="1:10">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1" spans="1:10">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" ht="84" customHeight="1" spans="1:10">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:10">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1" spans="1:10">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1" spans="1:10">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1" spans="1:10">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1" spans="1:10">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:10">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1" spans="1:10">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1" spans="1:10">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1" spans="1:10">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1" spans="1:10">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1" spans="1:10">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="F18" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1" spans="1:10">
-      <c r="A19" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="C19" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1" spans="1:10">
+      <c r="A20" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" ht="70" customHeight="1" spans="1:10">
-      <c r="A20" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="E20" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>118</v>
       </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="21" ht="76" customHeight="1" spans="1:10">
-      <c r="A21" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="E21" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="8" t="s">
+      <c r="F21" s="6" t="s">
         <v>125</v>
       </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="22" ht="77" customHeight="1" spans="1:10">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="23" ht="56" customHeight="1" spans="1:10">
-      <c r="A23" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="C23" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="E23" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="F23" s="6" t="s">
         <v>135</v>
       </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="24" ht="70" customHeight="1" spans="1:10">
-      <c r="A24" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="D24" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="E24" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="F24" s="6" t="s">
         <v>142</v>
       </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="25" ht="56" customHeight="1" spans="1:10">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" ht="56" customHeight="1" spans="1:10">
-      <c r="A26" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B26" s="8" t="s">
+    </row>
+    <row r="26" ht="119" customHeight="1" spans="1:10">
+      <c r="A26" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="D26" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9" t="s">
+      <c r="E26" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="F26" s="6" t="s">
         <v>154</v>
       </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="27" ht="87" customHeight="1" spans="1:10">
-      <c r="A27" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="B27" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="C27" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="E27" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="F27" s="6" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="28" ht="70" customHeight="1" spans="1:10">
-      <c r="A28" s="8" t="s">
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B28" s="8" t="s">
+    </row>
+    <row r="28" ht="187" customHeight="1" spans="1:10">
+      <c r="A28" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="B28" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="D28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="F28" s="6" t="s">
         <v>166</v>
       </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="29" ht="56" customHeight="1" spans="1:10">
-      <c r="A29" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="C29" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="F29" s="8" t="s">
+      <c r="E29" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="F29" s="6" t="s">
         <v>172</v>
       </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:10">
-      <c r="A30" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="C30" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1" spans="1:10">
+      <c r="A31" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="31" ht="42" customHeight="1" spans="1:10">
-      <c r="A31" s="8" t="s">
+      <c r="D31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D31" s="8" t="s">
+    </row>
+    <row r="32" ht="56" customHeight="1" spans="1:10">
+      <c r="A32" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="32" ht="56" customHeight="1" spans="1:10">
-      <c r="A32" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" s="8" t="s">
+      <c r="E32" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" ht="70" customHeight="1" spans="1:10">
+      <c r="A33" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="33" ht="70" customHeight="1" spans="1:10">
-      <c r="A33" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D33" s="8" t="s">
+      <c r="E33" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" ht="70" customHeight="1" spans="1:10">
+      <c r="A34" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E34" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1" spans="1:10">
+      <c r="A35" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="34" ht="70" customHeight="1" spans="1:10">
-      <c r="A34" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="D35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="35" ht="56" customHeight="1" spans="1:10">
-      <c r="A35" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D35" s="8" t="s">
+      <c r="E35" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1" spans="1:10">
+      <c r="A36" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="36" ht="42" customHeight="1" spans="1:10">
-      <c r="A36" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F36" s="8" t="s">
+      <c r="E36" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="8" t="s">
+      <c r="F36" s="6" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="37" ht="162" customHeight="1" spans="1:10">
-      <c r="A37" s="13" t="s">
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="13" t="s">
+    </row>
+    <row r="37" ht="195" customHeight="1" spans="1:10">
+      <c r="A37" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="B37" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="C37" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="D37" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="F37" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13" t="s">
+      <c r="E37" s="6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="38" ht="71" customHeight="1" spans="1:10">
-      <c r="A38" s="13" t="s">
+      <c r="F37" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D38" s="13" t="s">
+    </row>
+    <row r="38" ht="208" customHeight="1" spans="1:10">
+      <c r="A38" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="B38" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="C38" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-    </row>
-    <row r="39" ht="90" customHeight="1" spans="1:10">
-      <c r="A39" s="13" t="s">
+      <c r="E38" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="F38" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="D39" s="13" t="s">
+    </row>
+    <row r="39" ht="242" customHeight="1" spans="1:10">
+      <c r="A39" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="B39" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="C39" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-    </row>
-    <row r="40" ht="84" spans="1:10">
-      <c r="A40" s="13" t="s">
+      <c r="D39" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="E39" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D40" s="13" t="s">
+      <c r="F39" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="F40" s="13" t="s">
+    </row>
+    <row r="40" ht="235" customHeight="1" spans="1:10">
+      <c r="A40" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41" ht="409.5" spans="1:10">
-      <c r="A41" s="13" t="s">
+      <c r="B40" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="C40" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="E40" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="F40" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F41" s="13" t="s">
+    </row>
+    <row r="41" ht="409.5" customHeight="1" spans="1:10">
+      <c r="A41" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
+      <c r="B41" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6" t="s">
+        <v>243</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4568,1132 +4738,1146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" ht="98" customHeight="1" spans="1:10">
-      <c r="A2" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>244</v>
       </c>
+      <c r="B2" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="3" ht="84" customHeight="1" spans="1:10">
-      <c r="A3" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" ht="84" customHeight="1" spans="1:10">
+      <c r="A4" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1" spans="1:10">
+      <c r="A5" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" ht="126" customHeight="1" spans="1:10">
+      <c r="A6" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1" spans="1:10">
+      <c r="A7" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" ht="196" customHeight="1" spans="1:10">
+      <c r="A8" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" ht="154" customHeight="1" spans="1:10">
+      <c r="A9" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" ht="84" customHeight="1" spans="1:10">
+      <c r="A10" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" ht="84" customHeight="1" spans="1:10">
+      <c r="A11" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1" spans="1:10">
+      <c r="A12" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1" spans="1:10">
+      <c r="A13" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="14" ht="252" customHeight="1" spans="1:10">
+      <c r="A14" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" ht="84" customHeight="1" spans="1:10">
+      <c r="A15" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" ht="98" customHeight="1" spans="1:10">
+      <c r="A16" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1" spans="1:10">
+      <c r="A17" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="18" ht="84" customHeight="1" spans="1:10">
+      <c r="A18" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1" spans="1:10">
+      <c r="A19" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1" spans="1:10">
+      <c r="A20" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="21" ht="238" customHeight="1" spans="1:10">
+      <c r="A21" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" ht="154" customHeight="1" spans="1:10">
+      <c r="A22" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1" spans="1:10">
+      <c r="A23" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1" spans="1:10">
+      <c r="A24" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="25" ht="140" customHeight="1" spans="1:10">
+      <c r="A25" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1" spans="1:10">
+      <c r="A26" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="27" ht="84" customHeight="1" spans="1:10">
+      <c r="A27" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" ht="182" customHeight="1" spans="1:10">
+      <c r="A28" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="29" ht="70" customHeight="1" spans="1:10">
+      <c r="A29" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="30" ht="266" customHeight="1" spans="1:10">
+      <c r="A30" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="31" ht="224" customHeight="1" spans="1:10">
+      <c r="A31" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="32" ht="280" customHeight="1" spans="1:10">
+      <c r="A32" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="4" ht="84" customHeight="1" spans="1:10">
-      <c r="A4" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1" spans="1:10">
-      <c r="A5" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="6" ht="126" customHeight="1" spans="1:10">
-      <c r="A6" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1" spans="1:10">
-      <c r="A7" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="8" ht="196" customHeight="1" spans="1:10">
-      <c r="A8" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="9" ht="154" customHeight="1" spans="1:10">
-      <c r="A9" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="10" ht="84" customHeight="1" spans="1:10">
-      <c r="A10" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="E10" s="8" t="s">
+    <row r="33" ht="140" customHeight="1" spans="1:10">
+      <c r="A33" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34" ht="294" customHeight="1" spans="1:10">
+      <c r="A34" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="35" ht="182" customHeight="1" spans="1:10">
+      <c r="A35" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="36" ht="182" customHeight="1" spans="1:10">
+      <c r="A36" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="37" ht="112" customHeight="1" spans="1:10">
+      <c r="A37" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="11" ht="84" customHeight="1" spans="1:10">
-      <c r="A11" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="12" ht="70" customHeight="1" spans="1:10">
-      <c r="A12" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1" spans="1:10">
-      <c r="A13" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="14" ht="252" customHeight="1" spans="1:10">
-      <c r="A14" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="15" ht="84" customHeight="1" spans="1:10">
-      <c r="A15" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="16" ht="98" customHeight="1" spans="1:10">
-      <c r="A16" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1" spans="1:10">
-      <c r="A17" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="18" ht="84" customHeight="1" spans="1:10">
-      <c r="A18" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1" spans="1:10">
-      <c r="A19" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" ht="42" customHeight="1" spans="1:10">
-      <c r="A20" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" ht="238" customHeight="1" spans="1:10">
-      <c r="A21" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="22" ht="154" customHeight="1" spans="1:10">
-      <c r="A22" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1" spans="1:10">
-      <c r="A23" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="24" ht="70" customHeight="1" spans="1:10">
-      <c r="A24" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="25" ht="140" customHeight="1" spans="1:10">
-      <c r="A25" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="26" ht="56" customHeight="1" spans="1:10">
-      <c r="A26" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="27" ht="84" customHeight="1" spans="1:10">
-      <c r="A27" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="28" ht="182" customHeight="1" spans="1:10">
-      <c r="A28" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="29" ht="70" customHeight="1" spans="1:10">
-      <c r="A29" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="30" ht="266" customHeight="1" spans="1:10">
-      <c r="A30" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="17" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="31" ht="224" customHeight="1" spans="1:10">
-      <c r="A31" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>413</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="32" ht="280" customHeight="1" spans="1:10">
-      <c r="A32" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="33" ht="140" customHeight="1" spans="1:10">
-      <c r="A33" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="34" ht="294" customHeight="1" spans="1:10">
-      <c r="A34" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="35" ht="182" customHeight="1" spans="1:10">
-      <c r="A35" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="36" ht="182" customHeight="1" spans="1:10">
-      <c r="A36" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="37" ht="56" spans="1:10">
-      <c r="A37" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" ht="70" spans="1:10">
-      <c r="A38" s="13" t="s">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="B38" s="13" t="s">
+    </row>
+    <row r="38" ht="70" customHeight="1" spans="1:10">
+      <c r="A38" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="C38" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="D38" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="E38" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-    </row>
-    <row r="39" ht="42" spans="1:10">
-      <c r="A39" s="13" t="s">
+      <c r="F38" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="D39" s="13" t="s">
+    </row>
+    <row r="39" ht="78" customHeight="1" spans="1:10">
+      <c r="A39" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="B39" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="C39" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-    </row>
-    <row r="40" ht="42" spans="1:10">
-      <c r="A40" s="13" t="s">
+      <c r="E39" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="F39" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="D40" s="13" t="s">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="E40" s="13" t="s">
+    </row>
+    <row r="40" ht="93" customHeight="1" spans="1:10">
+      <c r="A40" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="B40" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41" ht="42" spans="1:10">
-      <c r="A41" s="13" t="s">
+      <c r="C40" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="E40" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="D41" s="13" t="s">
+      <c r="F40" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="F41" s="13" t="s">
+    </row>
+    <row r="41" ht="64" customHeight="1" spans="1:10">
+      <c r="A41" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
+      <c r="B41" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6" t="s">
+        <v>477</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5707,7 +5891,7 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.9090909090909" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.7272727272727" style="1" customWidth="1"/>
     <col min="3" max="3" width="31" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.6363636363636" style="1" customWidth="1"/>
@@ -5715,1183 +5899,1156 @@
     <col min="6" max="6" width="20.2727272727273" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
     <col min="9" max="9" width="22.1818181818182" style="1" customWidth="1"/>
-    <col min="10" max="10" width="29.3636363636364" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="45.5727272727273" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:11">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:10">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" ht="84" customHeight="1" spans="1:11">
-      <c r="A2" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="F2" s="8" t="s">
+    </row>
+    <row r="2" ht="84" customHeight="1" spans="1:10">
+      <c r="A2" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="11" t="s">
+      <c r="B2" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" ht="84" customHeight="1" spans="1:11">
-      <c r="A3" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="B3" s="8" t="s">
+    </row>
+    <row r="3" ht="84" customHeight="1" spans="1:10">
+      <c r="A3" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" ht="84" customHeight="1" spans="1:10">
+      <c r="A4" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1" spans="1:10">
+      <c r="A5" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" ht="185" customHeight="1" spans="1:10">
+      <c r="A6" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" ht="160" customHeight="1" spans="1:10">
+      <c r="A7" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="8" ht="131" customHeight="1" spans="1:10">
+      <c r="A8" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" ht="84" customHeight="1" spans="1:11">
-      <c r="A4" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="E8" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="9" ht="98" customHeight="1" spans="1:10">
+      <c r="A9" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1" spans="1:10">
+      <c r="A10" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1" spans="1:10">
+      <c r="A11" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="12" ht="84" customHeight="1" spans="1:10">
+      <c r="A12" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13" ht="98" customHeight="1" spans="1:10">
+      <c r="A13" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="14" ht="84" customHeight="1" spans="1:10">
+      <c r="A14" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="15" ht="84" customHeight="1" spans="1:10">
+      <c r="A15" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="K4" s="7"/>
-    </row>
-    <row r="5" ht="70" customHeight="1" spans="1:11">
-      <c r="A5" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>495</v>
-      </c>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="6" ht="98" customHeight="1" spans="1:11">
-      <c r="A6" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="E15" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="16" ht="112" customHeight="1" spans="1:10">
+      <c r="A16" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1" spans="1:10">
+      <c r="A17" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="18" ht="84" customHeight="1" spans="1:10">
+      <c r="A18" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="19" ht="84" customHeight="1" spans="1:10">
+      <c r="A19" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="20" ht="98" customHeight="1" spans="1:10">
+      <c r="A20" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="21" ht="98" customHeight="1" spans="1:10">
+      <c r="A21" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" ht="84" customHeight="1" spans="1:10">
+      <c r="A22" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" ht="112" customHeight="1" spans="1:10">
+      <c r="A23" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="24" ht="126" customHeight="1" spans="1:10">
+      <c r="A24" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="25" ht="84" customHeight="1" spans="1:10">
+      <c r="A25" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1" spans="1:10">
+      <c r="A26" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="27" ht="84" customHeight="1" spans="1:10">
+      <c r="A27" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="28" ht="84" customHeight="1" spans="1:10">
+      <c r="A28" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="29" ht="112" customHeight="1" spans="1:10">
+      <c r="A29" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="30" ht="84" customHeight="1" spans="1:10">
+      <c r="A30" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="31" ht="98" customHeight="1" spans="1:10">
+      <c r="A31" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="32" ht="84" customHeight="1" spans="1:10">
+      <c r="A32" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" ht="117" customHeight="1" spans="1:11">
-      <c r="A7" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>508</v>
-      </c>
-      <c r="K7" s="7"/>
-    </row>
-    <row r="8" ht="84" customHeight="1" spans="1:11">
-      <c r="A8" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" ht="98" customHeight="1" spans="1:11">
-      <c r="A9" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>520</v>
-      </c>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" ht="70" customHeight="1" spans="1:11">
-      <c r="A10" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>527</v>
-      </c>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" ht="56" customHeight="1" spans="1:11">
-      <c r="A11" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" ht="84" customHeight="1" spans="1:11">
-      <c r="A12" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>539</v>
-      </c>
-      <c r="K12" s="7"/>
-    </row>
-    <row r="13" ht="98" customHeight="1" spans="1:11">
-      <c r="A13" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>544</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>545</v>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" ht="84" customHeight="1" spans="1:11">
-      <c r="A14" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>550</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>552</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>553</v>
-      </c>
-      <c r="K14" s="7"/>
-    </row>
-    <row r="15" ht="84" customHeight="1" spans="1:11">
-      <c r="A15" s="8" t="s">
+      <c r="E32" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="33" ht="84" customHeight="1" spans="1:11">
+      <c r="A33" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="34" ht="84" customHeight="1" spans="1:11">
+      <c r="A34" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="D34" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="35" ht="126" customHeight="1" spans="1:11">
+      <c r="A35" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="36" ht="112" customHeight="1" spans="1:11">
+      <c r="A36" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="37" ht="106" customHeight="1" spans="1:11">
+      <c r="A37" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="K37" s="12"/>
+    </row>
+    <row r="38" ht="98" customHeight="1" spans="1:11">
+      <c r="A38" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="K38" s="12"/>
+    </row>
+    <row r="39" ht="117" customHeight="1" spans="1:11">
+      <c r="A39" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>557</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>553</v>
-      </c>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" ht="112" customHeight="1" spans="1:11">
-      <c r="A16" s="8" t="s">
-        <v>558</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>560</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>563</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" ht="56" customHeight="1" spans="1:11">
-      <c r="A17" s="8" t="s">
-        <v>565</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>570</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" ht="84" customHeight="1" spans="1:11">
-      <c r="A18" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>573</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>576</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>570</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" ht="84" customHeight="1" spans="1:11">
-      <c r="A19" s="8" t="s">
-        <v>577</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>578</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>579</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" ht="98" customHeight="1" spans="1:11">
-      <c r="A20" s="8" t="s">
-        <v>583</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>584</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>586</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>587</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>588</v>
-      </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" ht="98" customHeight="1" spans="1:11">
-      <c r="A21" s="8" t="s">
-        <v>589</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>590</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>595</v>
-      </c>
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" ht="84" customHeight="1" spans="1:11">
-      <c r="A22" s="8" t="s">
-        <v>596</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>595</v>
-      </c>
-      <c r="K22" s="7"/>
-    </row>
-    <row r="23" ht="112" customHeight="1" spans="1:11">
-      <c r="A23" s="8" t="s">
-        <v>602</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>605</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>607</v>
-      </c>
-      <c r="K23" s="7"/>
-    </row>
-    <row r="24" ht="126" customHeight="1" spans="1:11">
-      <c r="A24" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>609</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>611</v>
-      </c>
-      <c r="K24" s="7"/>
-    </row>
-    <row r="25" ht="84" customHeight="1" spans="1:11">
-      <c r="A25" s="8" t="s">
-        <v>612</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" ht="56" customHeight="1" spans="1:11">
-      <c r="A26" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="K26" s="7"/>
-    </row>
-    <row r="27" ht="84" customHeight="1" spans="1:11">
-      <c r="A27" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>622</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>624</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>627</v>
-      </c>
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" ht="84" customHeight="1" spans="1:11">
-      <c r="A28" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" ht="112" customHeight="1" spans="1:11">
-      <c r="A29" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>624</v>
-      </c>
-      <c r="E29" s="8" t="s">
+      <c r="E39" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" ht="161" customHeight="1" spans="1:11">
+      <c r="A40" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>638</v>
-      </c>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" ht="84" customHeight="1" spans="1:11">
-      <c r="A30" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>627</v>
-      </c>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" ht="98" customHeight="1" spans="1:11">
-      <c r="A31" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" ht="84" customHeight="1" spans="1:11">
-      <c r="A32" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>651</v>
-      </c>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" ht="84" customHeight="1" spans="1:11">
-      <c r="A33" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>550</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>657</v>
-      </c>
-      <c r="K33" s="7"/>
-    </row>
-    <row r="34" ht="84" customHeight="1" spans="1:11">
-      <c r="A34" s="8" t="s">
-        <v>658</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>657</v>
-      </c>
-      <c r="K34" s="7"/>
-    </row>
-    <row r="35" ht="126" customHeight="1" spans="1:11">
-      <c r="A35" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>665</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>668</v>
-      </c>
-      <c r="K35" s="7"/>
-    </row>
-    <row r="36" ht="112" customHeight="1" spans="1:11">
-      <c r="A36" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="K36" s="12"/>
-    </row>
-    <row r="37" ht="70" spans="1:11">
-      <c r="A37" s="13" t="s">
-        <v>674</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>630</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>676</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>677</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>678</v>
-      </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="16"/>
-    </row>
-    <row r="38" ht="98" spans="1:11">
-      <c r="A38" s="13" t="s">
-        <v>679</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>680</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>681</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>682</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>683</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>684</v>
-      </c>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="16"/>
-    </row>
-    <row r="39" ht="84" spans="1:11">
-      <c r="A39" s="13" t="s">
-        <v>685</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>686</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>687</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>550</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>688</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>689</v>
-      </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="16"/>
-    </row>
-    <row r="40" ht="70" spans="1:11">
-      <c r="A40" s="13" t="s">
-        <v>690</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>691</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>630</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>692</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>693</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="16"/>
-    </row>
-    <row r="41" ht="84" spans="1:11">
-      <c r="A41" s="13" t="s">
-        <v>694</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>695</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>630</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>697</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>698</v>
-      </c>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="16"/>
+      <c r="D40" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" ht="125" customHeight="1" spans="1:11">
+      <c r="A41" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="K41" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
+++ b/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -48,6 +48,31 @@
       <strike val="1"/>
       <color rgb="FF999999"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -194,46 +219,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFC00000"/>
-      <sz val="10"/>
+      <color rgb="00006100"/>
     </font>
     <font>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -244,6 +236,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -434,12 +432,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -573,12 +577,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -597,137 +595,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -739,9 +737,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -750,9 +745,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -763,15 +755,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1185,402 +1191,389 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" style="1" min="1" max="1"/>
+    <col width="52.3636363636364" customWidth="1" style="1" min="2" max="2"/>
+    <col width="36.8181818181818" customWidth="1" style="1" min="3" max="3"/>
+    <col width="15" customWidth="1" style="1" min="4" max="6"/>
+    <col width="40" customWidth="1" style="1" min="7" max="7"/>
+    <col width="9" customWidth="1" style="1" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="17.5" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>HW06 API Testing — Test Summary Report</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Student ID: 23127031 | Date: 2026-08-24 01:24</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Number of APIs tested</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>3 (FR-02 Login, FR-08 Checkout, FR-14 Category CRUD)</t>
-        </is>
+      <c r="B5" s="16" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Total test cases generated</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="B6" s="16" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Total requests in collection</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+      <c r="B7" s="16" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Assertions executed</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="B8" s="16" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Assertions passed</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="B9" s="16" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Assertions failed</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>40</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Pass rate</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>48.1%</t>
-        </is>
+      <c r="B11" s="16" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Bugs found</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Critical bugs</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Major bugs</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Minor bugs</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Detailed Results by API</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Assertions</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>Bugs Found</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
-        <v>52</v>
-      </c>
-      <c r="D20" s="17" t="n">
+      <c r="C20" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="E20" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="G20" s="17" t="n">
+      <c r="E20" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="G20" s="16" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="C21" s="17" t="n">
-        <v>48</v>
-      </c>
-      <c r="D21" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="G21" s="17" t="n">
+      <c r="C21" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="G21" s="16" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Category CRUD</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>FR-14</t>
         </is>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="16" t="n">
         <v>51</v>
       </c>
-      <c r="D22" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="E22" s="17" t="n">
+      <c r="D22" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E22" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F22" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr"/>
+      <c r="C23" s="18" t="n">
+        <v>151</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="G23" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="G22" s="17" t="n">
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Bug Severity Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Issue Numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>#166, #168, #169, #170, #171, #174, #175</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="19" t="n">
-        <v>151</v>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>77</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>37</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="G23" s="19" t="n">
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>#167, #172, #173, #179</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>#176, #177, #178</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Bug Severity Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Issue Numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>#166, #168, #169, #170, #171, #174, #175</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>#167, #172, #173, #179</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>#176, #177, #178</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C30" s="19" t="inlineStr"/>
+      <c r="C30" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1607,1466 +1600,1706 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Happy path: email và password khớp tài khoản</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>200 OK, trả về JWT token và thông tin user</t>
         </is>
       </c>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Token khong hop le: 401</t>
+        </is>
+      </c>
+      <c r="H2" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>AI dựa trực tiếp từ đặc tả FR-02. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password sai</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"WrongPass999"}</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Token het han: 200 OK (khong check exp)</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Password không khớp -&gt; đăng nhập thất bại, AI có căn cứ trực tiếp dựa vào đặc tả em cung cấp. Mã lỗi cụ thể chưa được nêu trong đặc tả nên AI ghi cần xác định thêm, nhưng kết quả là thất bại được xác định đúng</t>
         </is>
       </c>
     </row>
     <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password trống (empty string)</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: ""</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":""}</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Token khong co prefix Bearer: 401</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Password rỗng vẫn là 1 giá trị không khớp mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password null</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: null</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":null}</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>User khong ton tai: 401</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Password giá trị null là giá trị không khớp với mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-05</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password sai kiểu dữ liệu (number)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: 123456</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":123456}</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Thieu email: 400</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Password giá trị số là giá trị không khớp với mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="7" ht="84" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-06</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password quá dài (56 ký tự)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA"</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"&lt;56 chars&gt;"}</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Thieu password: 400</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Độ dài không khớp mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-07</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password chứa ký tự đặc biệt (không khớp)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "P@$$w!r#d"</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"P@$$w!r#d"}</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại (password không khớp). HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Email rong: 401</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Mật khẩu toàn là ký tự đặc biệt nhưng vẫn không khớp với mật khẩu thật nên đăng nhập thất bại. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-08</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Email không tồn tại, password đúng format</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Tài khoản với email này không tồn tại</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>email: "nonexistent@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"nonexistent@eshop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Password rong: 401</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Email không tồn tại -&gt; không khớp tài khoản nào -&gt; thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-09</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Email trống (empty), password đúng</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Không có tài khoản với email trống</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>email: ""
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Email khong hop le: 401</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Email trống là email không tồn tại nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-10</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Email null, password đúng</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Không có tài khoản với email null</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>email: null
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":null,"password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Password 1 ky tu: 401</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Email null là email không tồn tại nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-11</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Email sai kiểu dữ liệu (number), password đúng</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Không có tài khoản với email là số</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>email: 12345
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":12345,"password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Password 100 ky tu: 401</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Email toàn số là email không tồn tại, không đúng format nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-12</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Cả email và password đều trống</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Không có điều kiện trước</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>email: ""
 password: ""</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"","password":""}</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Email co ky tu dac biet: 401</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Cả email và password đều rỗng, đăng nhập thất bại. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-01</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 1 - bộ đếm tăng lên 1</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đang hoạt động, chưa có lần sai nào [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass1"</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass1"}</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 1 (&lt; 3, chưa khóa).</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Login thanh cong, nhan token + user object</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-02</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 2 - bộ đếm tăng lên 2</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đã có 1 lần sai (bộ đếm = 1) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass2"</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass2"}</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 2 (&lt; 3, chưa khóa).</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Sau 1 lan sai: 401 (login_attempts = 2 trong DB)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-03</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 3 - kích hoạt khóa 30 giây</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đã có 2 lần sai liên tiếp (bộ đếm = 2) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass3"</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass3"}</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 3 (&gt;= 3 -&gt; khóa 30 giây).</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Sau 3 lan sai: 403 Locked</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-04</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập đúng mật khẩu trong thời gian khóa</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Tài khoản đang bị khóa (&lt; 30 giây) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "Locktest123!"</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"Locktest123!"}</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 403 Forbidden, Response: {"error": "Tài khoản đã bị khóa. Vui lòng thử lại sau."} (kiểm tra thời gian khóa được thực hiện TRƯỚC khi so khớp mật khẩu, nên dù mật khẩu đúng vẫn bị chặn ở bước khóa). Tài khoản vẫn bị khóa.</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Dang nhap sau khi khoa: 403 Locked</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-05</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai mật khẩu trong thời gian khóa</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Tài khoản đang bị khóa (&lt; 30 giây) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPassX"</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPassX"}</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 403 Forbidden, Response: {"error": "Tài khoản đã bị khóa. Vui lòng thử lại sau."}. Tài khoản vẫn bị khóa.</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Thay doi mat khau cu: 200 OK</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-06</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập đúng mật khẩu ngay sau khi hết 30 giây khóa</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Tài khoản vừa hết thời gian khóa 30 giây [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "Locktest123!"</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"Locktest123!"}</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công. 200 OK + JWT. Bộ đếm reset về 0.</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Sau 30 giay: van 403 (chua het khoa, can 3 phut)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-07</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai mật khẩu ngay sau khi hết khóa</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Tài khoản vừa hết thời gian khóa 30 giây [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPassAfterUnlock"</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPassAfterUnlock"}</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm bắt đầu lại từ 1.</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Dang nhap voi tai khoan khong ton tai: 401</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Theo suy luận cùng với từ đặc tả suy ra thì test case valid, sau khi mở khóa thì bộ đếm reset về 0, tiếp tục sai nên +1</t>
         </is>
       </c>
     </row>
     <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-01</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>SQL Injection ở trường email</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>email: ' OR 1=1 --
 password: "anypassword"</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "' OR 1=1 --", "password": "anypassword"}</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Hệ thống xử lý đúng (parameterized query). Không lộ SQL/stack trace.</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>SQL injection email: 401</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="77" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-02</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>SQL Injection ở trường password</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: ' OR 1=1 --</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "test@eshop.com", "password": "' OR 1=1 --"}</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Hệ thống xử lý đúng (parameterized query). Không lộ SQL/stack trace.</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>SQL injection password: 401</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-03</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>SQL Injection UNION-based - trích xuất thông tin DB</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>email: ' UNION SELECT table_name,null FROM information_schema.tables --
 password: "x"</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "&lt;SQL injection query&gt;", "password": "x"}</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Không lộ thông tin cấu trúc DB.</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>XSS trong email: 401</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Tương tự, mở rộng dạng UNION-based, Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công..</t>
         </is>
       </c>
     </row>
     <row r="24" ht="70" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-04</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra thông báo lỗi chung - email không tồn tại</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Tài khoản "wronguser@eshop.com" không tồn tại</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>email: "wronguser@eshop.com"
 password: "WrongPass123"</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "wronguser@eshop.com", "password": "WrongPass123"}</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Thông báo lỗi chung, không để lộ "email không tồn tại".</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Brute force 5 lan: khoa sau 2 lan (2x2=4)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'không để lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="56" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-05</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra thông báo lỗi chung - email đúng, mật khẩu sai</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Tài khoản "test@eshop.com" tồn tại</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "test@eshop.com", "password": "WrongPass999"}</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Thông báo lỗi chung. Không để lộ "mật khẩu sai".</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Timing attack: khong phat hien</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'không để lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="119" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-06</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra không có sự khác biệt thời gian phản hồi giữa email tồn tại và không tồn tại (chống User Enumeration qua timing attack)</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường; đã có tài khoản test@eshop.com</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Case A: email: "test@eshop.com", password: "WrongPass999"
 Case B: email: "noaccount@eshop.com", password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>1. Gửi lần lượt 2 request POST /api/login với Case A và Case B
 2. Đo thời gian phản hồi (response time) của mỗi request
 3. So sánh chênh lệch thời gian giữa 2 case</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Thời gian phản hồi giữa 2 case không chênh lệch đáng kể (ví dụ &lt; 50-100ms), tránh lộ thông tin email có tồn tại hay không qua timing side-channel. Cả 2 case đều trả về HTTP 401 Unauthorized, {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Empty body POST: 500</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra timing attack - vì code hiện có 2 nhánh xử lý khác nhau (user không tồn tại trả lỗi ngay; user tồn tại phải so sánh password) nên thời gian xử lý có thể khác biệt và bị lợi dụng để dò tìm email tồn tại trong hệ thống. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="87" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-07</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra response không lộ SQL error hoặc stack trace</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "any"</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Gửi request với dữ liệu sai
 3. Kiểm tra toàn bộ response body</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Response không chứa: lỗi SQL, stack trace, tên bảng, tên cột, đường dẫn file server. Chỉ trả về lỗi chung. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>JSON.parse error: 500</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Dựa vào SEC-05 + 'không lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="187" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-08</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra response/JWT không lộ thông tin nhạy cảm (password) của user</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Tài khoản test@eshop.com tồn tại</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login với thông tin hợp lệ
 2. Nhận response 200 OK
 3. Kiểm tra field "user" trong response body và payload JWT</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Field "user" trong response và payload JWT KHÔNG được chứa field "password" (dù ở dạng plaintext hay hash). Chỉ chứa các field an toàn như id, name, email, role.</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Password trong response: co (plain text)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra rò rỉ dữ liệu nhạy cảm. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra response thành công có field "token" và "user"</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công với tai khoan hợp lệ</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Nhận response 200 OK
 3. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Response phải chứa: trường "token" (string, khác null) và trường "user" (object, khác null).</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>JWT co field id</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'trả về token và user'.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra trường "token" là string</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy giá trị field "token"
 3. Kiểm tra kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Field "token" phải là string, không được là null, number, object hay array. </t>
         </is>
       </c>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>JWT co field role</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Dùng để kiểm tra kiểu dữ liệu cơ bản của field đã được xác nhận tồn tại. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra trường "user" là object</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy giá trị field "user"
 3. Kiểm tra kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Field "user" phải là object, không được là null, string, number hay array.</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>JWT co field iat</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Dùng để kiểm tra kiểu dữ liệu cơ bản của field đã được xác nhận tồn tại. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="56" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-04</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT có cấu trúc 3 phần (header.payload.signature)</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, nhận được JWT token</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy token từ response
@@ -3074,47 +3307,55 @@
 4. Kiểm tra số phần</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Token phải có đúng 3 phần: header, payload, signature. Nếu không -&gt; thất bại</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Response co field token</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra cấu trúc JWT chuẩn (3 phần) - đúng với mọi JWT hợp lệ. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="70" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-05</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT header la base64 JSON hợp lệ</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần header (phần đầu tiên)
@@ -3122,47 +3363,55 @@
 4. Parse JSON</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Header sau decode phải là JSON hợp lệ, chứa tối thiểu 2 field: "alg" (thuật toán ký, mặc định "HS256" do thư viện jsonwebtoken khi không chỉ định algorithm) và "typ" ("JWT").</t>
         </is>
       </c>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Response co field user</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>JWT hợp lệ luôn phải decode được header. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="70" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-06</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT payload la base64 JSON hợp lệ</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần payload (phần thứ hai)
@@ -3170,322 +3419,386 @@
 4. Parse JSON</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Payload sau decode phải là JSON hợp lệ, chứa field "id" (id user) và "role". Field "iat" (issued at) được thư viện tự thêm. Lưu ý: KHÔNG có field "exp" (hết hạn) vì jwt.sign() được gọi không kèm option expiresIn -&gt; token không bao giờ hết hạn (rủi ro bảo mật, cần ghi vào bug report).</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>JWT co field exp: KHONG</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Payload luôn phải decode được. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-07</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT signature không rỗng</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần signature (phần cuối cùng)
 3. Kiểm tra độ dài</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Signature phải có độ dài &gt; 0, không được rỗng. Thuật toán ký mặc định là HS256 (HMAC-SHA256) vì jwt.sign() không truyền option algorithm.</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>JWT chi co 3 field: id, role, iat</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Chữ ký JWT không được rỗng - tính chất cơ bản của JWT. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-08</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT đúng định dạng base64url</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy token từ response
 3. Kiểm tra ký tự trong token</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>JWT chỉ chứa ký tự base64url: A-Z, a-z, 0-9, -, _, ".": phân cách 3 phần</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Response user co password field</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Định dạng base64url - tính chất cơ bản của JWT. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="195" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Email phân biệt hoa/thường</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>email: "Test@EShop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"Test@EShop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"} (vì so sánh email trong SQL phân biệt hoa/thường, "Test@EShop.com" khác "test@eshop.com" nên không tìm thấy user).</t>
         </is>
       </c>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>User role khong duoc tao product: 403</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Cần test thêm hệ thống có phân biệt chữ hoa, chữ thường hay không. Do tính chất bảo mật của email và password nên phân biệt chữ hoa, chữ thường. Lý do AI bỏ sót theo em nghĩ là do prompt của em chỉ yêu cầu domain partitioning cho field email một cách chung chung, không có gợi ý cụ thể, nên AI thường chỉ quan tâm đúng các trường hợp email đúng/sai định dạng mà không test các case nhạy cảm, chi tiết hơn như phân biệt chữ hoa với chữ thường</t>
         </is>
       </c>
     </row>
     <row r="38" ht="208" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Email có khoảng trắng đầu/cuối</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>email: " test@eshop.com "
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":" test@eshop.com ","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"} (email có khoảng trắng đầu/cuối không được trim trước khi so khớp trong DB, nên " test@eshop.com " khác với "test@eshop.com").</t>
         </is>
       </c>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Admin role duoc tao product: 200 OK</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Test case kiểm tra hệ thống có tự động trim khoảng trắng ở email trước khi xử lý hay không đặc tả không nêu rõ điều này. Lý do AI bỏ sót: prompt gốc chỉ yêu cầu domain partition theo định dạng email hợp lệ/không hợp lệ một cách chung chung, không đề cập input nhiễu như khoảng trắng thừa - đây là input edge-case thực tế thường gặp mà đặc tả không nêu, nên AI (chỉ dựa vào đặc tả) không tự sinh ra được.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="242" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Race condition - 2 request sai password gửi đồng thời</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Tài khoản locktest@eshop.com, bộ đếm đang = 0</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongA" (request 1)
 password: "WrongB" (request 2, gửi gần như cùng lúc)</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời (song song, không chờ response) 2 request POST /api/login sai password
 2. Kiểm tra login_attempts cuối cùng qua GET /api/admin/users hoặc thử đăng nhập lại</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Bộ đếm tăng đúng cho cả 2 lần thất bại.</t>
         </is>
       </c>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Token tampered: 401</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý để phát hiện lỗi đồng thời tiềm ẩn. Lý do AI bỏ sót: AI sinh test case dựa trên đặc tả API (request/response tĩnh), không có khả năng suy luận về hành vi đồng  thời vì AI chỉ được cung cấp đặc tả API, không có prompt chi tiết hơn về hành động này. Đây là hạn chế đặc trưng khi sinh test case chỉ từ đặc tả mà không phân tích thực tế.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="235" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Content-Type sai (form-urlencoded thay vì JSON)</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Header: Content-Type: application/x-www-form-urlencoded
 Body: email=test@eshop.com&amp;password=Test1234!</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login với Content-Type sai và body dạng form-encoded thay vì JSON</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Do body-parser chỉ parse JSON khi Content-Type là application/json, request dạng form-urlencoded sẽ có req.body rỗng ({}) -&gt; email/password đều undefined -&gt; DB không tìm thấy user khớp -&gt; HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Content-Type text/plain: 500 (server crash)</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý để kiểm tra khả năng chịu lỗi khi client gửi sai Content-Type - tình huống thực tế hay gặp. Lý do AI bỏ sót: AI thường giả định client luôn gửi đúng Content-Type theo đặc tả (application/json) khi sinh test case cho request body, không tự nghĩ ra kịch bản client gửi sai định dạng header vì đây là đặc tính của tầng HTTP/middleware (body-parser), nằm ngoài phạm vi đặc tả logic nghiệp vụ mà AI được cung cấp.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="409.5" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Email cực dài (tiềm năng DoS / buffer)</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Không có tài khoản nào khớp email này</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>email: "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login với email dài 5000+ ký tự</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Server không bị treo/crash: SQLite xử lý tham số dài bình thường qua parameterized query, không tìm thấy user khớp -&gt; HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Content-Type application/x-www-form-urlencoded: 500</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý để kiểm tra khả năng chống chịu input bất thường/DoS tiềm ẩn. Lý do AI bỏ sót: đặc tả API không đề cập giới hạn độ dài field email, và AI khi sinh test theo domain partition thường chỉ xét các mốc độ dài hợp lý (email hợp lệ/không hợp lệ theo định dạng) chứ không chủ động nghĩ tới input lớn nhằm mục đích kiểm thử bảo mật/hiệu năng - đây đòi hỏi prompt chi tiết hơn là chỉ dựa theo đặc tả chức năng có sẵn.</t>
         </is>
@@ -3519,1885 +3832,2205 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="98" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Shipping address hợp lệ</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Thanh toán thành công. HTTP 200 OK, Response: {"message":"Checkout successful","orderId":&lt;id&gt;}.</t>
         </is>
       </c>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="9" t="n"/>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Total amount am: 200 OK</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả, happy path bình thường.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Shipping address trống (empty string)</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": ""}</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": ""}</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Total amount 0: 200 OK</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói shipping_address có không được để trống hay không nhưng theo em shipping address không được để trống, suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Shipping address null</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": null}</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": null}</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Total amount null: 200 OK</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói shipping_address có không được null hay không nhưng theo em shipping address không được để trống, suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Shipping address quá dài (500 ký tự)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "&lt;500 char string&gt;"}</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "&lt;500 chars&gt;"}</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Total amount string: 200 OK</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không quy định giới hạn độ dài cho shipping_address nhưng cũng cần test để tránh DoS.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="126" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-01</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Shipping address chứa ký tự đặc biệt (HTML/SQL)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "&lt;script&gt;alert(1)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "&lt;script&gt;alert(1)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>SQL injection shipping_address: 200 OK</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không quy định nhưng theo em cần test xem hệ thống có escape hay không nên test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-01</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng có sản phẩm - thanh toán thành công</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có ít nhất 1 sản phẩm.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Thanh toán thành công. HTTP 200 OK, Response: {"message":"Checkout successful","orderId":&lt;id&gt;}.</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Checkout thanh cong, nhan order_id</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="196" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-02</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng trống - không thể thanh toán</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống (không có sản phẩm).</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Giỏ hàng trống báo lỗi khi thanh toán </t>
         </is>
       </c>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Checkout khong co token: 401</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Dù đặc tả gốc không quy định nhưng cần test case "không thể thanh toán khi giỏ trống" </t>
         </is>
       </c>
     </row>
     <row r="9" ht="154" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-05</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng trống, total_amount client gửi khác 0</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống.</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 500000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 500000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Total amount boolean: 200 OK</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="84" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-06</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - không chấp nhận giá trị client gửi</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 1, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 1, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Thieu total_amount: 200 OK</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-07</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - client gửi giá trị âm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": -50000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": -50000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Thieu shipping_address: 200 OK</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-08</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - client gửi giá trị rất lớn</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 999999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 999999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại</t>
         </is>
       </c>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Thieu payment_method: 200 OK</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-03</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng bị xóa sau thanh toán thành công</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout -&gt; thanh toán thành công
 2. GET /api/cart (kiểm tra giỏ hàng)
 3. Hoặc checkout lần nữa</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng bị xóa sau khi thanh toán thành công</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Checkout token het han: 200 (khong check exp)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Sau thanh toán thành công, giỏ hàng được xóa'.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="252" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-02</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Checkout khi chưa đăng nhập (không có token)</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token hoặc token không hợp lệ.</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">
 1. KHÔNG gửi header Authorization
 2. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized, Response: {"error":"Unauthorized"} khi không có token.</t>
         </is>
       </c>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>XSS trong shipping_address: 200 OK</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Chỉ người dùng đã đăng nhập mới tiến hành thanh toán được'.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="84" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-04</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra order mới tạo có status ban đầu là "pending"</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":100000,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout, lấy orderId
 2. GET /api/orders/:id
 3. Kiểm tra status</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>order mới tạo phải có status pending.</t>
         </is>
       </c>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Checkout user role: 200 OK</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Test case kiểm tra trạng thái khởi tạo của order, là điểm bắt đầu của state machine.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="98" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-05</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Checkout khi giỏ hàng trống</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống (không có sản phẩm nào).</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận giỏ hàng trống
 2. POST /api/checkout
 3. GET /api/cart - kiểm tra giỏ hàng vẫn trống</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Không checkout được khi giỏ hàng trống</t>
         </is>
       </c>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Checkout admin role: 200 OK</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ hệ thống có cho phép checkout khi giỏ hàng trống hay từ chối nhưng theo em nên từ chối.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-09</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>total_amount gửi giá trị null tường minh</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":null,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount: null
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Phải validate total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Thieu cart_item: 200 OK</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Test nếu gửi total_amount = null. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="18" ht="84" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-10</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>total_amount gửi kiểu boolean true thay vì number</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":true,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount: true
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Phải validate kiểu total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Thieu quantity: 200 OK</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra kiểu dữ liệu khác cho total_amount = boolean, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-11</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount thấp hơn thực tế</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 10000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = 10000
 3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Shipping address rong: 200 OK</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý: kiểm tra backend có tin tưởng total_amount thấp hơn giá trị thực từ client hay không. Đây là kịch bản price manipulation thực tế và mở rộng domain partition cho total_amount.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-12</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount cao hơn thực tế</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = 999999999
 3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Payment method rong: 200 OK</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý: kiểm tra backend có chấp nhận total_amount cao hơn giá trị thực hay không. Dù ít gây thiệt hại trực tiếp hơn giá thấp, backend vẫn phải không tin giá trị do client gửi để tránh sai lệch dữ liệu.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="238" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-13</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount sai kiểu (string)</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": "abc", "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = "abc"
 3. Kiểm tra xử lý của hệ thống</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Phải validate kiểu total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Cart item rong: 200 OK</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Trường hợp sai kiểu dữ liệu (string thay vì number) dù đặc tả không quy định, nhưng vẫn cần thiết trong test case.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="154" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-03</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>XSS trong shipping_address - mã HTML/Script</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "&lt;script&gt;alert(document.cookie)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa &lt;script&gt;alert(document.cookie)&lt;/script&gt;
 2. Nếu thanh toán thành công, GET /api/orders hoặc endpoint hiển thị địa chỉ
 3. Kiểm tra địa chỉ được escape an toàn</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Phải có escape shipping_address.</t>
         </is>
       </c>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Empty body: 200 OK</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Hệ thống phải escape mã HTML/script khi lưu hoặc hiển thị. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-04</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>XSS trong shipping_address - mã phức tạp hơn</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "&lt;img src=x onerror=alert(1)&gt;"}</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa &lt;img src=x onerror=alert(1)&gt;
 2. Kiểm tra response và cách hệ thống xử lý địa chỉ</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Phải có escape shipping_address</t>
         </is>
       </c>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Total amount string dai: 200 OK</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Hệ thống phải escape mã HTML/script khi lưu hoặc hiển thị. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="70" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Response thanh toán thành công có status 2xx</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm. Dữ liệu hợp lệ.</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với dữ liệu hợp lệ
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Response thành công là HTTP 200 OK vì route gọi res.json() mà không set status 201.</t>
         </is>
       </c>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Response co order_id</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="140" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Response thanh toán thành công có cấu trúc response hợp lệ</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm. Dữ liệu hợp lệ.</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với dữ liệu hợp lệ
 2. Kiểm tra toàn bộ response body</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Response thành công theo code gồm message và orderId. Không trả total_amount, status hay shipping_address.</t>
         </is>
       </c>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Response co message</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Tên field cụ thể trong response (orderId...) không được liệt kê trong đặc tả nhưng vẫn cần test cấu trúc hợp lệ JSON khi thành công</t>
         </is>
       </c>
     </row>
     <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-05</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Thiếu header Authorization - response báo lỗi</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Người dùng chưa đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout KHÔNG gửi header Authorization
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized, Response: {"error":"Unauthorized"}.</t>
         </is>
       </c>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Shipping address script tag: 200 OK</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Trực tiếp từ 'chỉ người dùng đã đăng nhập mới checkout được'.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="84" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-14</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Thiếu field bắt buộc shipping_address - response báo lỗi</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000}</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout THIẾU field shipping_address
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi</t>
         </is>
       </c>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Quantity am: 200 OK</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="182" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-15</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Thiếu field bắt buộc total_amount - response báo lỗi</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout THIẾU field total_amount
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi</t>
         </is>
       </c>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Quantity string: 200 OK</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="70" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-16</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Body trống - không gửi field nào - response báo lỗi</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với body rỗng {}
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Cả hai field đều không được validate trước INSERT; không có lỗi 400 ở tầng ứng dụng. Kết quả DB phụ thuộc schema.</t>
         </is>
       </c>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="266" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-06</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Checkout với token hết hạn</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã hết hạn. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;expired_token&gt;
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với expired_token</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>JWT hết hạn làm jwt.verify lỗi và middleware trả HTTP 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J30" s="19" t="inlineStr">
         <is>
           <t>Chỉ người dùng đã đăng nhập mới checkout được' được suy luận hợp lý là bao gồm token còn hiệu lực (chưa hết hạn). Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="31" ht="224" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-07</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Checkout với token giả mạo (sai chữ ký)</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã bị sửa đổi (sai chữ ký). Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;tampered_token&gt;
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với tampered_token</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>JWT sai chữ ký làm jwt.verify lỗi và middleware trả HTTP 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Token bị sửa đổi/sai chữ ký về bản chất không còn là 'người dùng đã đăng nhập hợp lệ'. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="32" ht="280" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-08</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Checkout với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user"). Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với user_token</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Checkout thành công</t>
         </is>
       </c>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả, happy path bình thường.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="140" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-17</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Checkout với giỏ hàng nhiều sản phẩm (3+ sản phẩm)</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 3 sản phẩm với giá trị khác nhau.</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 500000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>1. Thêm 3 sản phẩm vào giỏ hàng (giá: 100000, 150000, 250000)
 2. POST /api/checkout với total_amount sai
 3. Kiểm tra order</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Backend không tự tính lại total_amount từ giỏ hàng, kể cả nhiều sản phẩm; dùng trực tiếp giá trị client gửi.</t>
         </is>
       </c>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Dựa vào từ 'Backend phải tự tính lại tổng tiền' - áp dụng cho mọi số lượng sản phẩm trong giỏ, kể cả nhiều sản phẩm.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="294" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-09</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Checkout với shipping_address chứa SQL injection</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "' OR 1=1 --"}</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa SQL injection</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Parameterized query xử lý payload SQL injection an toàn; chuỗi được truyền như dữ liệu thay vì nối vào SQL.</t>
         </is>
       </c>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Dựa vào SEC-05 (parameterized query) là yêu cầu bảo mật chung của toàn hệ thống.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="182" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-18</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>shipping_address gửi sai kiểu dữ liệu number thay vì string</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":150000,"shipping_address":12345}</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address: 12345
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Thông báo lỗi type của shipping_address</t>
         </is>
       </c>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra sai kiểu dữ liệu của shipping_address.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="182" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Gọi GET /api/checkout thay POST</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/checkout (thay vì POST)</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>GET /api/checkout không có route GET; với Express hiện tại sẽ rơi vào HTTP 404 Not Found.</t>
         </is>
       </c>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Response co total_amount</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không mô tả hành vi khi gọi sai HTTP method - đây là hành vi mặc định của framework/router, không phải yêu cầu nghiệp vụ được đặc tả. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="37" ht="112" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Race condition - 2 request checkout đồng thời cùng 1 user</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body (gửi đồng thời 2 lần): {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời (song song) 2 request POST /api/checkout từ cùng 1 user, cùng giỏ hàng
 2. GET /api/orders/my-orders kiểm tra số đơn hàng được tạo</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Hai request đồng thời có thể tạo hai order riêng nếu đều INSERT thành công.</t>
         </is>
       </c>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Checkout 2 lan: 2 order tao thanh cong</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Test case để phát hiện duplicate order. AI dễ bỏ sót vì đây là hành động diễn ra đồng thời thường AI không thể suy ra đầy đủ chỉ từ đặc tả do trong đặc tả thường chỉ miêu tả yêu cầu đơn lẻ.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="70" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng của user khác không bị ảnh hưởng khi checkout</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>2 user đã đăng nhập: user A và user B, cả 2 đều có sản phẩm trong giỏ hàng riêng.</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>User A: Header: Authorization: Bearer {{userToken}}
 User B: Header: Authorization: Bearer {{userTokenB}} (cần tài khoản phụ thứ 2)</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>1. User A và User B cùng thêm sản phẩm vào giỏ (POST /api/cart)
 2. User A checkout (POST /api/checkout)
 3. GET /api/cart bằng token của User B - kiểm tra giỏ hàng B còn nguyên</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>userCarts được lưu theo userId nên cart của User B dùng key riêng và không bị User A ghi đè.</t>
         </is>
       </c>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Quantity am: 200 OK</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Test case để kiểm tra cách ly dữ liệu giữa người dùng. AI dễ bỏ sót vì đặc tả thường không mô tả.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>total_amount dạng số thập phân</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 99999.99, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount có phần thập phân</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Checkout thành công do tiền vẫn có thể số thập phân</t>
         </is>
       </c>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Quantity 0: 200 OK</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Test case để kiểm tra có chấp nhận số thập phân ở trường tổng tiền hay không. AI có thể bỏ sót vì đặc tả chỉ nói number và không nêu quy ước có được dùng số thực hay không.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="93" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Content-Type sai khi checkout</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Header: Content-Type: text/plain
 Body: total_amount=100000&amp;shipping_address=123ABC</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với Content-Type sai, body không phải JSON hợp lệ</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>bodyParser.json() chỉ parse JSON phù hợp; với Content-Type sai, req.body có thể không chứa các field mong đợi. Route phải validate trước INSERT</t>
         </is>
       </c>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Quantity string: 200 OK</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Test case cho input sai định dạng ở tầng HTTP. AI thường giả định client gửi đúng Content-Type theo đặc tả và bỏ sót hành vi gửi sai.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="64" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Gọi checkout liên tục nhiều lần trong thời gian ngắn (spam)</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"} (gửi 20 lần liên tiếp trong 1 giây)</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>1. Gửi 20 request POST /api/checkout liên tiếp rất nhanh (script loop, không phải người dùng thật bấm 20 lần)</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Phải báo lỗi hoặc có cơ chế chống DoS</t>
         </is>
       </c>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Product khong ton tai: 200 OK</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Test case để kiểm tra spam. AI sinh từ đặc tả thường tập trung từng request đơn lẻ hơn là tần suất cao hay test độ chống DoS.</t>
         </is>
@@ -5430,42 +6063,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -5475,215 +6108,247 @@
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="84" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên hợp lệ</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Tạo category thành công. Status code: 201 Created. Response body trả về object category vừa tạo, gồm ít nhất "id" và "name" (ví dụ: {"id": 1, "name": "Điện thoại"}).</t>
         </is>
       </c>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>POST ten trong: 200 OK</t>
+        </is>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên trống (empty string)</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>POST ten null: 200 OK</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Từ đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên null</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": null}</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": null}</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>POST ten 256 ky tu: 200 OK</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Null cũng là một dạng 'không có giá trị' - áp dụng cùng đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Tạo category thiếu field name</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {}</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>POST ten co special chars: 200 OK</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Thiếu hẳn field cũng vi phạm đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="185" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-05</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Tạo category với tên quá dài (255 ký tự)
 ➜ ĐÃ SỬA (INVALID): 
 Tạo category với tên rất dài (boundary test, không giả định giới hạn cụ thể)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "AAAA...(255 ký tự)"}
@@ -5692,7 +6357,7 @@
 Body: {"name": "A" x 1000 (chuỗi 1000 ký tự, không giả định 255)}</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên 255 ký tự
 2. Kiểm tra response
@@ -5701,456 +6366,536 @@
 2. Kiểm tra response và trạng thái hệ thống (không được lỗi 500)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Hệ thống báo lỗi có giới hạn độ dài tên category hay không?
 ➜ ĐÃ SỬA (INVALID): 
 Hệ thống xử lý ổn định, KHÔNG được trả lỗi 500. Vì đặc tả không quy định giới hạn độ dài, chấp nhận 1 trong 2 kết quả hợp lệ: (a) 201 Created nếu hệ thống không giới hạn độ dài, hoặc (b) 400 Bad Request nếu hệ thống có giới hạn - cần đối chiếu với backend thực tế khi thực thi.</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>POST ten trung: 200 OK</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>INVALID</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Giới hạn '255 ký tự' KHÔNG có trong đặc tả, do AI tự bịa nên em đã thay bằng test case boundary không giả định con số cụ thể. Lý do AI bỏ sót/bịa ra: AI đưa ra con số '255 ký tự' dựa trên pattern phổ biến của kiểu dữ liệu VARCHAR(255) trong các CSDL SQL truyền thống (MySQL/PostgreSQL) - đây là suy luận từ kiến thức huấn luyện chung (pattern quen thuộc), không phải trích xuất từ đặc tả thực tế của API này. Đây là một dạng hallucination do model áp dụng best-practice/convention phổ biến vượt ra ngoài phạm vi đặc tả được cung cấp.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-06</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên chỉ có khoảng trắng</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "   "}</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "   "
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>POST ten trung: 200 OK (cho phep)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ có trim khoảng trắng trước khi kiểm tra rỗng hay không, nhưng theo em suy luận khoảng trắng cũng đồng nghĩa với không có tên danh mục, nên em sẽ sửa kết quả từ chấp nhận tên sang từ chối tạo category.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="131" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-07</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên trùng với category đã có</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Đã có category "Điện thoại".</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "Điện thoại" (da ton tai)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên phải unique. Status code: 409 Conflict (hoặc 400 Bad Request nếu hệ thống dùng chung cơ chế validation error).</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>POST ten trung: 200 OK</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Đặc tả không yêu cầu tên category phải unique nhưng theo em tên danh mục nên là unique, em sẽ đổi kết quả từ cho phép tạo sang từ chối. </t>
         </is>
       </c>
     </row>
     <row r="9" ht="98" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-01</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên chứa ký tự đặc biệt</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện &lt;thoại&gt; &amp; Phụ kiện"}</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên chứa ký tự đặc biệt
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên không chứa ký tự đặc biệt nguy hiểm (HTML/script injection). Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>POST ten XSS: 200 OK</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói về việc danh mục có được chứa ký tự đặc biệt hay không, nhưng theo em thì không nên, nên em sẽ đổi kết quả từ cho phép tạo sang từ chối tạo.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-01</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Xem danh sách category - có category</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có ít nhất 1 category.</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Trả về danh sách category. Status code: 200 OK. Response body là một mảng các object category (ví dụ: [{"id":1,"name":"Điện thoại"}, ...]).</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>POST category thanh cong: 200 OK</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xem'.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-02</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Xem danh sách category - không có category nào</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Không có category nào.</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Trả về danh sách rỗng. Status code: 200 OK. Response body là mảng trống ([]), không phải null.</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>GET categories: 200 OK, co category moi</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xem' nhưng trường hợp rỗng.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="84" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-03</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Xóa category thành công</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id
 2. GET /api/categories để verify</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Xóa thành công. Category không còn trong danh sách. Status code: 204 No Content (theo convention REST phổ biến cho DELETE; 200 OK cũng có thể chấp nhận nếu backend trả kèm message).</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>DELETE category: 200 OK</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xóa'.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="98" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-08</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Xóa category không tồn tại</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. ID không tồn tại.</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Hệ thống trả lỗi 404</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>DELETE khong ton tai: 200 OK</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ nhưng em nghĩ hệ thống phải thông báo lỗi thay vì xác định thành công, nên em chuyển kết quả từ phân vân 2 trạng thái sang hệ thống phải trả lỗi.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-04</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Sửa category - thay đổi tên</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên mới
 2. GET /api/categories để verify</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Sửa thành công. Tên mới được cập nhật. Status code: 200 OK. Response body trả về object category đã cập nhật (ví dụ: {"id":1,"name":"Tên mới"}).</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>GET category by ID: 200 OK</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="15" ht="84" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-09</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Sửa category với tên trống</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên trống</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Từ chối sửa. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>GET by ID khong ton tai: 404</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="16" ht="112" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-05</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Luồng hoàn chỉnh: Tạo -&gt; Xem -&gt; Xóa -&gt; Xem</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Chưa có category "Test Category".</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Test Category"}</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "Test Category"
 2. GET /api/categories - xác nhận có
@@ -6158,1145 +6903,1353 @@
 4. GET /api/categories - xac nhan không còn</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Tạo thành công (POST → 201) → Xuất hiện trong danh sách (GET → 200, có category) → Xóa thành công (DELETE → 204) → Không còn trong danh sách (GET → 200, không có category).</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>PUT category: 200 OK</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Luồng Tạo-&gt;Xem-&gt;Xóa-&gt;Xem đúng phạm vi 'Thêm/Xem/Xóa' của đặc tả</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-02</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Tạo category khi chưa đăng nhập (không có token)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories KHÔNG gửi token</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>POST ten SQL inject: 200 OK</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="84" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-03</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Tạo category với token không hợp lệ</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhung token không hợp lệ.</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;invalid_token&gt;
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với invalid_token</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>DELETE khong token: 401</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="84" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-04</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Tạo category với token giả mạo (sai chữ ký)</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã bị sửa đổi.</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;tampered_token&gt;
 Body: {"name": "Category giả"}</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tampered_token</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token không hợp lệ (sai chữ ký). Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>DELETE user role: 200 OK</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="98" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-05</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Tạo category với token hết hạn</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã hết hạn.</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;expired_token&gt;
 Body: {"name": "Category hết hạn"}</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với expired_token</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token hết hạn. Status code: 401 Unauthorized. LƯU Ý: cần tạo token hết hạn trước khi test.</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>PUT khong token: 401</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="98" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-06</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Tạo category với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với user_token</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token hợp lệ nhưng role != "admin". Spec nói rõ: phải kiểm tra role = "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>POST khong token: 401</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả phải kiểm tra role='admin', không chỉ kiểm tra có token.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="84" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-07</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Xóa category với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id với user_token</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Từ chối xóa category. Role != "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>PUT user role: 200 OK</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả phải kiểm tra role='admin', không chỉ kiểm tra có token.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="112" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-08</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>GET /api/categories không có token</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Không gửi header Authorization</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories KHÔNG gửi token</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Từ chối truy cập. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>POST user role: 200 OK</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Dù đặc tả không nói rõ, nhưng theo em GET cũng cần token + role admin. Suy ra test case AI tạo rahợp lý.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="126" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-09</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>GET /api/categories với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories với user_token</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Từ chối xem danh sách category. Role != "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Dù đặc tả không nói rõ, nhưng theo em GET cũng cần token + role admin. Suy ra test case AI tạo ra hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="84" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>GET /api/categories trả về danh sách dạng mảng (array)</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ.</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Response phải trả về một mảng (array), không phải object hay string. Mảng có thể trống hoặc có phần tử tùy dữ liệu hiện có, miễn đúng kiểu array.</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Response co id</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra schema cơ bản (mảng). Suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>GET /api/categories trả về mảng rỗng khi không có category</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Không có category nào.</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Response trả về mảng rỗng chính xác là [] (không phải null, không phải object rỗng {}).</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Response co name</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra schema cơ bản (mảng). Suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="84" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>POST /api/categories thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Category mới"}</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên hợp lệ
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Response thành công phải có status 201 Created (convention chuẩn REST cho hành động tạo mới thành công; 200 OK có thể chấp nhận nếu backend không tuân thủ chuẩn tuyệt đối).</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Response co created_at</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Thành công thì trả về 2xx, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="28" ht="84" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-04</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>POST /api/categories thất bại (tên trống) trả về 4xx</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên trống
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Response lỗi phải có status 400 Bad Request. Không được trả về 2xx khi dữ liệu không hợp lệ.</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Response co updated_at</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Từ chối khi tên rỗng phải là 4xx - test case hợp lý, khớp với yêu cầu 'tên bắt buộc' của đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="112" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-05</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>POST /api/categories thành công có cấu trúc response hợp lệ</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Category mới"}</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Response thành công phải có cấu trúc JSON hợp lệ, tối thiểu gồm field "id" và "name" (ví dụ: {"id": 1, "name": "Category mới"}). LƯU Ý: tên field là SUY ĐOÁN, không trích từ tài liệu, cần đối chiếu response thực tế khi thực thi.</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>DELETE tra 200 khong phai 204</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Tên field cụ thể trong response không được liệt kê ở đặc tả nhưng vẫn phải test cấu trúc JSON nên test case hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="30" ht="84" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-06</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>DELETE /api/categories/:id thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Response thành công phải có status 204 No Content (đồng nhất với TC-FR14-ST-03; 200 OK cũng có thể chấp nhận nếu backend trả kèm message).</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>POST tra 200 khong phai 201</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Thành công thì trả về 2xx, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="31" ht="98" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-07</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>DELETE /api/categories/:id thất bại (id không tồn tại) trả về 4xx</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. ID không tồn tại.</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/99999
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Hệ thống trả lỗi 404 Not Found.</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Response message dung format</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ nhưng em nghĩ hệ thống phải thông báo lỗi thay vì xác định thành công, nên em chuyển kết quả từ phân vân 2 trạng thái sang hệ thống phải trả lỗi.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="84" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-08</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Response lỗi khi thiếu field name có cấu trúc báo lỗi</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với body rỗng
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Response phải báo lỗi với status 400 Bad Request và có cấu trúc JSON hợp lệ (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Categories list dung format</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Cấu trúc lỗi JSON hợp lệ khi thiếu field bắt buộc khớp yêu cầu 'tên bắt buộc'.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="84" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-09</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Sửa category thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Response thành công phải có status 200 OK.</t>
         </is>
       </c>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="34" ht="84" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-10</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Sửa category thất bại (tên trống) trả về 4xx</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên trống
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Response lỗi phải có status 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="35" ht="126" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-06</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Xóa category rồi tạo lại với tên giống - không bị trùng id</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category "Temp Category".</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Temp Category"}</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id của "Temp Category"
 2. POST /api/categories với tên "Temp Category" mới
 3. GET /api/categories - xác nhận chỉ có 1 với id mới</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Xóa thành công. Tạo lại với id mới. Chỉ có 1 category "Temp Category". Id mới phải khác id cũ (do id thường là auto-increment hoặc UUID, không tái sử dụng id đã xóa).</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>GET categories list: 200 OK</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Không quy định trong đặc tả, nhưng theo suy luận của em, test case AI sinh ra hợp lý. Kiểm tra được tính unique của danh mục sẽ được xác định đúng hay không.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="112" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-10</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Token user bình thường (role != admin) thực thi cả POST và DELETE</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"name": "Test"}</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với user_token
 2. DELETE /api/categories/:id với user_token</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Cả POST và DELETE đều bị từ chối. Token hợp lệ nhưng role != "admin". Status code: 403 Forbidden cho cả 2 request.</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Dung nhu expected</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="106" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Tạo category với field thừa không được định nghĩa</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Sách", "description": "Mô tả không nằm trong spec"}</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với body có field 'description' thừa ngoài spec</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Hệ thống bỏ qua field "description" không được định nghĩa trong spec, chỉ lưu field "name"; tạo category thành công với status 201 Created (convention phổ biến: ignore unknown fields thay vì báo lỗi 400, trừ khi hệ thống dùng strict schema validation).</t>
         </is>
       </c>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>POST ten 1 ky tu: 200 OK</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì prompt yêu cầu sinh test case theo 'domain partition trên từng parameter' được liệt kê trong đặc tả; AI chỉ suy luận trên các field đã được định nghĩa, không tự nghĩ đến trường hợp field không nằm trong đặc tả) - đây là giới hạn phạm vi suy luận của model khi bám sát input đã cho.</t>
         </is>
       </c>
-      <c r="K37" s="12" t="n"/>
+      <c r="K37" s="10" t="n"/>
     </row>
     <row r="38" ht="98" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Race condition - 2 admin tạo category cùng tên đồng thời</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập (2 phiên/token khác nhau nếu có thể). Chưa có category tên 'Sách'.</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body (gửi đồng thời 2 lần): {"name": "Sách"}</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời 2 request POST /api/categories cùng tên 'Sách'
 2. GET /api/categories kiểm tra có bao nhiêu category tên 'Sách' được tạo</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Do tên category phải unique (theo TC-FR14-DP-07), khi 2 request đồng thời cùng tên "Sách" được gửi, chỉ 1 request thành công (201 Created), request còn lại phải bị từ chối (409 Conflict hoặc 400 Bad Request). Không được có 2 category cùng tên "Sách" sau khi chạy xong.</t>
         </is>
       </c>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>POST ten 255 ky tu: 200 OK</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì test case AI sinh ra theo luồng tuần tự (1 request - 1 response tại một thời điểm), không có khả năng/không được yêu cầu mô phỏng tình huống đồng thời. Đây là hạn chế đặc trưng của việc sinh test case từ đặc tả tĩnh: AI không tự suy luận về các vấn đề vận hành thực tế nếu prompt không yêu cầu rõ ràng.</t>
         </is>
       </c>
-      <c r="K38" s="12" t="n"/>
+      <c r="K38" s="10" t="n"/>
     </row>
     <row r="39" ht="117" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Gọi HTTP method không được hỗ trợ (PATCH)</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần test.</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>1. PATCH /api/categories/:id (method không được liệt kê trong API spec - chỉ có GET/POST/PUT/DELETE)</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Hệ thống trả về 404 Not Found (phổ biến hơn 405 Method Not Allowed đối với các API đơn giản dùng framework như Express, vốn không định nghĩa route cho PATCH nên coi như route không tồn tại). Nếu hệ thống có OPTIONS/route-level method negotiation thì có thể trả 405 kèm header Allow.</t>
         </is>
       </c>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>POST ten co dau: 200 OK</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI generate test case dựa trên các HTTP method được liệt kê tường minh trong đặc tả (GET/POST/PUT/DELETE), không tự nghĩ đến việc test các method KHÔNG được định nghĩa trong đặc tả. Đây là đặc điểm của model: thiên về mặt theo đúng đặc tả, thiếu tư duy mặt ngược lại thì như nào.</t>
         </is>
       </c>
-      <c r="K39" s="12" t="n"/>
+      <c r="K39" s="10" t="n"/>
     </row>
     <row r="40" ht="161" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Content-Type sai khi tạo category</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Header: Content-Type: text/plain
 Body: name=Sach</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với Content-Type sai, body không phải JSON hợp lệ</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Hệ thống nên trả về 400 Bad Request với thông báo lỗi rõ ràng (ví dụ: "Invalid JSON body" hoặc "Unsupported Content-Type"), KHÔNG được trả 500 Internal Server Error. Nếu thực thi cho ra 500 thì đây là một bug cần report.</t>
         </is>
       </c>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>POST ten co so: 200 OK</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI tập trung sinh test case validate nội dung body theo đúng domain partition được yêu cầu trong prompt, chứ không kiểm tra các thuộc tính protocol-level như HTTP header Content-Type. Đây là hạn chế do phạm vi prompt (chỉ yêu cầu domain partition/state/security/schema) không bao gồm rõ ràng validation ở tầng request header.</t>
         </is>
       </c>
-      <c r="K40" s="12" t="n"/>
+      <c r="K40" s="10" t="n"/>
     </row>
     <row r="41" ht="125" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Tên category chứa ký tự Unicode có dấu / emoji</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Đồ gia dụng 🏠"}</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên chứa tiếng Việt có dấu và emoji
 2. GET /api/categories kiểm tra tên lưu và trả về có đúng nguyên gốc không</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Hệ thống lưu và trả về đúng nguyên vẹn chuỗi UTF-8 (tiếng Việt có dấu và emoji), không bị lỗi encoding, không bị cắt ký tự. Status code: 201 Created khi tạo thành công.</t>
         </is>
       </c>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>POST ten co ky tu dac biet: 200 OK</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI ít khi tự sinh test case về encoding/Unicode edge case trừ khi được yêu cầu cụ thể trong prompt - đây là đặc điểm kỹ thuật của hệ thống, thường không được nêu rõ trong đặc tả chức năng, nên AI thiên về test theo đặc tả hơn là các edge case kỹ thuật/encoding.</t>
         </is>
       </c>
-      <c r="K41" s="12" t="n"/>
+      <c r="K41" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
+++ b/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19200" windowHeight="7510" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19200" windowHeight="7510" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,17 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="29">
+  <numFmts count="0"/>
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -45,9 +41,21 @@
     <font>
       <name val="Times New Roman"/>
       <charset val="134"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
       <strike val="1"/>
       <color rgb="FF999999"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -75,6 +83,11 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
       <color rgb="FF0000FF"/>
@@ -88,6 +101,13 @@
       <color rgb="FF800080"/>
       <sz val="11"/>
       <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -218,12 +238,6 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <color rgb="00006100"/>
-    </font>
-    <font>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
   <fills count="37">
     <fill>
@@ -235,13 +249,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
     <fill>
@@ -430,18 +456,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -580,152 +594,142 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -743,11 +747,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -755,29 +768,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -830,7 +829,221 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -841,16 +1054,8 @@
       <rgbColor rgb="00FFFF00"/>
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="009C0006"/>
+      <rgbColor rgb="00006100"/>
       <rgbColor rgb="00000080"/>
       <rgbColor rgb="00808000"/>
       <rgbColor rgb="00800080"/>
@@ -864,7 +1069,7 @@
       <rgbColor rgb="00660066"/>
       <rgbColor rgb="00FF8080"/>
       <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00D9E1F2"/>
       <rgbColor rgb="00000080"/>
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="00FFFF00"/>
@@ -875,20 +1080,28 @@
       <rgbColor rgb="000000FF"/>
       <rgbColor rgb="0000CCFF"/>
       <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00C6EFCE"/>
       <rgbColor rgb="00FFFF99"/>
       <rgbColor rgb="0099CCFF"/>
       <rgbColor rgb="00FF99CC"/>
       <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="00FFC7CE"/>
+      <rgbColor rgb="004472C4"/>
       <rgbColor rgb="0033CCCC"/>
       <rgbColor rgb="0099CC00"/>
       <rgbColor rgb="00FFCC00"/>
       <rgbColor rgb="00FF9900"/>
       <rgbColor rgb="00FF6600"/>
       <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00999999"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
       <rgbColor rgb="00003300"/>
@@ -907,10 +1120,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -948,234 +1161,128 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1201,386 +1308,387 @@
     <col width="9" customWidth="1" style="1" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.5" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>HW06 API Testing — Test Summary Report</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Student ID: 23127031 | Date: 2026-08-24 01:24</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Number of APIs tested</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="18" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Total test cases generated</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="18" t="n">
         <v>151</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Total requests in collection</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="18" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Assertions executed</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="18" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Assertions passed</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="18" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Assertions failed</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>48.1%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Pass rate</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="18" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Bugs found</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Critical bugs</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Major bugs</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Minor bugs</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Detailed Results by API</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Assertions</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>Bugs Found</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="18" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="18" t="n">
         <v>26</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="18" t="n">
         <v>32</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="18" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Category CRUD</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>FR-14</t>
         </is>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="18" t="n">
         <v>51</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="18" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr"/>
-      <c r="C23" s="18" t="n">
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n">
         <v>151</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="20" t="n">
         <v>77</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="20" t="n">
         <v>42</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="20" t="n">
         <v>78</v>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="G23" s="20" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Bug Severity Breakdown</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Issue Numbers</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>#166, #168, #169, #170, #171, #174, #175</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>#167, #172, #173, #179</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>#176, #177, #178</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="C30" s="18" t="inlineStr"/>
+      <c r="C30" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1594,7 +1702,10 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="28.0909090909091" defaultRowHeight="14"/>
   <cols>
     <col width="15.6363636363636" customWidth="1" style="1" min="1" max="1"/>
-    <col width="28.0909090909091" customWidth="1" style="1" min="2" max="9"/>
+    <col width="28.0909090909091" customWidth="1" style="1" min="2" max="6"/>
+    <col width="37.0636363636364" customWidth="1" style="1" min="7" max="7"/>
+    <col width="35.4909090909091" customWidth="1" style="1" min="8" max="8"/>
+    <col width="28.0909090909091" customWidth="1" style="1" min="9" max="9"/>
     <col width="35" customWidth="1" style="1" min="10" max="10"/>
     <col width="28.0909090909091" customWidth="1" style="1" min="11" max="16384"/>
   </cols>
@@ -1651,7 +1762,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="56" customHeight="1">
+    <row r="2" ht="55.5" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-01</t>
@@ -1686,10 +1797,10 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Token khong hop le: 401</t>
-        </is>
-      </c>
-      <c r="H2" s="20" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1740,12 +1851,12 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Token het han: 200 OK (khong check exp)</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -1759,7 +1870,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
+    <row r="4" ht="69.75" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-03</t>
@@ -1794,10 +1905,10 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Token khong co prefix Bearer: 401</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1813,7 +1924,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.5" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-04</t>
@@ -1848,12 +1959,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>User khong ton tai: 401</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -1867,7 +1978,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.5" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-05</t>
@@ -1902,12 +2013,12 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Thieu email: 400</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1956,12 +2067,12 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Thieu password: 400</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -1975,7 +2086,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.5" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-07</t>
@@ -2010,12 +2121,12 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Email rong: 401</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -2029,7 +2140,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.5" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-08</t>
@@ -2064,10 +2175,10 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Password rong: 401</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2083,7 +2194,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.5" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-09</t>
@@ -2118,10 +2229,10 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Email khong hop le: 401</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2137,7 +2248,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.5" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-10</t>
@@ -2172,10 +2283,10 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Password 1 ky tu: 401</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2191,7 +2302,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.5" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-11</t>
@@ -2226,10 +2337,10 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Password 100 ky tu: 401</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2280,10 +2391,10 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Email co ky tu dac biet: 401</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2299,7 +2410,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.5" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-01</t>
@@ -2334,10 +2445,10 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Login thanh cong, nhan token + user object</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2353,7 +2464,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.5" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-02</t>
@@ -2388,12 +2499,12 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Sau 1 lan sai: 401 (login_attempts = 2 trong DB)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -2407,7 +2518,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.5" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-03</t>
@@ -2442,12 +2553,12 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Sau 3 lan sai: 403 Locked</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -2461,7 +2572,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.5" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-04</t>
@@ -2496,10 +2607,10 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Dang nhap sau khi khoa: 403 Locked</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2515,7 +2626,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.5" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-05</t>
@@ -2550,10 +2661,10 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Thay doi mat khau cu: 200 OK</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2569,7 +2680,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="55.5" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-06</t>
@@ -2604,10 +2715,10 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Sau 30 giay: van 403 (chua het khoa, can 3 phut)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
+          <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2623,7 +2734,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="69.75" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-07</t>
@@ -2658,12 +2769,12 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Dang nhap voi tai khoan khong ton tai: 401</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -2677,7 +2788,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="76" customHeight="1">
+    <row r="21" ht="75.75" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-01</t>
@@ -2712,10 +2823,10 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>SQL injection email: 401</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2731,7 +2842,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="77" customHeight="1">
+    <row r="22" ht="76.5" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-02</t>
@@ -2766,12 +2877,12 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>SQL injection password: 401</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -2785,7 +2896,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="55.5" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-03</t>
@@ -2820,10 +2931,10 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>XSS trong email: 401</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2839,7 +2950,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="69.75" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-04</t>
@@ -2874,12 +2985,12 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Brute force 5 lan: khoa sau 2 lan (2x2=4)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -2893,7 +3004,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="55.5" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-05</t>
@@ -2928,10 +3039,10 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Timing attack: khong phat hien</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2947,7 +3058,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="119" customHeight="1">
+    <row r="26" ht="118.5" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-06</t>
@@ -2983,10 +3094,10 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Empty body POST: 500</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
+          <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3038,10 +3149,10 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>JSON.parse error: 500</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
+          <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3057,7 +3168,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="187" customHeight="1">
+    <row r="28" ht="186.75" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-08</t>
@@ -3093,12 +3204,12 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Password trong response: co (plain text)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -3112,7 +3223,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="55.5" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-01</t>
@@ -3148,10 +3259,10 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>JWT co field id</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3203,10 +3314,10 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>JWT co field role</t>
-        </is>
-      </c>
-      <c r="H30" s="20" t="inlineStr">
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3258,10 +3369,10 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>JWT co field iat</t>
-        </is>
-      </c>
-      <c r="H31" s="20" t="inlineStr">
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3277,7 +3388,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="55.5" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-04</t>
@@ -3314,10 +3425,10 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Response co field token</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3333,7 +3444,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="70" customHeight="1">
+    <row r="33" ht="69.75" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-05</t>
@@ -3370,10 +3481,10 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Response co field user</t>
-        </is>
-      </c>
-      <c r="H33" s="20" t="inlineStr">
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3389,7 +3500,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="69.75" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-06</t>
@@ -3426,12 +3537,12 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>JWT co field exp: KHONG</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
@@ -3445,7 +3556,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="55.5" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-07</t>
@@ -3481,12 +3592,12 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>JWT chi co 3 field: id, role, iat</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -3536,12 +3647,12 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Response user co password field</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -3590,12 +3701,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>User role khong duoc tao product: 403</t>
-        </is>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I37" s="5" t="n"/>
@@ -3605,7 +3716,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="208" customHeight="1">
+    <row r="38" ht="207.75" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-02</t>
@@ -3640,10 +3751,10 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Admin role duoc tao product: 200 OK</t>
-        </is>
-      </c>
-      <c r="H38" s="23" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3655,7 +3766,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="242" customHeight="1">
+    <row r="39" ht="241.5" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-03</t>
@@ -3691,10 +3802,10 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Token tampered: 401</t>
-        </is>
-      </c>
-      <c r="H39" s="23" t="inlineStr">
+          <t>B1 POST: 500 Internal Server Error; B2 GET: 401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3706,7 +3817,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="235" customHeight="1">
+    <row r="40" ht="234.75" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-04</t>
@@ -3740,10 +3851,10 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Content-Type text/plain: 500 (server crash)</t>
-        </is>
-      </c>
-      <c r="H40" s="22" t="inlineStr">
+          <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3789,10 +3900,10 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Content-Type application/x-www-form-urlencoded: 500</t>
-        </is>
-      </c>
-      <c r="H41" s="22" t="inlineStr">
+          <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3805,7 +3916,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -3816,7 +3928,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J41"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="21.5454545454545" customWidth="1" style="1" min="1" max="1"/>
     <col width="30.4545454545455" customWidth="1" style="1" min="2" max="2"/>
@@ -3883,7 +3995,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="98" customHeight="1">
+    <row r="2" ht="97.5" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-01</t>
@@ -3919,10 +4031,10 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Total amount am: 200 OK</t>
-        </is>
-      </c>
-      <c r="H2" s="22" t="inlineStr">
+          <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3974,12 +4086,12 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Total amount 0: 200 OK</t>
-        </is>
-      </c>
-      <c r="H3" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -4029,12 +4141,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Total amount null: 200 OK</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -4048,7 +4160,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
+    <row r="5" ht="69.75" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-04</t>
@@ -4084,12 +4196,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Total amount string: 200 OK</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -4139,12 +4251,12 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>SQL injection shipping_address: 200 OK</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -4158,7 +4270,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row r="7" ht="69.75" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-01</t>
@@ -4194,12 +4306,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Checkout thanh cong, nhan order_id</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -4213,7 +4325,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="196" customHeight="1">
+    <row r="8" ht="195.75" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-02</t>
@@ -4249,10 +4361,10 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Checkout khong co token: 401</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4268,7 +4380,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="154" customHeight="1">
+    <row r="9" ht="153.75" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-05</t>
@@ -4304,12 +4416,12 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Total amount boolean: 200 OK</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -4359,12 +4471,12 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Thieu total_amount: 200 OK</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -4414,12 +4526,12 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Thieu shipping_address: 200 OK</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -4433,7 +4545,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="69.75" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-08</t>
@@ -4469,12 +4581,12 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Thieu payment_method: 200 OK</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -4488,7 +4600,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.5" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-03</t>
@@ -4524,12 +4636,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Checkout token het han: 200 (khong check exp)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>B1 POST: 400 Bad Request; B2 GET: 200 OK</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -4579,12 +4691,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>XSS trong shipping_address: 200 OK</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -4634,10 +4746,10 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Checkout user role: 200 OK</t>
-        </is>
-      </c>
-      <c r="H15" s="23" t="inlineStr">
+          <t>B1 POST: 400 Bad Request; B2 GET: 404 Not Found</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4653,7 +4765,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="98" customHeight="1">
+    <row r="16" ht="97.5" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-05</t>
@@ -4689,10 +4801,10 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Checkout admin role: 200 OK</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
+          <t>B1 GET: 200 OK; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4708,7 +4820,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.5" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-09</t>
@@ -4743,12 +4855,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Thieu cart_item: 200 OK</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -4797,12 +4909,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Thieu quantity: 200 OK</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -4852,12 +4964,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Shipping address rong: 200 OK</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -4907,12 +5019,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Payment method rong: 200 OK</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -4926,7 +5038,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="238" customHeight="1">
+    <row r="21" ht="237.75" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-13</t>
@@ -4962,12 +5074,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Cart item rong: 200 OK</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -4981,7 +5093,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="154" customHeight="1">
+    <row r="22" ht="153.75" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-03</t>
@@ -5017,12 +5129,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Empty body: 200 OK</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>B1 POST: 400 Bad Request; B2 GET: 404 Not Found</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -5071,12 +5183,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Total amount string dai: 200 OK</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -5090,7 +5202,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="69.75" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-01</t>
@@ -5125,10 +5237,10 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Response co order_id</t>
-        </is>
-      </c>
-      <c r="H24" s="23" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5144,7 +5256,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="140" customHeight="1">
+    <row r="25" ht="139.5" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-02</t>
@@ -5179,10 +5291,10 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Response co message</t>
-        </is>
-      </c>
-      <c r="H25" s="23" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5198,7 +5310,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="55.5" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-05</t>
@@ -5233,12 +5345,12 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Shipping address script tag: 200 OK</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -5287,12 +5399,12 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Quantity am: 200 OK</t>
-        </is>
-      </c>
-      <c r="H27" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -5306,7 +5418,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="182" customHeight="1">
+    <row r="28" ht="181.5" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-15</t>
@@ -5341,12 +5453,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Quantity string: 200 OK</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -5360,7 +5472,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="69.75" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-16</t>
@@ -5395,10 +5507,10 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5414,7 +5526,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="266" customHeight="1">
+    <row r="30" ht="265.5" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-06</t>
@@ -5448,10 +5560,10 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5461,13 +5573,13 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Chỉ người dùng đã đăng nhập mới checkout được' được suy luận hợp lý là bao gồm token còn hiệu lực (chưa hết hạn). Test case hợp lý</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="224" customHeight="1">
+    <row r="31" ht="223.5" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-07</t>
@@ -5501,10 +5613,10 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H31" s="23" t="inlineStr">
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5520,7 +5632,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="280" customHeight="1">
+    <row r="32" ht="279.75" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-08</t>
@@ -5554,10 +5666,10 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H32" s="23" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5573,7 +5685,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="140" customHeight="1">
+    <row r="33" ht="139.5" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-17</t>
@@ -5609,10 +5721,10 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H33" s="23" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5662,10 +5774,10 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H34" s="23" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5681,7 +5793,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="182" customHeight="1">
+    <row r="35" ht="181.5" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-18</t>
@@ -5716,10 +5828,10 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H35" s="23" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5735,7 +5847,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="182" customHeight="1">
+    <row r="36" ht="181.5" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-03</t>
@@ -5768,10 +5880,10 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Response co total_amount</t>
-        </is>
-      </c>
-      <c r="H36" s="23" t="inlineStr">
+          <t>404 Not Found</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5787,7 +5899,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="112" customHeight="1">
+    <row r="37" ht="111.75" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-01</t>
@@ -5822,12 +5934,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Checkout 2 lan: 2 order tao thanh cong</t>
-        </is>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>B1 POST: 400 Bad Request; B2 GET: 200 OK</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I37" s="5" t="n"/>
@@ -5837,7 +5949,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="70" customHeight="1">
+    <row r="38" ht="69.75" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-02</t>
@@ -5873,12 +5985,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Quantity am: 200 OK</t>
-        </is>
-      </c>
-      <c r="H38" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>B1 POST: 400 Bad Request; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I38" s="5" t="n"/>
@@ -5922,12 +6034,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Quantity 0: 200 OK</t>
-        </is>
-      </c>
-      <c r="H39" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
@@ -5972,12 +6084,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Quantity string: 200 OK</t>
-        </is>
-      </c>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
@@ -5987,7 +6099,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="64" customHeight="1">
+    <row r="41" ht="63.75" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-05</t>
@@ -6021,12 +6133,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Product khong ton tai: 200 OK</t>
-        </is>
-      </c>
-      <c r="H41" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
@@ -6037,7 +6149,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -6056,13 +6169,14 @@
     <col width="21.6363636363636" customWidth="1" style="1" min="4" max="4"/>
     <col width="21.7272727272727" customWidth="1" style="1" min="5" max="5"/>
     <col width="20.2727272727273" customWidth="1" style="1" min="6" max="6"/>
-    <col width="9" customWidth="1" style="1" min="7" max="8"/>
+    <col width="41.4090909090909" customWidth="1" style="1" min="7" max="7"/>
+    <col width="9" customWidth="1" style="1" min="8" max="8"/>
     <col width="22.1818181818182" customWidth="1" style="1" min="9" max="9"/>
-    <col width="45.5727272727273" customWidth="1" style="2" min="10" max="10"/>
+    <col width="45.5818181818182" customWidth="1" style="2" min="10" max="10"/>
     <col width="9" customWidth="1" style="1" min="11" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TC ID</t>
@@ -6149,15 +6263,15 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>POST ten trong: 200 OK</t>
-        </is>
-      </c>
-      <c r="H2" s="21" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6203,15 +6317,15 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>POST ten null: 200 OK</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6257,15 +6371,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>POST ten 256 ky tu: 200 OK</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6276,7 +6390,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
+    <row r="5" ht="69.75" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-04</t>
@@ -6311,90 +6425,80 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>POST ten co special chars: 200 OK</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Thiếu hẳn field cũng vi phạm đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="184.5" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>TC-FR14-DP-05</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Tao category voi ten rat dai (boundary test, 1000 ky tu)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Header: Authorization: Bearer {{adminToken}}
+Body: {"name": "A" x 1000 (chuoi 1000 ky tu)}</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>1. POST /api/categories voi ten 1000 ky tu
+2. Kiem tra response</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>He thong xu ly on dinh, KHONG duoc tra loi 500. Chap nhan 1 trong 2 ket qua: (a) 201 Created neu he thong khong gioi han do dai, hoac (b) 400 Bad Request neu he thong co gioi han.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>200 OK - He thong chap nhan ten 1000 ky tu</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Thiếu hẳn field cũng vi phạm đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="185" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>TC-FR14-DP-05</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Tạo category với tên quá dài (255 ký tự)
-➜ ĐÃ SỬA (INVALID): 
-Tạo category với tên rất dài (boundary test, không giả định giới hạn cụ thể)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Header: Authorization: Bearer {{adminToken}}
-Body: {"name": "AAAA...(255 ký tự)"}
-➜ ĐÃ SỬA (INVALID): 
-Header: Authorization: Bearer {{adminToken}}
-Body: {"name": "A" x 1000 (chuỗi 1000 ký tự, không giả định 255)}</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>1. POST /api/categories với tên 255 ký tự
-2. Kiểm tra response
-➜ ĐÃ SỬA (INVALID): 
-1. POST /api/categories với tên 1000 ký tự
-2. Kiểm tra response và trạng thái hệ thống (không được lỗi 500)</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Hệ thống báo lỗi có giới hạn độ dài tên category hay không?
-➜ ĐÃ SỬA (INVALID): 
-Hệ thống xử lý ổn định, KHÔNG được trả lỗi 500. Vì đặc tả không quy định giới hạn độ dài, chấp nhận 1 trong 2 kết quả hợp lệ: (a) 201 Created nếu hệ thống không giới hạn độ dài, hoặc (b) 400 Bad Request nếu hệ thống có giới hạn - cần đối chiếu với backend thực tế khi thực thi.</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>POST ten trung: 200 OK</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>INVALID</t>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>VALID</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Giới hạn '255 ký tự' KHÔNG có trong đặc tả, do AI tự bịa nên em đã thay bằng test case boundary không giả định con số cụ thể. Lý do AI bỏ sót/bịa ra: AI đưa ra con số '255 ký tự' dựa trên pattern phổ biến của kiểu dữ liệu VARCHAR(255) trong các CSDL SQL truyền thống (MySQL/PostgreSQL) - đây là suy luận từ kiến thức huấn luyện chung (pattern quen thuộc), không phải trích xuất từ đặc tả thực tế của API này. Đây là một dạng hallucination do model áp dụng best-practice/convention phổ biến vượt ra ngoài phạm vi đặc tả được cung cấp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="160" customHeight="1">
+          <t>Test case boundary cho do dai ten. He thong tra 200 OK thay vi 400/501.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="159.75" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-06</t>
@@ -6429,15 +6533,15 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>POST ten trung: 200 OK (cho phep)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -6448,7 +6552,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="131" customHeight="1">
+    <row r="8" ht="130.5" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-07</t>
@@ -6482,15 +6586,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>POST ten trung: 200 OK</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 409 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -6501,7 +6605,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="98" customHeight="1">
+    <row r="9" ht="97.5" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-01</t>
@@ -6536,15 +6640,15 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>POST ten XSS: 200 OK</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -6555,7 +6659,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="69.75" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-01</t>
@@ -6588,15 +6692,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>POST category thanh cong: 200 OK</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6607,7 +6711,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.5" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-02</t>
@@ -6640,15 +6744,15 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>GET categories: 200 OK, co category moi</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6694,15 +6798,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>DELETE category: 200 OK</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
+          <t>B1 DELETE: 200 OK; B2 GET: 200 OK; B3 DELETE: 200 OK - BUG: kỳ vọng 204 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6713,7 +6817,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="98" customHeight="1">
+    <row r="13" ht="97.5" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-08</t>
@@ -6747,15 +6851,15 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>DELETE khong ton tai: 200 OK</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
+          <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 404 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -6801,15 +6905,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>GET category by ID: 200 OK</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
+          <t>B1 PUT: 400 Bad Request; B2 GET: 200 OK</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6854,15 +6958,15 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>GET by ID khong ton tai: 404</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6873,7 +6977,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="112" customHeight="1">
+    <row r="16" ht="111.75" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-05</t>
@@ -6910,15 +7014,15 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>PUT category: 200 OK</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
+          <t>B1 POST: 400 Bad Request; B2 GET: 200 OK; B3 DELETE: 200 OK; B4 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -6929,7 +7033,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.5" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-02</t>
@@ -6963,15 +7067,15 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>POST ten SQL inject: 200 OK</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7016,15 +7120,15 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>DELETE khong token: 401</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7069,15 +7173,15 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>DELETE user role: 200 OK</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7088,7 +7192,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="98" customHeight="1">
+    <row r="20" ht="97.5" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-05</t>
@@ -7122,15 +7226,15 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>PUT khong token: 401</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
+          <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7141,7 +7245,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="98" customHeight="1">
+    <row r="21" ht="97.5" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-06</t>
@@ -7175,15 +7279,15 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>POST khong token: 401</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7228,15 +7332,15 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>PUT user role: 200 OK</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+          <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7247,7 +7351,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="112" customHeight="1">
+    <row r="23" ht="111.75" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-08</t>
@@ -7280,15 +7384,15 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>POST user role: 200 OK</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 401 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7332,15 +7436,15 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7385,15 +7489,15 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Response co id</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7404,7 +7508,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="55.5" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-02</t>
@@ -7438,15 +7542,15 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Response co name</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7492,15 +7596,15 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Response co created_at</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7546,15 +7650,15 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Response co updated_at</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7565,7 +7669,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="112" customHeight="1">
+    <row r="29" ht="111.75" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-05</t>
@@ -7600,15 +7704,15 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>DELETE tra 200 khong phai 204</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7654,15 +7758,15 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>POST tra 200 khong phai 201</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
+          <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 204 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7673,7 +7777,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="98" customHeight="1">
+    <row r="31" ht="97.5" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-07</t>
@@ -7708,15 +7812,15 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Response message dung format</t>
-        </is>
-      </c>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
+          <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 404 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>INCOMPLETE</t>
         </is>
@@ -7762,15 +7866,15 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Categories list dung format</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7816,15 +7920,15 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H33" s="20" t="inlineStr">
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7870,15 +7974,15 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7925,15 +8029,15 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>GET categories list: 200 OK</t>
-        </is>
-      </c>
-      <c r="H35" s="20" t="inlineStr">
+          <t>B1 DELETE: 200 OK; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7944,7 +8048,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="112" customHeight="1">
+    <row r="36" ht="111.75" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-10</t>
@@ -7979,15 +8083,15 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Dung nhu expected</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
+          <t>B1 POST: 400 Bad Request; B2 DELETE: 200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
@@ -7998,7 +8102,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="106" customHeight="1">
+    <row r="37" ht="105.75" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-01</t>
@@ -8032,23 +8136,23 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>POST ten 1 ky tu: 200 OK</t>
-        </is>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
+          <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I37" s="9" t="n"/>
+      <c r="I37" s="12" t="n"/>
       <c r="J37" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì prompt yêu cầu sinh test case theo 'domain partition trên từng parameter' được liệt kê trong đặc tả; AI chỉ suy luận trên các field đã được định nghĩa, không tự nghĩ đến trường hợp field không nằm trong đặc tả) - đây là giới hạn phạm vi suy luận của model khi bám sát input đã cho.</t>
         </is>
       </c>
-      <c r="K37" s="10" t="n"/>
-    </row>
-    <row r="38" ht="98" customHeight="1">
+      <c r="K37" s="13" t="n"/>
+    </row>
+    <row r="38" ht="97.5" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-02</t>
@@ -8083,21 +8187,21 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>POST ten 255 ky tu: 200 OK</t>
-        </is>
-      </c>
-      <c r="H38" s="22" t="inlineStr">
+          <t>B1 POST: 400 Bad Request; B2 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I38" s="9" t="n"/>
+      <c r="I38" s="12" t="n"/>
       <c r="J38" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì test case AI sinh ra theo luồng tuần tự (1 request - 1 response tại một thời điểm), không có khả năng/không được yêu cầu mô phỏng tình huống đồng thời. Đây là hạn chế đặc trưng của việc sinh test case từ đặc tả tĩnh: AI không tự suy luận về các vấn đề vận hành thực tế nếu prompt không yêu cầu rõ ràng.</t>
         </is>
       </c>
-      <c r="K38" s="10" t="n"/>
+      <c r="K38" s="13" t="n"/>
     </row>
     <row r="39" ht="117" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -8133,23 +8237,23 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>POST ten co dau: 200 OK</t>
-        </is>
-      </c>
-      <c r="H39" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="n"/>
+          <t>404 Not Found</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="n"/>
       <c r="J39" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI generate test case dựa trên các HTTP method được liệt kê tường minh trong đặc tả (GET/POST/PUT/DELETE), không tự nghĩ đến việc test các method KHÔNG được định nghĩa trong đặc tả. Đây là đặc điểm của model: thiên về mặt theo đúng đặc tả, thiếu tư duy mặt ngược lại thì như nào.</t>
         </is>
       </c>
-      <c r="K39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="161" customHeight="1">
+      <c r="K39" s="13" t="n"/>
+    </row>
+    <row r="40" ht="160.5" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-04</t>
@@ -8184,23 +8288,23 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>POST ten co so: 200 OK</t>
-        </is>
-      </c>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="n"/>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="n"/>
       <c r="J40" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI tập trung sinh test case validate nội dung body theo đúng domain partition được yêu cầu trong prompt, chứ không kiểm tra các thuộc tính protocol-level như HTTP header Content-Type. Đây là hạn chế do phạm vi prompt (chỉ yêu cầu domain partition/state/security/schema) không bao gồm rõ ràng validation ở tầng request header.</t>
         </is>
       </c>
-      <c r="K40" s="10" t="n"/>
-    </row>
-    <row r="41" ht="125" customHeight="1">
+      <c r="K40" s="13" t="n"/>
+    </row>
+    <row r="41" ht="124.5" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-05</t>
@@ -8235,23 +8339,24 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>POST ten co ky tu dac biet: 200 OK</t>
-        </is>
-      </c>
-      <c r="H41" s="22" t="inlineStr">
+          <t>B1 POST: 400 Bad Request; B2 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I41" s="9" t="n"/>
+      <c r="I41" s="12" t="n"/>
       <c r="J41" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI ít khi tự sinh test case về encoding/Unicode edge case trừ khi được yêu cầu cụ thể trong prompt - đây là đặc điểm kỹ thuật của hệ thống, thường không được nêu rõ trong đặc tả chức năng, nên AI thiên về test theo đặc tả hơn là các edge case kỹ thuật/encoding.</t>
         </is>
       </c>
-      <c r="K41" s="10" t="n"/>
+      <c r="K41" s="13" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
+++ b/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19200" windowHeight="7510" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19200" windowHeight="7510" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -47,8 +47,7 @@
     <font>
       <name val="Times New Roman"/>
       <charset val="134"/>
-      <strike val="1"/>
-      <color rgb="FF999999"/>
+      <color theme="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -238,8 +237,19 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -456,8 +466,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -590,6 +606,12 @@
         <color theme="4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -729,7 +751,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -754,7 +776,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -768,8 +790,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -777,6 +818,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1297,390 +1342,485 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="30" customWidth="1" style="1" min="1" max="1"/>
-    <col width="52.3636363636364" customWidth="1" style="1" min="2" max="2"/>
-    <col width="36.8181818181818" customWidth="1" style="1" min="3" max="3"/>
-    <col width="15" customWidth="1" style="1" min="4" max="6"/>
-    <col width="40" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9" customWidth="1" style="1" min="8" max="16384"/>
+    <col width="30" customWidth="1" style="14" min="1" max="1"/>
+    <col width="52.3636363636364" customWidth="1" style="14" min="2" max="2"/>
+    <col width="36.8181818181818" customWidth="1" style="14" min="3" max="3"/>
+    <col width="15" customWidth="1" style="14" min="4" max="6"/>
+    <col width="40" customWidth="1" style="14" min="7" max="7"/>
+    <col width="9" customWidth="1" style="14" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>HW06 API Testing — Test Summary Report</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Student ID: 23127031 | Date: 2026-08-24 01:24</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Number of APIs tested</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="25" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Total test cases generated</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="25" t="n">
         <v>151</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Total requests in collection</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="25" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Assertions executed</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="25" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Assertions passed</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="25" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Assertions failed</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>48.1%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Pass rate</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="25" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Bugs found</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Critical bugs</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Major bugs</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Minor bugs</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Detailed Results by API</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>Assertions</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>Bugs Found</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="25" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="25" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Category CRUD</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>FR-14</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="25" t="n">
         <v>51</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="G22" s="18" t="n">
+      <c r="G22" s="25" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n">
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n">
         <v>151</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="27" t="n">
         <v>77</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="27" t="n">
         <v>78</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="27" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Bug Severity Breakdown</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>Issue Numbers</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>#166, #168, #169, #170, #171, #174, #175</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>#167, #172, #173, #179</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>#176, #177, #178</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C30" s="20" t="n"/>
+      <c r="C30" s="27" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>AI Audit Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>Test case dung, co ket qua ro rang</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>Test case bi bo di vi AI hallucination</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>Test case can bo sung them</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>EXT (no label)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>Test case extension tu tay them</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="n">
+        <v>120</v>
+      </c>
+      <c r="C38" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1701,1716 +1841,1716 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="28.0909090909091" defaultRowHeight="14"/>
   <cols>
-    <col width="15.6363636363636" customWidth="1" style="1" min="1" max="1"/>
-    <col width="28.0909090909091" customWidth="1" style="1" min="2" max="6"/>
-    <col width="37.0636363636364" customWidth="1" style="1" min="7" max="7"/>
-    <col width="35.4909090909091" customWidth="1" style="1" min="8" max="8"/>
-    <col width="28.0909090909091" customWidth="1" style="1" min="9" max="9"/>
-    <col width="35" customWidth="1" style="1" min="10" max="10"/>
-    <col width="28.0909090909091" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="15.6363636363636" customWidth="1" style="14" min="1" max="1"/>
+    <col width="28.0909090909091" customWidth="1" style="14" min="2" max="6"/>
+    <col width="37.0636363636364" customWidth="1" style="14" min="7" max="7"/>
+    <col width="35.4909090909091" customWidth="1" style="14" min="8" max="8"/>
+    <col width="28.0909090909091" customWidth="1" style="14" min="9" max="9"/>
+    <col width="35" customWidth="1" style="14" min="10" max="10"/>
+    <col width="28.0909090909091" customWidth="1" style="14" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="55.5" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Happy path: email và password khớp tài khoản</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>200 OK, trả về JWT token và thông tin user</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>AI dựa trực tiếp từ đặc tả FR-02. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Email đúng, password sai</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"WrongPass999"}</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Password không khớp -&gt; đăng nhập thất bại, AI có căn cứ trực tiếp dựa vào đặc tả em cung cấp. Mã lỗi cụ thể chưa được nêu trong đặc tả nên AI ghi cần xác định thêm, nhưng kết quả là thất bại được xác định đúng</t>
         </is>
       </c>
     </row>
     <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Email đúng, password trống (empty string)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: ""</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":""}</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Password rỗng vẫn là 1 giá trị không khớp mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="5" ht="55.5" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Email đúng, password null</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: null</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":null}</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Password giá trị null là giá trị không khớp với mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="6" ht="55.5" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-05</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Email đúng, password sai kiểu dữ liệu (number)</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: 123456</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":123456}</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>Password giá trị số là giá trị không khớp với mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="7" ht="84" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-06</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Email đúng, password quá dài (56 ký tự)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA"</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"&lt;56 chars&gt;"}</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Độ dài không khớp mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="8" ht="55.5" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-07</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Email đúng, password chứa ký tự đặc biệt (không khớp)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "P@$$w!r#d"</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"P@$$w!r#d"}</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại (password không khớp). HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Mật khẩu toàn là ký tự đặc biệt nhưng vẫn không khớp với mật khẩu thật nên đăng nhập thất bại. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="9" ht="55.5" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-08</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Email không tồn tại, password đúng format</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Tài khoản với email này không tồn tại</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>email: "nonexistent@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"nonexistent@eshop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>Email không tồn tại -&gt; không khớp tài khoản nào -&gt; thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="55.5" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-09</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Email trống (empty), password đúng</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Không có tài khoản với email trống</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>email: ""
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>Email trống là email không tồn tại nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="55.5" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-10</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Email null, password đúng</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Không có tài khoản với email null</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>email: null
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":null,"password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>Email null là email không tồn tại nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="55.5" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-11</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Email sai kiểu dữ liệu (number), password đúng</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Không có tài khoản với email là số</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>email: 12345
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":12345,"password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Email toàn số là email không tồn tại, không đúng format nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-DP-12</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Cả email và password đều trống</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Không có điều kiện trước</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>email: ""
 password: ""</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"","password":""}</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>Cả email và password đều rỗng, đăng nhập thất bại. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="14" ht="55.5" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-ST-01</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 1 - bộ đếm tăng lên 1</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đang hoạt động, chưa có lần sai nào [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass1"</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass1"}</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 1 (&lt; 3, chưa khóa).</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="15" ht="55.5" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-ST-02</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 2 - bộ đếm tăng lên 2</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đã có 1 lần sai (bộ đếm = 1) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass2"</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass2"}</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 2 (&lt; 3, chưa khóa).</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="16" ht="55.5" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-ST-03</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 3 - kích hoạt khóa 30 giây</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đã có 2 lần sai liên tiếp (bộ đếm = 2) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass3"</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass3"}</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 3 (&gt;= 3 -&gt; khóa 30 giây).</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55.5" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-ST-04</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập đúng mật khẩu trong thời gian khóa</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Tài khoản đang bị khóa (&lt; 30 giây) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "Locktest123!"</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"Locktest123!"}</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 403 Forbidden, Response: {"error": "Tài khoản đã bị khóa. Vui lòng thử lại sau."} (kiểm tra thời gian khóa được thực hiện TRƯỚC khi so khớp mật khẩu, nên dù mật khẩu đúng vẫn bị chặn ở bước khóa). Tài khoản vẫn bị khóa.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="18" ht="55.5" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-ST-05</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập sai mật khẩu trong thời gian khóa</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Tài khoản đang bị khóa (&lt; 30 giây) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPassX"</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPassX"}</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 403 Forbidden, Response: {"error": "Tài khoản đã bị khóa. Vui lòng thử lại sau."}. Tài khoản vẫn bị khóa.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="19" ht="55.5" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-ST-06</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập đúng mật khẩu ngay sau khi hết 30 giây khóa</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Tài khoản vừa hết thời gian khóa 30 giây [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "Locktest123!"</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"Locktest123!"}</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công. 200 OK + JWT. Bộ đếm reset về 0.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="20" ht="69.75" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-ST-07</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập sai mật khẩu ngay sau khi hết khóa</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Tài khoản vừa hết thời gian khóa 30 giây [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPassAfterUnlock"</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPassAfterUnlock"}</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm bắt đầu lại từ 1.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>Theo suy luận cùng với từ đặc tả suy ra thì test case valid, sau khi mở khóa thì bộ đếm reset về 0, tiếp tục sai nên +1</t>
         </is>
       </c>
     </row>
     <row r="21" ht="75.75" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-01</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>SQL Injection ở trường email</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>email: ' OR 1=1 --
 password: "anypassword"</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "' OR 1=1 --", "password": "anypassword"}</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Hệ thống xử lý đúng (parameterized query). Không lộ SQL/stack trace.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="76.5" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-02</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>SQL Injection ở trường password</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: ' OR 1=1 --</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "test@eshop.com", "password": "' OR 1=1 --"}</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Hệ thống xử lý đúng (parameterized query). Không lộ SQL/stack trace.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="55.5" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-03</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>SQL Injection UNION-based - trích xuất thông tin DB</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>email: ' UNION SELECT table_name,null FROM information_schema.tables --
 password: "x"</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "&lt;SQL injection query&gt;", "password": "x"}</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Không lộ thông tin cấu trúc DB.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="I23" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>Tương tự, mở rộng dạng UNION-based, Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công..</t>
         </is>
       </c>
     </row>
     <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-04</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra thông báo lỗi chung - email không tồn tại</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Tài khoản "wronguser@eshop.com" không tồn tại</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>email: "wronguser@eshop.com"
 password: "WrongPass123"</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "wronguser@eshop.com", "password": "WrongPass123"}</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Thông báo lỗi chung, không để lộ "email không tồn tại".</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'không để lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="55.5" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-05</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra thông báo lỗi chung - email đúng, mật khẩu sai</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>Tài khoản "test@eshop.com" tồn tại</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "test@eshop.com", "password": "WrongPass999"}</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Thông báo lỗi chung. Không để lộ "mật khẩu sai".</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="I25" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'không để lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="118.5" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-06</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra không có sự khác biệt thời gian phản hồi giữa email tồn tại và không tồn tại (chống User Enumeration qua timing attack)</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường; đã có tài khoản test@eshop.com</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Case A: email: "test@eshop.com", password: "WrongPass999"
 Case B: email: "noaccount@eshop.com", password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>1. Gửi lần lượt 2 request POST /api/login với Case A và Case B
 2. Đo thời gian phản hồi (response time) của mỗi request
 3. So sánh chênh lệch thời gian giữa 2 case</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Thời gian phản hồi giữa 2 case không chênh lệch đáng kể (ví dụ &lt; 50-100ms), tránh lộ thông tin email có tồn tại hay không qua timing side-channel. Cả 2 case đều trả về HTTP 401 Unauthorized, {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="I26" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra timing attack - vì code hiện có 2 nhánh xử lý khác nhau (user không tồn tại trả lỗi ngay; user tồn tại phải so sánh password) nên thời gian xử lý có thể khác biệt và bị lợi dụng để dò tìm email tồn tại trong hệ thống. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="87" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-07</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra response không lộ SQL error hoặc stack trace</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "any"</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Gửi request với dữ liệu sai
 3. Kiểm tra toàn bộ response body</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>Response không chứa: lỗi SQL, stack trace, tên bảng, tên cột, đường dẫn file server. Chỉ trả về lỗi chung. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>Dựa vào SEC-05 + 'không lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="186.75" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-08</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra response/JWT không lộ thông tin nhạy cảm (password) của user</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Tài khoản test@eshop.com tồn tại</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login với thông tin hợp lệ
 2. Nhận response 200 OK
 3. Kiểm tra field "user" trong response body và payload JWT</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Field "user" trong response và payload JWT KHÔNG được chứa field "password" (dù ở dạng plaintext hay hash). Chỉ chứa các field an toàn như id, name, email, role.</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra rò rỉ dữ liệu nhạy cảm. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="29" ht="55.5" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra response thành công có field "token" và "user"</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công với tai khoan hợp lệ</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Nhận response 200 OK
 3. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>Response phải chứa: trường "token" (string, khác null) và trường "user" (object, khác null).</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'trả về token và user'.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra trường "token" là string</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy giá trị field "token"
 3. Kiểm tra kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Field "token" phải là string, không được là null, number, object hay array. </t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="I30" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>Dùng để kiểm tra kiểu dữ liệu cơ bản của field đã được xác nhận tồn tại. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra trường "user" là object</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy giá trị field "user"
 3. Kiểm tra kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>Field "user" phải là object, không được là null, string, number hay array.</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>Dùng để kiểm tra kiểu dữ liệu cơ bản của field đã được xác nhận tồn tại. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="55.5" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-04</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra JWT có cấu trúc 3 phần (header.payload.signature)</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, nhận được JWT token</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy token từ response
@@ -3418,55 +3558,55 @@
 4. Kiểm tra số phần</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Token phải có đúng 3 phần: header, payload, signature. Nếu không -&gt; thất bại</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra cấu trúc JWT chuẩn (3 phần) - đúng với mọi JWT hợp lệ. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="69.75" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-05</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra JWT header la base64 JSON hợp lệ</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần header (phần đầu tiên)
@@ -3474,55 +3614,55 @@
 4. Parse JSON</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>Header sau decode phải là JSON hợp lệ, chứa tối thiểu 2 field: "alg" (thuật toán ký, mặc định "HS256" do thư viện jsonwebtoken khi không chỉ định algorithm) và "typ" ("JWT").</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>JWT hợp lệ luôn phải decode được header. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="69.75" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-06</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra JWT payload la base64 JSON hợp lệ</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần payload (phần thứ hai)
@@ -3530,386 +3670,386 @@
 4. Parse JSON</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Payload sau decode phải là JSON hợp lệ, chứa field "id" (id user) và "role". Field "iat" (issued at) được thư viện tự thêm. Lưu ý: KHÔNG có field "exp" (hết hạn) vì jwt.sign() được gọi không kèm option expiresIn -&gt; token không bao giờ hết hạn (rủi ro bảo mật, cần ghi vào bug report).</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>Payload luôn phải decode được. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="55.5" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-07</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra JWT signature không rỗng</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần signature (phần cuối cùng)
 3. Kiểm tra độ dài</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Signature phải có độ dài &gt; 0, không được rỗng. Thuật toán ký mặc định là HS256 (HMAC-SHA256) vì jwt.sign() không truyền option algorithm.</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>Chữ ký JWT không được rỗng - tính chất cơ bản của JWT. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-08</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra JWT đúng định dạng base64url</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy token từ response
 3. Kiểm tra ký tự trong token</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>JWT chỉ chứa ký tự base64url: A-Z, a-z, 0-9, -, _, ".": phân cách 3 phần</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="I36" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>Định dạng base64url - tính chất cơ bản của JWT. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="195" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Email phân biệt hoa/thường</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>email: "Test@EShop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"Test@EShop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"} (vì so sánh email trong SQL phân biệt hoa/thường, "Test@EShop.com" khác "test@eshop.com" nên không tìm thấy user).</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="I37" s="16" t="n"/>
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>Cần test thêm hệ thống có phân biệt chữ hoa, chữ thường hay không. Do tính chất bảo mật của email và password nên phân biệt chữ hoa, chữ thường. Lý do AI bỏ sót theo em nghĩ là do prompt của em chỉ yêu cầu domain partitioning cho field email một cách chung chung, không có gợi ý cụ thể, nên AI thường chỉ quan tâm đúng các trường hợp email đúng/sai định dạng mà không test các case nhạy cảm, chi tiết hơn như phân biệt chữ hoa với chữ thường</t>
         </is>
       </c>
     </row>
     <row r="38" ht="207.75" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Email có khoảng trắng đầu/cuối</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>email: " test@eshop.com "
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":" test@eshop.com ","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"} (email có khoảng trắng đầu/cuối không được trim trước khi so khớp trong DB, nên " test@eshop.com " khác với "test@eshop.com").</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="I38" s="16" t="n"/>
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>Test case kiểm tra hệ thống có tự động trim khoảng trắng ở email trước khi xử lý hay không đặc tả không nêu rõ điều này. Lý do AI bỏ sót: prompt gốc chỉ yêu cầu domain partition theo định dạng email hợp lệ/không hợp lệ một cách chung chung, không đề cập input nhiễu như khoảng trắng thừa - đây là input edge-case thực tế thường gặp mà đặc tả không nêu, nên AI (chỉ dựa vào đặc tả) không tự sinh ra được.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="241.5" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>Race condition - 2 request sai password gửi đồng thời</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>Tài khoản locktest@eshop.com, bộ đếm đang = 0</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongA" (request 1)
 password: "WrongB" (request 2, gửi gần như cùng lúc)</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời (song song, không chờ response) 2 request POST /api/login sai password
 2. Kiểm tra login_attempts cuối cùng qua GET /api/admin/users hoặc thử đăng nhập lại</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>Bộ đếm tăng đúng cho cả 2 lần thất bại.</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>B1 POST: 500 Internal Server Error; B2 GET: 401 Unauthorized</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H39" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="I39" s="16" t="n"/>
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>Test case hợp lý để phát hiện lỗi đồng thời tiềm ẩn. Lý do AI bỏ sót: AI sinh test case dựa trên đặc tả API (request/response tĩnh), không có khả năng suy luận về hành vi đồng  thời vì AI chỉ được cung cấp đặc tả API, không có prompt chi tiết hơn về hành động này. Đây là hạn chế đặc trưng khi sinh test case chỉ từ đặc tả mà không phân tích thực tế.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="234.75" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Content-Type sai (form-urlencoded thay vì JSON)</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Header: Content-Type: application/x-www-form-urlencoded
 Body: email=test@eshop.com&amp;password=Test1234!</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login với Content-Type sai và body dạng form-encoded thay vì JSON</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>Do body-parser chỉ parse JSON khi Content-Type là application/json, request dạng form-urlencoded sẽ có req.body rỗng ({}) -&gt; email/password đều undefined -&gt; DB không tìm thấy user khớp -&gt; HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="I40" s="16" t="n"/>
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>Test case hợp lý để kiểm tra khả năng chịu lỗi khi client gửi sai Content-Type - tình huống thực tế hay gặp. Lý do AI bỏ sót: AI thường giả định client luôn gửi đúng Content-Type theo đặc tả (application/json) khi sinh test case cho request body, không tự nghĩ ra kịch bản client gửi sai định dạng header vì đây là đặc tính của tầng HTTP/middleware (body-parser), nằm ngoài phạm vi đặc tả logic nghiệp vụ mà AI được cung cấp.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="409.5" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Email cực dài (tiềm năng DoS / buffer)</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>Không có tài khoản nào khớp email này</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>email: "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/login với email dài 5000+ ký tự</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>Server không bị treo/crash: SQLite xử lý tham số dài bình thường qua parameterized query, không tìm thấy user khớp -&gt; HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="I41" s="16" t="n"/>
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>Test case hợp lý để kiểm tra khả năng chống chịu input bất thường/DoS tiềm ẩn. Lý do AI bỏ sót: đặc tả API không đề cập giới hạn độ dài field email, và AI khi sinh test theo domain partition thường chỉ xét các mốc độ dài hợp lý (email hợp lệ/không hợp lệ theo định dạng) chứ không chủ động nghĩ tới input lớn nhằm mục đích kiểm thử bảo mật/hiệu năng - đây đòi hỏi prompt chi tiết hơn là chỉ dựa theo đặc tả chức năng có sẵn.</t>
         </is>
@@ -3930,2219 +4070,2219 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="21.5454545454545" customWidth="1" style="1" min="1" max="1"/>
-    <col width="30.4545454545455" customWidth="1" style="1" min="2" max="2"/>
-    <col width="40" customWidth="1" style="1" min="3" max="3"/>
-    <col width="50" customWidth="1" style="1" min="4" max="4"/>
-    <col width="45" customWidth="1" style="1" min="5" max="5"/>
-    <col width="55" customWidth="1" style="1" min="6" max="6"/>
-    <col width="18" customWidth="1" style="1" min="7" max="7"/>
-    <col width="12" customWidth="1" style="1" min="8" max="8"/>
-    <col width="18.0909090909091" customWidth="1" style="1" min="9" max="9"/>
-    <col width="29.6363636363636" customWidth="1" style="1" min="10" max="10"/>
-    <col width="8" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="21.5454545454545" customWidth="1" style="14" min="1" max="1"/>
+    <col width="30.4545454545455" customWidth="1" style="14" min="2" max="2"/>
+    <col width="40" customWidth="1" style="14" min="3" max="3"/>
+    <col width="50" customWidth="1" style="14" min="4" max="4"/>
+    <col width="45" customWidth="1" style="14" min="5" max="5"/>
+    <col width="55" customWidth="1" style="14" min="6" max="6"/>
+    <col width="18" customWidth="1" style="14" min="7" max="7"/>
+    <col width="12" customWidth="1" style="14" min="8" max="8"/>
+    <col width="18.0909090909091" customWidth="1" style="14" min="9" max="9"/>
+    <col width="29.6363636363636" customWidth="1" style="14" min="10" max="10"/>
+    <col width="8" customWidth="1" style="14" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="97.5" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Shipping address hợp lệ</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Thanh toán thành công. HTTP 200 OK, Response: {"message":"Checkout successful","orderId":&lt;id&gt;}.</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả, happy path bình thường.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Shipping address trống (empty string)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": ""}</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": ""}</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không nói shipping_address có không được để trống hay không nhưng theo em shipping address không được để trống, suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Shipping address null</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": null}</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": null}</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không nói shipping_address có không được null hay không nhưng theo em shipping address không được để trống, suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Shipping address quá dài (500 ký tự)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "&lt;500 char string&gt;"}</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "&lt;500 chars&gt;"}</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không quy định giới hạn độ dài cho shipping_address nhưng cũng cần test để tránh DoS.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="126" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-01</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Shipping address chứa ký tự đặc biệt (HTML/SQL)</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "&lt;script&gt;alert(1)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "&lt;script&gt;alert(1)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không quy định nhưng theo em cần test xem hệ thống có escape hay không nên test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="69.75" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-ST-01</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Giỏ hàng có sản phẩm - thanh toán thành công</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có ít nhất 1 sản phẩm.</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Thanh toán thành công. HTTP 200 OK, Response: {"message":"Checkout successful","orderId":&lt;id&gt;}.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="195.75" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-ST-02</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Giỏ hàng trống - không thể thanh toán</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống (không có sản phẩm).</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Giỏ hàng trống báo lỗi khi thanh toán </t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Dù đặc tả gốc không quy định nhưng cần test case "không thể thanh toán khi giỏ trống" </t>
         </is>
       </c>
     </row>
     <row r="9" ht="153.75" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-05</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Giỏ hàng trống, total_amount client gửi khác 0</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống.</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 500000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 500000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="84" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-06</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - không chấp nhận giá trị client gửi</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 1, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 1, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-07</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - client gửi giá trị âm</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": -50000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": -50000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="69.75" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-08</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - client gửi giá trị rất lớn</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 999999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 999999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Backend tự tính lại</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="55.5" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-ST-03</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Giỏ hàng bị xóa sau thanh toán thành công</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout -&gt; thanh toán thành công
 2. GET /api/cart (kiểm tra giỏ hàng)
 3. Hoặc checkout lần nữa</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Giỏ hàng bị xóa sau khi thanh toán thành công</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Sau thanh toán thành công, giỏ hàng được xóa'.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="252" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-02</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Checkout khi chưa đăng nhập (không có token)</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token hoặc token không hợp lệ.</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
 1. KHÔNG gửi header Authorization
 2. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized, Response: {"error":"Unauthorized"} khi không có token.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Chỉ người dùng đã đăng nhập mới tiến hành thanh toán được'.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="84" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-ST-04</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra order mới tạo có status ban đầu là "pending"</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":100000,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout, lấy orderId
 2. GET /api/orders/:id
 3. Kiểm tra status</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>order mới tạo phải có status pending.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 404 Not Found</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>Test case kiểm tra trạng thái khởi tạo của order, là điểm bắt đầu của state machine.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="97.5" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-ST-05</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Checkout khi giỏ hàng trống</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống (không có sản phẩm nào).</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận giỏ hàng trống
 2. POST /api/checkout
 3. GET /api/cart - kiểm tra giỏ hàng vẫn trống</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Không checkout được khi giỏ hàng trống</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ hệ thống có cho phép checkout khi giỏ hàng trống hay từ chối nhưng theo em nên từ chối.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55.5" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-09</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>total_amount gửi giá trị null tường minh</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":null,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount: null
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Phải validate total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>Test nếu gửi total_amount = null. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="18" ht="84" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-10</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>total_amount gửi kiểu boolean true thay vì number</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":true,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount: true
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Phải validate kiểu total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra kiểu dữ liệu khác cho total_amount = boolean, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-11</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount thấp hơn thực tế</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 10000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = 10000
 3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>Test case hợp lý: kiểm tra backend có tin tưởng total_amount thấp hơn giá trị thực từ client hay không. Đây là kịch bản price manipulation thực tế và mở rộng domain partition cho total_amount.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-12</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount cao hơn thực tế</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = 999999999
 3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>Test case hợp lý: kiểm tra backend có chấp nhận total_amount cao hơn giá trị thực hay không. Dù ít gây thiệt hại trực tiếp hơn giá thấp, backend vẫn phải không tin giá trị do client gửi để tránh sai lệch dữ liệu.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="237.75" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-13</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount sai kiểu (string)</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": "abc", "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = "abc"
 3. Kiểm tra xử lý của hệ thống</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>Phải validate kiểu total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>Trường hợp sai kiểu dữ liệu (string thay vì number) dù đặc tả không quy định, nhưng vẫn cần thiết trong test case.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="153.75" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-03</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>XSS trong shipping_address - mã HTML/Script</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "&lt;script&gt;alert(document.cookie)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa &lt;script&gt;alert(document.cookie)&lt;/script&gt;
 2. Nếu thanh toán thành công, GET /api/orders hoặc endpoint hiển thị địa chỉ
 3. Kiểm tra địa chỉ được escape an toàn</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Phải có escape shipping_address.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 404 Not Found</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>Hệ thống phải escape mã HTML/script khi lưu hoặc hiển thị. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-04</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>XSS trong shipping_address - mã phức tạp hơn</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "&lt;img src=x onerror=alert(1)&gt;"}</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa &lt;img src=x onerror=alert(1)&gt;
 2. Kiểm tra response và cách hệ thống xử lý địa chỉ</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>Phải có escape shipping_address</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>Hệ thống phải escape mã HTML/script khi lưu hoặc hiển thị. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Response thanh toán thành công có status 2xx</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm. Dữ liệu hợp lệ.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với dữ liệu hợp lệ
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Response thành công là HTTP 200 OK vì route gọi res.json() mà không set status 201.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="139.5" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Response thanh toán thành công có cấu trúc response hợp lệ</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm. Dữ liệu hợp lệ.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với dữ liệu hợp lệ
 2. Kiểm tra toàn bộ response body</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>Response thành công theo code gồm message và orderId. Không trả total_amount, status hay shipping_address.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>Tên field cụ thể trong response (orderId...) không được liệt kê trong đặc tả nhưng vẫn cần test cấu trúc hợp lệ JSON khi thành công</t>
         </is>
       </c>
     </row>
     <row r="26" ht="55.5" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-05</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Thiếu header Authorization - response báo lỗi</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Người dùng chưa đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout KHÔNG gửi header Authorization
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized, Response: {"error":"Unauthorized"}.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>Trực tiếp từ 'chỉ người dùng đã đăng nhập mới checkout được'.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="84" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-14</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Thiếu field bắt buộc shipping_address - response báo lỗi</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000}</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout THIẾU field shipping_address
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="181.5" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-15</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Thiếu field bắt buộc total_amount - response báo lỗi</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout THIẾU field total_amount
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Báo lỗi</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="69.75" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-16</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Body trống - không gửi field nào - response báo lỗi</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với body rỗng {}
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>Cả hai field đều không được validate trước INSERT; không có lỗi 400 ở tầng ứng dụng. Kết quả DB phụ thuộc schema.</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="265.5" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-06</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Checkout với token hết hạn</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã hết hạn. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;expired_token&gt;
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với expired_token</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>JWT hết hạn làm jwt.verify lỗi và middleware trả HTTP 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>Chỉ người dùng đã đăng nhập mới checkout được' được suy luận hợp lý là bao gồm token còn hiệu lực (chưa hết hạn). Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="31" ht="223.5" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-07</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Checkout với token giả mạo (sai chữ ký)</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã bị sửa đổi (sai chữ ký). Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;tampered_token&gt;
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với tampered_token</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>JWT sai chữ ký làm jwt.verify lỗi và middleware trả HTTP 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>Token bị sửa đổi/sai chữ ký về bản chất không còn là 'người dùng đã đăng nhập hợp lệ'. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="32" ht="279.75" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-08</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Checkout với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user"). Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với user_token</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Checkout thành công</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả, happy path bình thường.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="139.5" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-17</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Checkout với giỏ hàng nhiều sản phẩm (3+ sản phẩm)</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 3 sản phẩm với giá trị khác nhau.</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 500000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>1. Thêm 3 sản phẩm vào giỏ hàng (giá: 100000, 150000, 250000)
 2. POST /api/checkout với total_amount sai
 3. Kiểm tra order</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>Backend không tự tính lại total_amount từ giỏ hàng, kể cả nhiều sản phẩm; dùng trực tiếp giá trị client gửi.</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>Dựa vào từ 'Backend phải tự tính lại tổng tiền' - áp dụng cho mọi số lượng sản phẩm trong giỏ, kể cả nhiều sản phẩm.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="294" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-09</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Checkout với shipping_address chứa SQL injection</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "' OR 1=1 --"}</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa SQL injection</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Parameterized query xử lý payload SQL injection an toàn; chuỗi được truyền như dữ liệu thay vì nối vào SQL.</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>Dựa vào SEC-05 (parameterized query) là yêu cầu bảo mật chung của toàn hệ thống.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="181.5" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-DP-18</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>shipping_address gửi sai kiểu dữ liệu number thay vì string</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":150000,"shipping_address":12345}</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address: 12345
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Thông báo lỗi type của shipping_address</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra sai kiểu dữ liệu của shipping_address.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="181.5" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Gọi GET /api/checkout thay POST</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/checkout (thay vì POST)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>GET /api/checkout không có route GET; với Express hiện tại sẽ rơi vào HTTP 404 Not Found.</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không mô tả hành vi khi gọi sai HTTP method - đây là hành vi mặc định của framework/router, không phải yêu cầu nghiệp vụ được đặc tả. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="37" ht="111.75" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Race condition - 2 request checkout đồng thời cùng 1 user</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body (gửi đồng thời 2 lần): {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời (song song) 2 request POST /api/checkout từ cùng 1 user, cùng giỏ hàng
 2. GET /api/orders/my-orders kiểm tra số đơn hàng được tạo</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Hai request đồng thời có thể tạo hai order riêng nếu đều INSERT thành công.</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="I37" s="16" t="n"/>
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>Test case để phát hiện duplicate order. AI dễ bỏ sót vì đây là hành động diễn ra đồng thời thường AI không thể suy ra đầy đủ chỉ từ đặc tả do trong đặc tả thường chỉ miêu tả yêu cầu đơn lẻ.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="69.75" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Giỏ hàng của user khác không bị ảnh hưởng khi checkout</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>2 user đã đăng nhập: user A và user B, cả 2 đều có sản phẩm trong giỏ hàng riêng.</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>User A: Header: Authorization: Bearer {{userToken}}
 User B: Header: Authorization: Bearer {{userTokenB}} (cần tài khoản phụ thứ 2)</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>1. User A và User B cùng thêm sản phẩm vào giỏ (POST /api/cart)
 2. User A checkout (POST /api/checkout)
 3. GET /api/cart bằng token của User B - kiểm tra giỏ hàng B còn nguyên</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>userCarts được lưu theo userId nên cart của User B dùng key riêng và không bị User A ghi đè.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="I38" s="16" t="n"/>
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>Test case để kiểm tra cách ly dữ liệu giữa người dùng. AI dễ bỏ sót vì đặc tả thường không mô tả.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>total_amount dạng số thập phân</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 99999.99, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount có phần thập phân</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>Checkout thành công do tiền vẫn có thể số thập phân</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="I39" s="16" t="n"/>
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>Test case để kiểm tra có chấp nhận số thập phân ở trường tổng tiền hay không. AI có thể bỏ sót vì đặc tả chỉ nói number và không nêu quy ước có được dùng số thực hay không.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="93" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Content-Type sai khi checkout</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Header: Content-Type: text/plain
 Body: total_amount=100000&amp;shipping_address=123ABC</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với Content-Type sai, body không phải JSON hợp lệ</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>bodyParser.json() chỉ parse JSON phù hợp; với Content-Type sai, req.body có thể không chứa các field mong đợi. Route phải validate trước INSERT</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="I40" s="16" t="n"/>
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>Test case cho input sai định dạng ở tầng HTTP. AI thường giả định client gửi đúng Content-Type theo đặc tả và bỏ sót hành vi gửi sai.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="63.75" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Gọi checkout liên tục nhiều lần trong thời gian ngắn (spam)</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"} (gửi 20 lần liên tiếp trong 1 giây)</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>1. Gửi 20 request POST /api/checkout liên tiếp rất nhanh (script loop, không phải người dùng thật bấm 20 lần)</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>Phải báo lỗi hoặc có cơ chế chống DoS</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="I41" s="16" t="n"/>
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>Test case để kiểm tra spam. AI sinh từ đặc tả thường tập trung từng request đơn lẻ hơn là tần suất cao hay test độ chống DoS.</t>
         </is>
@@ -6163,56 +6303,56 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="21.9090909090909" customWidth="1" style="1" min="1" max="1"/>
-    <col width="26.7272727272727" customWidth="1" style="1" min="2" max="2"/>
-    <col width="31" customWidth="1" style="1" min="3" max="3"/>
-    <col width="21.6363636363636" customWidth="1" style="1" min="4" max="4"/>
-    <col width="21.7272727272727" customWidth="1" style="1" min="5" max="5"/>
-    <col width="20.2727272727273" customWidth="1" style="1" min="6" max="6"/>
-    <col width="41.4090909090909" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9" customWidth="1" style="1" min="8" max="8"/>
-    <col width="22.1818181818182" customWidth="1" style="1" min="9" max="9"/>
+    <col width="21.9090909090909" customWidth="1" style="14" min="1" max="1"/>
+    <col width="26.7272727272727" customWidth="1" style="14" min="2" max="2"/>
+    <col width="31" customWidth="1" style="14" min="3" max="3"/>
+    <col width="21.6363636363636" customWidth="1" style="14" min="4" max="4"/>
+    <col width="21.7272727272727" customWidth="1" style="14" min="5" max="5"/>
+    <col width="20.2727272727273" customWidth="1" style="14" min="6" max="6"/>
+    <col width="41.4090909090909" customWidth="1" style="14" min="7" max="7"/>
+    <col width="9" customWidth="1" style="14" min="8" max="8"/>
+    <col width="22.1818181818182" customWidth="1" style="14" min="9" max="9"/>
     <col width="45.5818181818182" customWidth="1" style="2" min="10" max="10"/>
-    <col width="9" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="14" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -6222,51 +6362,51 @@
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="84" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Tạo category với tên hợp lệ</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Tạo category thành công. Status code: 201 Created. Response body trả về object category vừa tạo, gồm ít nhất "id" và "name" (ví dụ: {"id": 1, "name": "Điện thoại"}).</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6276,51 +6416,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Tạo category với tên trống (empty string)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6330,51 +6470,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Từ đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Tạo category với tên null</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": null}</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": null}</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6384,51 +6524,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Null cũng là một dạng 'không có giá trị' - áp dụng cùng đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Tạo category thiếu field name</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {}</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6438,24 +6578,24 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Thiếu hẳn field cũng vi phạm đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="184.5" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-05</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Tao category voi ten rat dai (boundary test, 1000 ky tu)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+          <t>Tạo category với tên rất dài (boundary test, 1000 ký tự)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
@@ -6463,26 +6603,26 @@
       <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
-Body: {"name": "A" x 1000 (chuoi 1000 ky tu)}</t>
+Body: {"name": "A" x 1000 (chuỗi 1000 ký tự)}</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>1. POST /api/categories voi ten 1000 ky tu
-2. Kiem tra response</t>
+          <t>1. POST /api/categories với tên 1000 ký tự
+2. Kiểm tra response</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>He thong xu ly on dinh, KHONG duoc tra loi 500. Chap nhan 1 trong 2 ket qua: (a) 201 Created neu he thong khong gioi han do dai, hoac (b) 400 Bad Request neu he thong co gioi han.</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>200 OK - He thong chap nhan ten 1000 ky tu</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+          <t>Hệ thống xử lý ổn định, không được trả về 500. Chấp nhận 1 trong 2 kết quả: (a) 201 Created nếu hệ thống không giới hạn độ dài, hoặc (b) 400 Bad Request nếu hệ thống có giới hạn.</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>200 OK – Hệ thống chấp nhận tên 1000 ký tự.</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6492,51 +6632,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Test case boundary cho do dai ten. He thong tra 200 OK thay vi 400/501.</t>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Test case boundary cho độ dài tên. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="7" ht="159.75" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-06</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Tạo category với tên chỉ có khoảng trắng</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "   "}</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "   "
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6546,50 +6686,50 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ có trim khoảng trắng trước khi kiểm tra rỗng hay không, nhưng theo em suy luận khoảng trắng cũng đồng nghĩa với không có tên danh mục, nên em sẽ sửa kết quả từ chấp nhận tên sang từ chối tạo category.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="130.5" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-07</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Tạo category với tên trùng với category đã có</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Đã có category "Điện thoại".</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "Điện thoại" (da ton tai)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên phải unique. Status code: 409 Conflict (hoặc 400 Bad Request nếu hệ thống dùng chung cơ chế validation error).</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 409 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6599,51 +6739,51 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Đặc tả không yêu cầu tên category phải unique nhưng theo em tên danh mục nên là unique, em sẽ đổi kết quả từ cho phép tạo sang từ chối. </t>
         </is>
       </c>
     </row>
     <row r="9" ht="97.5" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-01</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Tạo category với tên chứa ký tự đặc biệt</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện &lt;thoại&gt; &amp; Phụ kiện"}</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên chứa ký tự đặc biệt
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên không chứa ký tự đặc biệt nguy hiểm (HTML/script injection). Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6653,49 +6793,49 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không nói về việc danh mục có được chứa ký tự đặc biệt hay không, nhưng theo em thì không nên, nên em sẽ đổi kết quả từ cho phép tạo sang từ chối tạo.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="69.75" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-ST-01</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Xem danh sách category - có category</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có ít nhất 1 category.</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/categories</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Trả về danh sách category. Status code: 200 OK. Response body là một mảng các object category (ví dụ: [{"id":1,"name":"Điện thoại"}, ...]).</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6705,49 +6845,49 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xem'.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="55.5" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-ST-02</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Xem danh sách category - không có category nào</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Không có category nào.</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/categories</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Trả về danh sách rỗng. Status code: 200 OK. Response body là mảng trống ([]), không phải null.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6757,51 +6897,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xem' nhưng trường hợp rỗng.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="84" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-ST-03</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Xóa category thành công</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id
 2. GET /api/categories để verify</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Xóa thành công. Category không còn trong danh sách. Status code: 204 No Content (theo convention REST phổ biến cho DELETE; 200 OK cũng có thể chấp nhận nếu backend trả kèm message).</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 GET: 200 OK; B3 DELETE: 200 OK - BUG: kỳ vọng 204 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6811,50 +6951,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xóa'.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="97.5" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-08</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Xóa category không tồn tại</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. ID không tồn tại.</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Hệ thống trả lỗi 404</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 404 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6864,51 +7004,51 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ nhưng em nghĩ hệ thống phải thông báo lỗi thay vì xác định thành công, nên em chuyển kết quả từ phân vân 2 trạng thái sang hệ thống phải trả lỗi.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-ST-04</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Sửa category - thay đổi tên</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên mới
 2. GET /api/categories để verify</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Sửa thành công. Tên mới được cập nhật. Status code: 200 OK. Response body trả về object category đã cập nhật (ví dụ: {"id":1,"name":"Tên mới"}).</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>B1 PUT: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6918,50 +7058,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="15" ht="84" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-DP-09</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Sửa category với tên trống</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên trống</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>Từ chối sửa. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6971,35 +7111,35 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>Đúng với đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="16" ht="111.75" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-ST-05</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Luồng hoàn chỉnh: Tạo -&gt; Xem -&gt; Xóa -&gt; Xem</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Chưa có category "Test Category".</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Test Category"}</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "Test Category"
 2. GET /api/categories - xác nhận có
@@ -7007,17 +7147,17 @@
 4. GET /api/categories - xac nhan không còn</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Tạo thành công (POST → 201) → Xuất hiện trong danh sách (GET → 200, có category) → Xóa thành công (DELETE → 204) → Không còn trong danh sách (GET → 200, không có category).</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK; B3 DELETE: 200 OK; B4 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7027,50 +7167,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>Luồng Tạo-&gt;Xem-&gt;Xóa-&gt;Xem đúng phạm vi 'Thêm/Xem/Xóa' của đặc tả</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55.5" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-02</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Tạo category khi chưa đăng nhập (không có token)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories KHÔNG gửi token</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7080,50 +7220,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="84" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-03</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Tạo category với token không hợp lệ</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Người dùng có token nhung token không hợp lệ.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;invalid_token&gt;
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với invalid_token</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7133,50 +7273,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="84" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-04</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Tạo category với token giả mạo (sai chữ ký)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã bị sửa đổi.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;tampered_token&gt;
 Body: {"name": "Category giả"}</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tampered_token</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token không hợp lệ (sai chữ ký). Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7186,50 +7326,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="97.5" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-05</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Tạo category với token hết hạn</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã hết hạn.</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;expired_token&gt;
 Body: {"name": "Category hết hạn"}</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với expired_token</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token hết hạn. Status code: 401 Unauthorized. LƯU Ý: cần tạo token hết hạn trước khi test.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7239,50 +7379,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="97.5" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-06</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Tạo category với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với user_token</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token hợp lệ nhưng role != "admin". Spec nói rõ: phải kiểm tra role = "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7292,50 +7432,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả phải kiểm tra role='admin', không chỉ kiểm tra có token.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="84" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-07</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Xóa category với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id với user_token</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Từ chối xóa category. Role != "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7345,49 +7485,49 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả phải kiểm tra role='admin', không chỉ kiểm tra có token.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="111.75" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-08</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>GET /api/categories không có token</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Không gửi header Authorization</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/categories KHÔNG gửi token</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>Từ chối truy cập. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 401 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7397,49 +7537,49 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>Dù đặc tả không nói rõ, nhưng theo em GET cũng cần token + role admin. Suy ra test case AI tạo rahợp lý.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="126" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-09</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>GET /api/categories với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/categories với user_token</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Từ chối xem danh sách category. Role != "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7449,50 +7589,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>Dù đặc tả không nói rõ, nhưng theo em GET cũng cần token + role admin. Suy ra test case AI tạo ra hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="84" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>GET /api/categories trả về danh sách dạng mảng (array)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>Response phải trả về một mảng (array), không phải object hay string. Mảng có thể trống hoặc có phần tử tùy dữ liệu hiện có, miễn đúng kiểu array.</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7502,50 +7642,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra schema cơ bản (mảng). Suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="55.5" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>GET /api/categories trả về mảng rỗng khi không có category</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Không có category nào.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>1. GET /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Response trả về mảng rỗng chính xác là [] (không phải null, không phải object rỗng {}).</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7555,51 +7695,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>Kiểm tra schema cơ bản (mảng). Suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="84" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>POST /api/categories thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Category mới"}</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên hợp lệ
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>Response thành công phải có status 201 Created (convention chuẩn REST cho hành động tạo mới thành công; 200 OK có thể chấp nhận nếu backend không tuân thủ chuẩn tuyệt đối).</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7609,51 +7749,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>Thành công thì trả về 2xx, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="28" ht="84" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-04</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>POST /api/categories thất bại (tên trống) trả về 4xx</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên trống
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Response lỗi phải có status 400 Bad Request. Không được trả về 2xx khi dữ liệu không hợp lệ.</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7663,51 +7803,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>Từ chối khi tên rỗng phải là 4xx - test case hợp lý, khớp với yêu cầu 'tên bắt buộc' của đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="111.75" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-05</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>POST /api/categories thành công có cấu trúc response hợp lệ</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Category mới"}</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>Response thành công phải có cấu trúc JSON hợp lệ, tối thiểu gồm field "id" và "name" (ví dụ: {"id": 1, "name": "Category mới"}). LƯU Ý: tên field là SUY ĐOÁN, không trích từ tài liệu, cần đối chiếu response thực tế khi thực thi.</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7717,51 +7857,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>Tên field cụ thể trong response không được liệt kê ở đặc tả nhưng vẫn phải test cấu trúc JSON nên test case hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="30" ht="84" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-06</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>DELETE /api/categories/:id thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>Response thành công phải có status 204 No Content (đồng nhất với TC-FR14-ST-03; 200 OK cũng có thể chấp nhận nếu backend trả kèm message).</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 204 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7771,51 +7911,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>Thành công thì trả về 2xx, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="31" ht="97.5" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-07</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>DELETE /api/categories/:id thất bại (id không tồn tại) trả về 4xx</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. ID không tồn tại.</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/99999
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>Hệ thống trả lỗi 404 Not Found.</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 404 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7825,51 +7965,51 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ nhưng em nghĩ hệ thống phải thông báo lỗi thay vì xác định thành công, nên em chuyển kết quả từ phân vân 2 trạng thái sang hệ thống phải trả lỗi.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="84" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-08</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Response lỗi khi thiếu field name có cấu trúc báo lỗi</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với body rỗng
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Response phải báo lỗi với status 400 Bad Request và có cấu trúc JSON hợp lệ (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7879,51 +8019,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>Cấu trúc lỗi JSON hợp lệ khi thiếu field bắt buộc khớp yêu cầu 'tên bắt buộc'.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="84" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-09</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Sửa category thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>Response thành công phải có status 200 OK.</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7933,51 +8073,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="34" ht="84" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-10</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Sửa category thất bại (tên trống) trả về 4xx</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên trống
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Response lỗi phải có status 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7987,52 +8127,52 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="35" ht="126" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-ST-06</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Xóa category rồi tạo lại với tên giống - không bị trùng id</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category "Temp Category".</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Temp Category"}</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id của "Temp Category"
 2. POST /api/categories với tên "Temp Category" mới
 3. GET /api/categories - xác nhận chỉ có 1 với id mới</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Xóa thành công. Tạo lại với id mới. Chỉ có 1 category "Temp Category". Id mới phải khác id cũ (do id thường là auto-increment hoặc UUID, không tái sử dụng id đã xóa).</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="19" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8042,51 +8182,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>Không quy định trong đặc tả, nhưng theo suy luận của em, test case AI sinh ra hợp lý. Kiểm tra được tính unique của danh mục sẽ được xác định đúng hay không.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="111.75" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-10</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Token user bình thường (role != admin) thực thi cả POST và DELETE</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"name": "Test"}</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với user_token
 2. DELETE /api/categories/:id với user_token</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Cả POST và DELETE đều bị từ chối. Token hợp lệ nhưng role != "admin". Status code: 403 Forbidden cho cả 2 request.</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 DELETE: 200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8096,56 +8236,56 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="105.75" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Tạo category với field thừa không được định nghĩa</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Sách", "description": "Mô tả không nằm trong spec"}</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với body có field 'description' thừa ngoài spec</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Hệ thống bỏ qua field "description" không được định nghĩa trong spec, chỉ lưu field "name"; tạo category thành công với status 201 Created (convention phổ biến: ignore unknown fields thay vì báo lỗi 400, trừ khi hệ thống dùng strict schema validation).</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
       <c r="I37" s="12" t="n"/>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>AI bỏ sót vì prompt yêu cầu sinh test case theo 'domain partition trên từng parameter' được liệt kê trong đặc tả; AI chỉ suy luận trên các field đã được định nghĩa, không tự nghĩ đến trường hợp field không nằm trong đặc tả) - đây là giới hạn phạm vi suy luận của model khi bám sát input đã cho.</t>
         </is>
@@ -8153,50 +8293,50 @@
       <c r="K37" s="13" t="n"/>
     </row>
     <row r="38" ht="97.5" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Race condition - 2 admin tạo category cùng tên đồng thời</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập (2 phiên/token khác nhau nếu có thể). Chưa có category tên 'Sách'.</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body (gửi đồng thời 2 lần): {"name": "Sách"}</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời 2 request POST /api/categories cùng tên 'Sách'
 2. GET /api/categories kiểm tra có bao nhiêu category tên 'Sách' được tạo</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Do tên category phải unique (theo TC-FR14-DP-07), khi 2 request đồng thời cùng tên "Sách" được gửi, chỉ 1 request thành công (201 Created), request còn lại phải bị từ chối (409 Conflict hoặc 400 Bad Request). Không được có 2 category cùng tên "Sách" sau khi chạy xong.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
       <c r="I38" s="12" t="n"/>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>AI bỏ sót vì test case AI sinh ra theo luồng tuần tự (1 request - 1 response tại một thời điểm), không có khả năng/không được yêu cầu mô phỏng tình huống đồng thời. Đây là hạn chế đặc trưng của việc sinh test case từ đặc tả tĩnh: AI không tự suy luận về các vấn đề vận hành thực tế nếu prompt không yêu cầu rõ ràng.</t>
         </is>
@@ -8204,49 +8344,49 @@
       <c r="K38" s="13" t="n"/>
     </row>
     <row r="39" ht="117" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>Gọi HTTP method không được hỗ trợ (PATCH)</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần test.</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>1. PATCH /api/categories/:id (method không được liệt kê trong API spec - chỉ có GET/POST/PUT/DELETE)</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>Hệ thống trả về 404 Not Found (phổ biến hơn 405 Method Not Allowed đối với các API đơn giản dùng framework như Express, vốn không định nghĩa route cho PATCH nên coi như route không tồn tại). Nếu hệ thống có OPTIONS/route-level method negotiation thì có thể trả 405 kèm header Allow.</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="I39" s="12" t="n"/>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI generate test case dựa trên các HTTP method được liệt kê tường minh trong đặc tả (GET/POST/PUT/DELETE), không tự nghĩ đến việc test các method KHÔNG được định nghĩa trong đặc tả. Đây là đặc điểm của model: thiên về mặt theo đúng đặc tả, thiếu tư duy mặt ngược lại thì như nào.</t>
         </is>
@@ -8254,50 +8394,50 @@
       <c r="K39" s="13" t="n"/>
     </row>
     <row r="40" ht="160.5" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Content-Type sai khi tạo category</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Header: Content-Type: text/plain
 Body: name=Sach</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với Content-Type sai, body không phải JSON hợp lệ</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>Hệ thống nên trả về 400 Bad Request với thông báo lỗi rõ ràng (ví dụ: "Invalid JSON body" hoặc "Unsupported Content-Type"), KHÔNG được trả 500 Internal Server Error. Nếu thực thi cho ra 500 thì đây là một bug cần report.</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="I40" s="12" t="n"/>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI tập trung sinh test case validate nội dung body theo đúng domain partition được yêu cầu trong prompt, chứ không kiểm tra các thuộc tính protocol-level như HTTP header Content-Type. Đây là hạn chế do phạm vi prompt (chỉ yêu cầu domain partition/state/security/schema) không bao gồm rõ ràng validation ở tầng request header.</t>
         </is>
@@ -8305,50 +8445,50 @@
       <c r="K40" s="13" t="n"/>
     </row>
     <row r="41" ht="124.5" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Tên category chứa ký tự Unicode có dấu / emoji</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Đồ gia dụng 🏠"}</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên chứa tiếng Việt có dấu và emoji
 2. GET /api/categories kiểm tra tên lưu và trả về có đúng nguyên gốc không</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>Hệ thống lưu và trả về đúng nguyên vẹn chuỗi UTF-8 (tiếng Việt có dấu và emoji), không bị lỗi encoding, không bị cắt ký tự. Status code: 201 Created khi tạo thành công.</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
       <c r="I41" s="12" t="n"/>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI ít khi tự sinh test case về encoding/Unicode edge case trừ khi được yêu cầu cụ thể trong prompt - đây là đặc điểm kỹ thuật của hệ thống, thường không được nêu rõ trong đặc tả chức năng, nên AI thiên về test theo đặc tả hơn là các edge case kỹ thuật/encoding.</t>
         </is>

--- a/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
+++ b/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
@@ -80,6 +80,13 @@
       <charset val="134"/>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -239,17 +246,14 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -278,6 +282,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -616,21 +626,18 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
@@ -639,37 +646,37 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyAlignment="1">
@@ -684,74 +691,77 @@
     <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -790,38 +800,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1342,38 +1339,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="30" customWidth="1" style="14" min="1" max="1"/>
-    <col width="52.3636363636364" customWidth="1" style="14" min="2" max="2"/>
-    <col width="36.8181818181818" customWidth="1" style="14" min="3" max="3"/>
-    <col width="15" customWidth="1" style="14" min="4" max="6"/>
-    <col width="40" customWidth="1" style="14" min="7" max="7"/>
-    <col width="9" customWidth="1" style="14" min="8" max="16384"/>
+    <col width="30" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15" customWidth="1" style="1" min="3" max="3"/>
+    <col width="15" customWidth="1" style="1" min="4" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" style="1" min="7" max="7"/>
+    <col width="9" customWidth="1" style="1" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>HW06 API Testing — Test Summary Report</t>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>HW06 API Testing - Test Summary Report</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>Student ID: 23127031 | Date: 2026-08-24 01:24</t>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Student ID: 23127031 | Date: 2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -1386,7 +1385,7 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1396,7 +1395,7 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -1406,39 +1405,37 @@
         </is>
       </c>
       <c r="B7" s="25" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Assertions executed</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="B8" s="26" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Assertions passed</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="B9" s="26" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Assertions failed</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>48.1%</t>
-        </is>
+      <c r="B10" s="26" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -1447,8 +1444,10 @@
           <t>Pass rate</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
-        <v>14</v>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1457,90 +1456,129 @@
           <t>Bugs found</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B12" s="25" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>Critical bugs</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Major bugs</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
+          <t>Critical bugs</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
           <t>Major bugs</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="B15" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Minor bugs</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B16" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>Detailed Results by API</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>Detailed Results by API</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Assertions</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Bugs Found</t>
         </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Test Cases</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1555,19 +1593,19 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1582,245 +1620,214 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E21" s="25" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="G21" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Category CRUD</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>FR-14</t>
         </is>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="28" t="n">
         <v>51</v>
       </c>
-      <c r="D22" s="25" t="n">
-        <v>23</v>
-      </c>
-      <c r="E22" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="G22" s="25" t="n">
-        <v>4</v>
+      <c r="D22" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n">
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n">
         <v>151</v>
       </c>
-      <c r="D23" s="27" t="n">
-        <v>77</v>
-      </c>
-      <c r="E23" s="27" t="n">
-        <v>42</v>
-      </c>
-      <c r="F23" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>14</v>
-      </c>
+      <c r="D23" s="29" t="n">
+        <v>120</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="20" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>Bug Severity Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>Issue Numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>#166, #168, #169, #170, #171, #174</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>#166, #168, #169, #170, #171, #174, #175</t>
+          <t>#167, #172, #173, #179</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>#167, #172, #173, #179</t>
+          <t>#176, #177, #178</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>#176, #177, #178</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="C30" s="27" t="n"/>
+      <c r="B29" s="30" t="n">
+        <v>13</v>
+      </c>
+      <c r="C29" s="21" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>AI Audit Summary</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>AI Audit Summary</t>
-        </is>
-      </c>
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="B34" s="30" t="n">
-        <v>100</v>
-      </c>
-      <c r="C34" s="30" t="inlineStr">
-        <is>
-          <t>Test case dung, co ket qua ro rang</t>
-        </is>
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>INVALID</t>
-        </is>
-      </c>
-      <c r="B35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>Test case bi bo di vi AI hallucination</t>
-        </is>
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="B36" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" s="30" t="inlineStr">
-        <is>
-          <t>Test case can bo sung them</t>
-        </is>
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>EXT (no label)</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>EXT (no label)</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>Test case extension tu tay them</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B38" s="31" t="n">
+      <c r="B37" s="21" t="n">
         <v>120</v>
       </c>
-      <c r="C38" s="31" t="inlineStr"/>
+      <c r="C37" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1841,1716 +1848,1716 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="28.0909090909091" defaultRowHeight="14"/>
   <cols>
-    <col width="15.6363636363636" customWidth="1" style="14" min="1" max="1"/>
-    <col width="28.0909090909091" customWidth="1" style="14" min="2" max="6"/>
-    <col width="37.0636363636364" customWidth="1" style="14" min="7" max="7"/>
-    <col width="35.4909090909091" customWidth="1" style="14" min="8" max="8"/>
-    <col width="28.0909090909091" customWidth="1" style="14" min="9" max="9"/>
-    <col width="35" customWidth="1" style="14" min="10" max="10"/>
-    <col width="28.0909090909091" customWidth="1" style="14" min="11" max="16384"/>
+    <col width="15.6363636363636" customWidth="1" style="1" min="1" max="1"/>
+    <col width="28.0909090909091" customWidth="1" style="1" min="2" max="6"/>
+    <col width="37.0636363636364" customWidth="1" style="1" min="7" max="7"/>
+    <col width="35.4909090909091" customWidth="1" style="1" min="8" max="8"/>
+    <col width="28.0909090909091" customWidth="1" style="1" min="9" max="9"/>
+    <col width="35" customWidth="1" style="1" min="10" max="10"/>
+    <col width="28.0909090909091" customWidth="1" style="1" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="55.5" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Happy path: email và password khớp tài khoản</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>200 OK, trả về JWT token và thông tin user</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I2" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>AI dựa trực tiếp từ đặc tả FR-02. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password sai</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"WrongPass999"}</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Password không khớp -&gt; đăng nhập thất bại, AI có căn cứ trực tiếp dựa vào đặc tả em cung cấp. Mã lỗi cụ thể chưa được nêu trong đặc tả nên AI ghi cần xác định thêm, nhưng kết quả là thất bại được xác định đúng</t>
         </is>
       </c>
     </row>
     <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password trống (empty string)</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: ""</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":""}</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Password rỗng vẫn là 1 giá trị không khớp mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="5" ht="55.5" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password null</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: null</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":null}</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Password giá trị null là giá trị không khớp với mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="6" ht="55.5" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-05</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password sai kiểu dữ liệu (number)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: 123456</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":123456}</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Password giá trị số là giá trị không khớp với mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="7" ht="84" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-06</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password quá dài (56 ký tự)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA"</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"&lt;56 chars&gt;"}</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Độ dài không khớp mật khẩu thật. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="8" ht="55.5" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-07</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Email đúng, password chứa ký tự đặc biệt (không khớp)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại trong hệ thống</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "P@$$w!r#d"</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"test@eshop.com","password":"P@$$w!r#d"}</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại (password không khớp). HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Mật khẩu toàn là ký tự đặc biệt nhưng vẫn không khớp với mật khẩu thật nên đăng nhập thất bại. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="9" ht="55.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-08</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Email không tồn tại, password đúng format</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Tài khoản với email này không tồn tại</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>email: "nonexistent@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"nonexistent@eshop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Email không tồn tại -&gt; không khớp tài khoản nào -&gt; thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="55.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-09</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Email trống (empty), password đúng</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Không có tài khoản với email trống</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>email: ""
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Email trống là email không tồn tại nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="55.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-10</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Email null, password đúng</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Không có tài khoản với email null</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>email: null
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":null,"password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Email null là email không tồn tại nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="55.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-11</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Email sai kiểu dữ liệu (number), password đúng</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Không có tài khoản với email là số</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>email: 12345
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":12345,"password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Email toàn số là email không tồn tại, không đúng format nên đăng nhập cũng thất bại, đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-DP-12</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Cả email và password đều trống</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Không có điều kiện trước</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>email: ""
 password: ""</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"","password":""}</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Cả email và password đều rỗng, đăng nhập thất bại. Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="14" ht="55.5" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-01</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 1 - bộ đếm tăng lên 1</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đang hoạt động, chưa có lần sai nào [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass1"</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass1"}</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 1 (&lt; 3, chưa khóa).</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="15" ht="55.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-02</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 2 - bộ đếm tăng lên 2</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đã có 1 lần sai (bộ đếm = 1) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass2"</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass2"}</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 2 (&lt; 3, chưa khóa).</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="16" ht="55.5" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-03</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai lần 3 - kích hoạt khóa 30 giây</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại, đã có 2 lần sai liên tiếp (bộ đếm = 2) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPass3"</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPass3"}</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm = 3 (&gt;= 3 -&gt; khóa 30 giây).</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-04</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập đúng mật khẩu trong thời gian khóa</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Tài khoản đang bị khóa (&lt; 30 giây) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "Locktest123!"</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"Locktest123!"}</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 403 Forbidden, Response: {"error": "Tài khoản đã bị khóa. Vui lòng thử lại sau."} (kiểm tra thời gian khóa được thực hiện TRƯỚC khi so khớp mật khẩu, nên dù mật khẩu đúng vẫn bị chặn ở bước khóa). Tài khoản vẫn bị khóa.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="18" ht="55.5" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-05</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai mật khẩu trong thời gian khóa</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Tài khoản đang bị khóa (&lt; 30 giây) [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPassX"</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPassX"}</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 403 Forbidden, Response: {"error": "Tài khoản đã bị khóa. Vui lòng thử lại sau."}. Tài khoản vẫn bị khóa.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="19" ht="55.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-06</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập đúng mật khẩu ngay sau khi hết 30 giây khóa</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Tài khoản vừa hết thời gian khóa 30 giây [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "Locktest123!"</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"Locktest123!"}</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công. 200 OK + JWT. Bộ đếm reset về 0.</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="20" ht="69.75" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-ST-07</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập sai mật khẩu ngay sau khi hết khóa</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Tài khoản vừa hết thời gian khóa 30 giây [Tài khoản locktest@eshop.com - PHẢI tạo trước bằng POST /api/register, KHÔNG dùng chung với test@eshop.com]</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongPassAfterUnlock"</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"locktest@eshop.com","password":"WrongPassAfterUnlock"}</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Bộ đếm bắt đầu lại từ 1.</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Theo suy luận cùng với từ đặc tả suy ra thì test case valid, sau khi mở khóa thì bộ đếm reset về 0, tiếp tục sai nên +1</t>
         </is>
       </c>
     </row>
     <row r="21" ht="75.75" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-01</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>SQL Injection ở trường email</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>email: ' OR 1=1 --
 password: "anypassword"</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "' OR 1=1 --", "password": "anypassword"}</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Hệ thống xử lý đúng (parameterized query). Không lộ SQL/stack trace.</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="76.5" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-02</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>SQL Injection ở trường password</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: ' OR 1=1 --</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "test@eshop.com", "password": "' OR 1=1 --"}</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Hệ thống xử lý đúng (parameterized query). Không lộ SQL/stack trace.</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="55.5" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-03</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>SQL Injection UNION-based - trích xuất thông tin DB</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>email: ' UNION SELECT table_name,null FROM information_schema.tables --
 password: "x"</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "&lt;SQL injection query&gt;", "password": "x"}</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Không lộ thông tin cấu trúc DB.</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Tương tự, mở rộng dạng UNION-based, Có căn cứ dựa vào đặc tả SEC-05 (parameterized query) - không được để SQL injection thành công..</t>
         </is>
       </c>
     </row>
     <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-04</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra thông báo lỗi chung - email không tồn tại</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Tài khoản "wronguser@eshop.com" không tồn tại</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>email: "wronguser@eshop.com"
 password: "WrongPass123"</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "wronguser@eshop.com", "password": "WrongPass123"}</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Thông báo lỗi chung, không để lộ "email không tồn tại".</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'không để lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="55.5" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-05</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra thông báo lỗi chung - email đúng, mật khẩu sai</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Tài khoản "test@eshop.com" tồn tại</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email": "test@eshop.com", "password": "WrongPass999"}</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}. Thông báo lỗi chung. Không để lộ "mật khẩu sai".</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I25" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'không để lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="118.5" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-06</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra không có sự khác biệt thời gian phản hồi giữa email tồn tại và không tồn tại (chống User Enumeration qua timing attack)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường; đã có tài khoản test@eshop.com</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Case A: email: "test@eshop.com", password: "WrongPass999"
 Case B: email: "noaccount@eshop.com", password: "WrongPass999"</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>1. Gửi lần lượt 2 request POST /api/login với Case A và Case B
 2. Đo thời gian phản hồi (response time) của mỗi request
 3. So sánh chênh lệch thời gian giữa 2 case</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Thời gian phản hồi giữa 2 case không chênh lệch đáng kể (ví dụ &lt; 50-100ms), tránh lộ thông tin email có tồn tại hay không qua timing side-channel. Cả 2 case đều trả về HTTP 401 Unauthorized, {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra timing attack - vì code hiện có 2 nhánh xử lý khác nhau (user không tồn tại trả lỗi ngay; user tồn tại phải so sánh password) nên thời gian xử lý có thể khác biệt và bị lợi dụng để dò tìm email tồn tại trong hệ thống. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="87" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-07</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra response không lộ SQL error hoặc stack trace</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Hệ thống đang hoạt động bình thường</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "any"</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Gửi request với dữ liệu sai
 3. Kiểm tra toàn bộ response body</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Response không chứa: lỗi SQL, stack trace, tên bảng, tên cột, đường dẫn file server. Chỉ trả về lỗi chung. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Dựa vào SEC-05 + 'không lộ chi tiết nguyên nhân'.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="186.75" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SEC-08</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra response/JWT không lộ thông tin nhạy cảm (password) của user</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Tài khoản test@eshop.com tồn tại</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login với thông tin hợp lệ
 2. Nhận response 200 OK
 3. Kiểm tra field "user" trong response body và payload JWT</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Field "user" trong response và payload JWT KHÔNG được chứa field "password" (dù ở dạng plaintext hay hash). Chỉ chứa các field an toàn như id, name, email, role.</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra rò rỉ dữ liệu nhạy cảm. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="29" ht="55.5" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra response thành công có field "token" và "user"</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công với tai khoan hợp lệ</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Nhận response 200 OK
 3. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Response phải chứa: trường "token" (string, khác null) và trường "user" (object, khác null).</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'trả về token và user'.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra trường "token" là string</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy giá trị field "token"
 3. Kiểm tra kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Field "token" phải là string, không được là null, number, object hay array. </t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H30" s="20" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Dùng để kiểm tra kiểu dữ liệu cơ bản của field đã được xác nhận tồn tại. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra trường "user" là object</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy giá trị field "user"
 3. Kiểm tra kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Field "user" phải là object, không được là null, string, number hay array.</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Dùng để kiểm tra kiểu dữ liệu cơ bản của field đã được xác nhận tồn tại. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="55.5" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-04</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT có cấu trúc 3 phần (header.payload.signature)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, nhận được JWT token</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy token từ response
@@ -3558,55 +3565,55 @@
 4. Kiểm tra số phần</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Token phải có đúng 3 phần: header, payload, signature. Nếu không -&gt; thất bại</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I32" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra cấu trúc JWT chuẩn (3 phần) - đúng với mọi JWT hợp lệ. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="69.75" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-05</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT header la base64 JSON hợp lệ</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần header (phần đầu tiên)
@@ -3614,55 +3621,55 @@
 4. Parse JSON</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Header sau decode phải là JSON hợp lệ, chứa tối thiểu 2 field: "alg" (thuật toán ký, mặc định "HS256" do thư viện jsonwebtoken khi không chỉ định algorithm) và "typ" ("JWT").</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H33" s="20" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>JWT hợp lệ luôn phải decode được header. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="69.75" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-06</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT payload la base64 JSON hợp lệ</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần payload (phần thứ hai)
@@ -3670,386 +3677,386 @@
 4. Parse JSON</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Payload sau decode phải là JSON hợp lệ, chứa field "id" (id user) và "role". Field "iat" (issued at) được thư viện tự thêm. Lưu ý: KHÔNG có field "exp" (hết hạn) vì jwt.sign() được gọi không kèm option expiresIn -&gt; token không bao giờ hết hạn (rủi ro bảo mật, cần ghi vào bug report).</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Payload luôn phải decode được. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="55.5" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-07</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT signature không rỗng</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công, JWT co 3 phan</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy phần signature (phần cuối cùng)
 3. Kiểm tra độ dài</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Signature phải có độ dài &gt; 0, không được rỗng. Thuật toán ký mặc định là HS256 (HMAC-SHA256) vì jwt.sign() không truyền option algorithm.</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Chữ ký JWT không được rỗng - tính chất cơ bản của JWT. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-SCHEMA-08</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra JWT đúng định dạng base64url</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thành công</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>email: "test@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Lấy token từ response
 3. Kiểm tra ký tự trong token</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>JWT chỉ chứa ký tự base64url: A-Z, a-z, 0-9, -, _, ".": phân cách 3 phần</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I36" s="19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Định dạng base64url - tính chất cơ bản của JWT. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="195" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Email phân biệt hoa/thường</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>email: "Test@EShop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":"Test@EShop.com","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"} (vì so sánh email trong SQL phân biệt hoa/thường, "Test@EShop.com" khác "test@eshop.com" nên không tìm thấy user).</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Cần test thêm hệ thống có phân biệt chữ hoa, chữ thường hay không. Do tính chất bảo mật của email và password nên phân biệt chữ hoa, chữ thường. Lý do AI bỏ sót theo em nghĩ là do prompt của em chỉ yêu cầu domain partitioning cho field email một cách chung chung, không có gợi ý cụ thể, nên AI thường chỉ quan tâm đúng các trường hợp email đúng/sai định dạng mà không test các case nhạy cảm, chi tiết hơn như phân biệt chữ hoa với chữ thường</t>
         </is>
       </c>
     </row>
     <row r="38" ht="207.75" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Email có khoảng trắng đầu/cuối</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>email: " test@eshop.com "
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login
 2. Body: {"email":" test@eshop.com ","password":"Test1234!"}</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Đăng nhập thất bại. HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"} (email có khoảng trắng đầu/cuối không được trim trước khi so khớp trong DB, nên " test@eshop.com " khác với "test@eshop.com").</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H38" s="18" t="inlineStr">
+      <c r="H38" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Test case kiểm tra hệ thống có tự động trim khoảng trắng ở email trước khi xử lý hay không đặc tả không nêu rõ điều này. Lý do AI bỏ sót: prompt gốc chỉ yêu cầu domain partition theo định dạng email hợp lệ/không hợp lệ một cách chung chung, không đề cập input nhiễu như khoảng trắng thừa - đây là input edge-case thực tế thường gặp mà đặc tả không nêu, nên AI (chỉ dựa vào đặc tả) không tự sinh ra được.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="241.5" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Race condition - 2 request sai password gửi đồng thời</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Tài khoản locktest@eshop.com, bộ đếm đang = 0</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>email: "locktest@eshop.com"
 password: "WrongA" (request 1)
 password: "WrongB" (request 2, gửi gần như cùng lúc)</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời (song song, không chờ response) 2 request POST /api/login sai password
 2. Kiểm tra login_attempts cuối cùng qua GET /api/admin/users hoặc thử đăng nhập lại</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Bộ đếm tăng đúng cho cả 2 lần thất bại.</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>B1 POST: 500 Internal Server Error; B2 GET: 401 Unauthorized</t>
         </is>
       </c>
-      <c r="H39" s="18" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="inlineStr">
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý để phát hiện lỗi đồng thời tiềm ẩn. Lý do AI bỏ sót: AI sinh test case dựa trên đặc tả API (request/response tĩnh), không có khả năng suy luận về hành vi đồng  thời vì AI chỉ được cung cấp đặc tả API, không có prompt chi tiết hơn về hành động này. Đây là hạn chế đặc trưng khi sinh test case chỉ từ đặc tả mà không phân tích thực tế.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="234.75" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Content-Type sai (form-urlencoded thay vì JSON)</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Tài khoản tồn tại: test@eshop.com</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Header: Content-Type: application/x-www-form-urlencoded
 Body: email=test@eshop.com&amp;password=Test1234!</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login với Content-Type sai và body dạng form-encoded thay vì JSON</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Do body-parser chỉ parse JSON khi Content-Type là application/json, request dạng form-urlencoded sẽ có req.body rỗng ({}) -&gt; email/password đều undefined -&gt; DB không tìm thấy user khớp -&gt; HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H40" s="17" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý để kiểm tra khả năng chịu lỗi khi client gửi sai Content-Type - tình huống thực tế hay gặp. Lý do AI bỏ sót: AI thường giả định client luôn gửi đúng Content-Type theo đặc tả (application/json) khi sinh test case cho request body, không tự nghĩ ra kịch bản client gửi sai định dạng header vì đây là đặc tính của tầng HTTP/middleware (body-parser), nằm ngoài phạm vi đặc tả logic nghiệp vụ mà AI được cung cấp.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="409.5" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-FR02-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Email cực dài (tiềm năng DoS / buffer)</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Không có tài khoản nào khớp email này</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>email: "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa@eshop.com"
 password: "Test1234!"</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/login với email dài 5000+ ký tự</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Server không bị treo/crash: SQLite xử lý tham số dài bình thường qua parameterized query, không tìm thấy user khớp -&gt; HTTP 401 Unauthorized, Response: {"error": "Invalid email or password"}.</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý để kiểm tra khả năng chống chịu input bất thường/DoS tiềm ẩn. Lý do AI bỏ sót: đặc tả API không đề cập giới hạn độ dài field email, và AI khi sinh test theo domain partition thường chỉ xét các mốc độ dài hợp lý (email hợp lệ/không hợp lệ theo định dạng) chứ không chủ động nghĩ tới input lớn nhằm mục đích kiểm thử bảo mật/hiệu năng - đây đòi hỏi prompt chi tiết hơn là chỉ dựa theo đặc tả chức năng có sẵn.</t>
         </is>
@@ -4070,2219 +4077,2219 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="21.5454545454545" customWidth="1" style="14" min="1" max="1"/>
-    <col width="30.4545454545455" customWidth="1" style="14" min="2" max="2"/>
-    <col width="40" customWidth="1" style="14" min="3" max="3"/>
-    <col width="50" customWidth="1" style="14" min="4" max="4"/>
-    <col width="45" customWidth="1" style="14" min="5" max="5"/>
-    <col width="55" customWidth="1" style="14" min="6" max="6"/>
-    <col width="18" customWidth="1" style="14" min="7" max="7"/>
-    <col width="12" customWidth="1" style="14" min="8" max="8"/>
-    <col width="18.0909090909091" customWidth="1" style="14" min="9" max="9"/>
-    <col width="29.6363636363636" customWidth="1" style="14" min="10" max="10"/>
-    <col width="8" customWidth="1" style="14" min="11" max="16384"/>
+    <col width="21.5454545454545" customWidth="1" style="1" min="1" max="1"/>
+    <col width="30.4545454545455" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" customWidth="1" style="1" min="3" max="3"/>
+    <col width="50" customWidth="1" style="1" min="4" max="4"/>
+    <col width="45" customWidth="1" style="1" min="5" max="5"/>
+    <col width="55" customWidth="1" style="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="1" min="7" max="7"/>
+    <col width="12" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.0909090909091" customWidth="1" style="1" min="9" max="9"/>
+    <col width="29.6363636363636" customWidth="1" style="1" min="10" max="10"/>
+    <col width="8" customWidth="1" style="1" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="97.5" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Shipping address hợp lệ</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Thanh toán thành công. HTTP 200 OK, Response: {"message":"Checkout successful","orderId":&lt;id&gt;}.</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả, happy path bình thường.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Shipping address trống (empty string)</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": ""}</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": ""}</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói shipping_address có không được để trống hay không nhưng theo em shipping address không được để trống, suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Shipping address null</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": null}</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": null}</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói shipping_address có không được null hay không nhưng theo em shipping address không được để trống, suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Shipping address quá dài (500 ký tự)</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "&lt;500 char string&gt;"}</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "&lt;500 chars&gt;"}</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không quy định giới hạn độ dài cho shipping_address nhưng cũng cần test để tránh DoS.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="126" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Shipping address chứa ký tự đặc biệt (HTML/SQL)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "&lt;script&gt;alert(1)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "&lt;script&gt;alert(1)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Phải validate shipping_address</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không quy định nhưng theo em cần test xem hệ thống có escape hay không nên test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="69.75" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-01</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng có sản phẩm - thanh toán thành công</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có ít nhất 1 sản phẩm.</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Thanh toán thành công. HTTP 200 OK, Response: {"message":"Checkout successful","orderId":&lt;id&gt;}.</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="195.75" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-02</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng trống - không thể thanh toán</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống (không có sản phẩm).</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Giỏ hàng trống báo lỗi khi thanh toán </t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Dù đặc tả gốc không quy định nhưng cần test case "không thể thanh toán khi giỏ trống" </t>
         </is>
       </c>
     </row>
     <row r="9" ht="153.75" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-05</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng trống, total_amount client gửi khác 0</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống.</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 500000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 500000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="84" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-06</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - không chấp nhận giá trị client gửi</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 1, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 1, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-07</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - client gửi giá trị âm</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": -50000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": -50000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="69.75" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-08</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại total_amount - client gửi giá trị rất lớn</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 999999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout
 2. Header: Authorization: Bearer &lt;token&gt;
 3. Body: {"total_amount": 999999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Backend phải tự tính lại tổng tiền, không chấp nhận giá trị total_amount do client gửi' - áp dụng cho mọi giá trị client gửi, kể cả khi giỏ hàng trống (tổng = 0).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="55.5" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-03</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng bị xóa sau thanh toán thành công</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout -&gt; thanh toán thành công
 2. GET /api/cart (kiểm tra giỏ hàng)
 3. Hoặc checkout lần nữa</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng bị xóa sau khi thanh toán thành công</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Sau thanh toán thành công, giỏ hàng được xóa'.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="252" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-02</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Checkout khi chưa đăng nhập (không có token)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token hoặc token không hợp lệ.</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">
 1. KHÔNG gửi header Authorization
 2. Body: {"total_amount": 100000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized, Response: {"error":"Unauthorized"} khi không có token.</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Chỉ người dùng đã đăng nhập mới tiến hành thanh toán được'.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="84" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-04</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra order mới tạo có status ban đầu là "pending"</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":100000,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout, lấy orderId
 2. GET /api/orders/:id
 3. Kiểm tra status</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>order mới tạo phải có status pending.</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 404 Not Found</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Test case kiểm tra trạng thái khởi tạo của order, là điểm bắt đầu của state machine.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="97.5" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-ST-05</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Checkout khi giỏ hàng trống</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng trống (không có sản phẩm nào).</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 0, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận giỏ hàng trống
 2. POST /api/checkout
 3. GET /api/cart - kiểm tra giỏ hàng vẫn trống</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Không checkout được khi giỏ hàng trống</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ hệ thống có cho phép checkout khi giỏ hàng trống hay từ chối nhưng theo em nên từ chối.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-09</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>total_amount gửi giá trị null tường minh</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":null,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount: null
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Phải validate total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Test nếu gửi total_amount = null. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="18" ht="84" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-10</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>total_amount gửi kiểu boolean true thay vì number</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":true,"shipping_address":"123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount: true
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Phải validate kiểu total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra kiểu dữ liệu khác cho total_amount = boolean, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-11</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount thấp hơn thực tế</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 10000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = 10000
 3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý: kiểm tra backend có tin tưởng total_amount thấp hơn giá trị thực từ client hay không. Đây là kịch bản price manipulation thực tế và mở rộng domain partition cho total_amount.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-12</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount cao hơn thực tế</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 999999999, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = 999999999
 3. Kiểm tra order được tạo với tổng tính từ giỏ hàng</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi, backend tự tính lại</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý: kiểm tra backend có chấp nhận total_amount cao hơn giá trị thực hay không. Dù ít gây thiệt hại trực tiếp hơn giá thấp, backend vẫn phải không tin giá trị do client gửi để tránh sai lệch dữ liệu.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="237.75" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-13</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Backend tự tính lại - client gửi total_amount sai kiểu (string)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 2 sản phẩm, tổng giá trị 150000.</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": "abc", "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/cart - xác nhận tổng = 150000
 2. POST /api/checkout với total_amount = "abc"
 3. Kiểm tra xử lý của hệ thống</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Phải validate kiểu total_amount và báo lỗi</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Trường hợp sai kiểu dữ liệu (string thay vì number) dù đặc tả không quy định, nhưng vẫn cần thiết trong test case.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="153.75" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-03</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>XSS trong shipping_address - mã HTML/Script</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "&lt;script&gt;alert(document.cookie)&lt;/script&gt;"}</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa &lt;script&gt;alert(document.cookie)&lt;/script&gt;
 2. Nếu thanh toán thành công, GET /api/orders hoặc endpoint hiển thị địa chỉ
 3. Kiểm tra địa chỉ được escape an toàn</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Phải có escape shipping_address.</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 404 Not Found</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Hệ thống phải escape mã HTML/script khi lưu hoặc hiển thị. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-04</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>XSS trong shipping_address - mã phức tạp hơn</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "&lt;img src=x onerror=alert(1)&gt;"}</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa &lt;img src=x onerror=alert(1)&gt;
 2. Kiểm tra response và cách hệ thống xử lý địa chỉ</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Phải có escape shipping_address</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Hệ thống phải escape mã HTML/script khi lưu hoặc hiển thị. Test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Response thanh toán thành công có status 2xx</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm. Dữ liệu hợp lệ.</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với dữ liệu hợp lệ
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Response thành công là HTTP 200 OK vì route gọi res.json() mà không set status 201.</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="139.5" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Response thanh toán thành công có cấu trúc response hợp lệ</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm. Dữ liệu hợp lệ.</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với dữ liệu hợp lệ
 2. Kiểm tra toàn bộ response body</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Response thành công theo code gồm message và orderId. Không trả total_amount, status hay shipping_address.</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Tên field cụ thể trong response (orderId...) không được liệt kê trong đặc tả nhưng vẫn cần test cấu trúc hợp lệ JSON khi thành công</t>
         </is>
       </c>
     </row>
     <row r="26" ht="55.5" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-05</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Thiếu header Authorization - response báo lỗi</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Người dùng chưa đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"total_amount": 150000, "shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout KHÔNG gửi header Authorization
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized, Response: {"error":"Unauthorized"}.</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Trực tiếp từ 'chỉ người dùng đã đăng nhập mới checkout được'.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="84" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-14</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Thiếu field bắt buộc shipping_address - response báo lỗi</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 150000}</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout THIẾU field shipping_address
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="181.5" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-15</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Thiếu field bắt buộc total_amount - response báo lỗi</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"shipping_address": "123 ABC, Q1, TP.HCM"}</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout THIẾU field total_amount
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Báo lỗi</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="69.75" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-16</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Body trống - không gửi field nào - response báo lỗi</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với body rỗng {}
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Cả hai field đều không được validate trước INSERT; không có lỗi 400 ở tầng ứng dụng. Kết quả DB phụ thuộc schema.</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H29" s="18" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Test case hợp lý vì phải gửi đầy đủ field.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="265.5" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-06</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Checkout với token hết hạn</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã hết hạn. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;expired_token&gt;
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với expired_token</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>JWT hết hạn làm jwt.verify lỗi và middleware trả HTTP 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H30" s="18" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Chỉ người dùng đã đăng nhập mới checkout được' được suy luận hợp lý là bao gồm token còn hiệu lực (chưa hết hạn). Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="31" ht="223.5" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-07</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Checkout với token giả mạo (sai chữ ký)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã bị sửa đổi (sai chữ ký). Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;tampered_token&gt;
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với tampered_token</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>JWT sai chữ ký làm jwt.verify lỗi và middleware trả HTTP 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H31" s="18" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Token bị sửa đổi/sai chữ ký về bản chất không còn là 'người dùng đã đăng nhập hợp lệ'. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="32" ht="279.75" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-08</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Checkout với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user"). Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với user_token</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Checkout thành công</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả, happy path bình thường.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="139.5" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-17</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Checkout với giỏ hàng nhiều sản phẩm (3+ sản phẩm)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có 3 sản phẩm với giá trị khác nhau.</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 500000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>1. Thêm 3 sản phẩm vào giỏ hàng (giá: 100000, 150000, 250000)
 2. POST /api/checkout với total_amount sai
 3. Kiểm tra order</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Backend không tự tính lại total_amount từ giỏ hàng, kể cả nhiều sản phẩm; dùng trực tiếp giá trị client gửi.</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H33" s="18" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Dựa vào từ 'Backend phải tự tính lại tổng tiền' - áp dụng cho mọi số lượng sản phẩm trong giỏ, kể cả nhiều sản phẩm.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="294" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SEC-09</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Checkout với shipping_address chứa SQL injection</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "' OR 1=1 --"}</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address chứa SQL injection</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Parameterized query xử lý payload SQL injection an toàn; chuỗi được truyền như dữ liệu thay vì nối vào SQL.</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H34" s="18" t="inlineStr">
+      <c r="H34" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Dựa vào SEC-05 (parameterized query) là yêu cầu bảo mật chung của toàn hệ thống.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="181.5" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-DP-18</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>shipping_address gửi sai kiểu dữ liệu number thay vì string</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount":150000,"shipping_address":12345}</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với shipping_address: 12345
 2. Kiểm tra response và dữ liệu lưu</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Thông báo lỗi type của shipping_address</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra sai kiểu dữ liệu của shipping_address.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="181.5" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Gọi GET /api/checkout thay POST</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/checkout (thay vì POST)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>GET /api/checkout không có route GET; với Express hiện tại sẽ rơi vào HTTP 404 Not Found.</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không mô tả hành vi khi gọi sai HTTP method - đây là hành vi mặc định của framework/router, không phải yêu cầu nghiệp vụ được đặc tả. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="37" ht="111.75" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Race condition - 2 request checkout đồng thời cùng 1 user</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm tổng giá trị 100000.</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body (gửi đồng thời 2 lần): {"total_amount": 100000, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời (song song) 2 request POST /api/checkout từ cùng 1 user, cùng giỏ hàng
 2. GET /api/orders/my-orders kiểm tra số đơn hàng được tạo</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Hai request đồng thời có thể tạo hai order riêng nếu đều INSERT thành công.</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Test case để phát hiện duplicate order. AI dễ bỏ sót vì đây là hành động diễn ra đồng thời thường AI không thể suy ra đầy đủ chỉ từ đặc tả do trong đặc tả thường chỉ miêu tả yêu cầu đơn lẻ.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="69.75" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Giỏ hàng của user khác không bị ảnh hưởng khi checkout</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>2 user đã đăng nhập: user A và user B, cả 2 đều có sản phẩm trong giỏ hàng riêng.</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>User A: Header: Authorization: Bearer {{userToken}}
 User B: Header: Authorization: Bearer {{userTokenB}} (cần tài khoản phụ thứ 2)</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>1. User A và User B cùng thêm sản phẩm vào giỏ (POST /api/cart)
 2. User A checkout (POST /api/checkout)
 3. GET /api/cart bằng token của User B - kiểm tra giỏ hàng B còn nguyên</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>userCarts được lưu theo userId nên cart của User B dùng key riêng và không bị User A ghi đè.</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H38" s="17" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Test case để kiểm tra cách ly dữ liệu giữa người dùng. AI dễ bỏ sót vì đặc tả thường không mô tả.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>total_amount dạng số thập phân</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 99999.99, "shipping_address": "123 ABC"}</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với total_amount có phần thập phân</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Checkout thành công do tiền vẫn có thể số thập phân</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="inlineStr">
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Test case để kiểm tra có chấp nhận số thập phân ở trường tổng tiền hay không. AI có thể bỏ sót vì đặc tả chỉ nói number và không nêu quy ước có được dùng số thực hay không.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="93" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Content-Type sai khi checkout</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Header: Content-Type: text/plain
 Body: total_amount=100000&amp;shipping_address=123ABC</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/checkout với Content-Type sai, body không phải JSON hợp lệ</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>bodyParser.json() chỉ parse JSON phù hợp; với Content-Type sai, req.body có thể không chứa các field mong đợi. Route phải validate trước INSERT</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H40" s="17" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Test case cho input sai định dạng ở tầng HTTP. AI thường giả định client gửi đúng Content-Type theo đặc tả và bỏ sót hành vi gửi sai.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="63.75" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-FR08-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Gọi checkout liên tục nhiều lần trong thời gian ngắn (spam)</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập. Giỏ hàng có sản phẩm.</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"total_amount": 100000, "shipping_address": "123 ABC"} (gửi 20 lần liên tiếp trong 1 giây)</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>1. Gửi 20 request POST /api/checkout liên tiếp rất nhanh (script loop, không phải người dùng thật bấm 20 lần)</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Phải báo lỗi hoặc có cơ chế chống DoS</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Test case để kiểm tra spam. AI sinh từ đặc tả thường tập trung từng request đơn lẻ hơn là tần suất cao hay test độ chống DoS.</t>
         </is>
@@ -6303,56 +6310,56 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="21.9090909090909" customWidth="1" style="14" min="1" max="1"/>
-    <col width="26.7272727272727" customWidth="1" style="14" min="2" max="2"/>
-    <col width="31" customWidth="1" style="14" min="3" max="3"/>
-    <col width="21.6363636363636" customWidth="1" style="14" min="4" max="4"/>
-    <col width="21.7272727272727" customWidth="1" style="14" min="5" max="5"/>
-    <col width="20.2727272727273" customWidth="1" style="14" min="6" max="6"/>
-    <col width="41.4090909090909" customWidth="1" style="14" min="7" max="7"/>
-    <col width="9" customWidth="1" style="14" min="8" max="8"/>
-    <col width="22.1818181818182" customWidth="1" style="14" min="9" max="9"/>
+    <col width="21.9090909090909" customWidth="1" style="1" min="1" max="1"/>
+    <col width="26.7272727272727" customWidth="1" style="1" min="2" max="2"/>
+    <col width="31" customWidth="1" style="1" min="3" max="3"/>
+    <col width="21.6363636363636" customWidth="1" style="1" min="4" max="4"/>
+    <col width="21.7272727272727" customWidth="1" style="1" min="5" max="5"/>
+    <col width="20.2727272727273" customWidth="1" style="1" min="6" max="6"/>
+    <col width="41.4090909090909" customWidth="1" style="1" min="7" max="7"/>
+    <col width="9" customWidth="1" style="1" min="8" max="8"/>
+    <col width="22.1818181818182" customWidth="1" style="1" min="9" max="9"/>
     <col width="45.5818181818182" customWidth="1" style="2" min="10" max="10"/>
-    <col width="9" customWidth="1" style="14" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="1" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -6362,51 +6369,51 @@
           <t>Audit Label</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2" ht="84" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên hợp lệ</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Tạo category thành công. Status code: 201 Created. Response body trả về object category vừa tạo, gồm ít nhất "id" và "name" (ví dụ: {"id": 1, "name": "Điện thoại"}).</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6416,51 +6423,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên trống (empty string)</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6470,51 +6477,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Từ đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên null</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": null}</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {"name": null}</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6524,51 +6531,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Null cũng là một dạng 'không có giá trị' - áp dụng cùng đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Tạo category thiếu field name</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Body: {}</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6578,14 +6585,14 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Thiếu hẳn field cũng vi phạm đặc tả: 'Tên danh mục là bắt buộc, không được để trống'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="184.5" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-05</t>
         </is>
@@ -6595,7 +6602,7 @@
           <t>Tạo category với tên rất dài (boundary test, 1000 ký tự)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
@@ -6617,12 +6624,12 @@
           <t>Hệ thống xử lý ổn định, không được trả về 500. Chấp nhận 1 trong 2 kết quả: (a) 201 Created nếu hệ thống không giới hạn độ dài, hoặc (b) 400 Bad Request nếu hệ thống có giới hạn.</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>200 OK – Hệ thống chấp nhận tên 1000 ký tự.</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6632,51 +6639,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Test case boundary cho độ dài tên. Test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="7" ht="159.75" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-06</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên chỉ có khoảng trắng</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "   "}</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "   "
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên là bắt buộc. Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6686,50 +6693,50 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ có trim khoảng trắng trước khi kiểm tra rỗng hay không, nhưng theo em suy luận khoảng trắng cũng đồng nghĩa với không có tên danh mục, nên em sẽ sửa kết quả từ chấp nhận tên sang từ chối tạo category.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="130.5" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-07</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên trùng với category đã có</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Đã có category "Điện thoại".</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "Điện thoại" (da ton tai)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên phải unique. Status code: 409 Conflict (hoặc 400 Bad Request nếu hệ thống dùng chung cơ chế validation error).</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 409 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6739,51 +6746,51 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Đặc tả không yêu cầu tên category phải unique nhưng theo em tên danh mục nên là unique, em sẽ đổi kết quả từ cho phép tạo sang từ chối. </t>
         </is>
       </c>
     </row>
     <row r="9" ht="97.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-01</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Tạo category với tên chứa ký tự đặc biệt</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ với role = "admin".</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Điện &lt;thoại&gt; &amp; Phụ kiện"}</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên chứa ký tự đặc biệt
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Tên không chứa ký tự đặc biệt nguy hiểm (HTML/script injection). Status code: 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6793,49 +6800,49 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói về việc danh mục có được chứa ký tự đặc biệt hay không, nhưng theo em thì không nên, nên em sẽ đổi kết quả từ cho phép tạo sang từ chối tạo.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="69.75" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-01</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Xem danh sách category - có category</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có ít nhất 1 category.</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Trả về danh sách category. Status code: 200 OK. Response body là một mảng các object category (ví dụ: [{"id":1,"name":"Điện thoại"}, ...]).</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6845,49 +6852,49 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xem'.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="55.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-02</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Xem danh sách category - không có category nào</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Không có category nào.</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Trả về danh sách rỗng. Status code: 200 OK. Response body là mảng trống ([]), không phải null.</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6897,51 +6904,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xem' nhưng trường hợp rỗng.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="84" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-03</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Xóa category thành công</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id
 2. GET /api/categories để verify</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Xóa thành công. Category không còn trong danh sách. Status code: 204 No Content (theo convention REST phổ biến cho DELETE; 200 OK cũng có thể chấp nhận nếu backend trả kèm message).</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 GET: 200 OK; B3 DELETE: 200 OK - BUG: kỳ vọng 204 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6951,50 +6958,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'Admin có thể Xóa'.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="97.5" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Xóa category không tồn tại</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. ID không tồn tại.</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Hệ thống trả lỗi 404</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 404 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7004,51 +7011,51 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ nhưng em nghĩ hệ thống phải thông báo lỗi thay vì xác định thành công, nên em chuyển kết quả từ phân vân 2 trạng thái sang hệ thống phải trả lỗi.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-04</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Sửa category - thay đổi tên</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên mới
 2. GET /api/categories để verify</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Sửa thành công. Tên mới được cập nhật. Status code: 200 OK. Response body trả về object category đã cập nhật (ví dụ: {"id":1,"name":"Tên mới"}).</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>B1 PUT: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7058,50 +7065,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="15" ht="84" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-DP-09</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Sửa category với tên trống</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên trống</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Từ chối sửa. Tên là bắt buộc. Status code: 400 Bad Request, body chứa thông báo lỗi (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7111,35 +7118,35 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Đúng với đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="16" ht="111.75" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-05</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Luồng hoàn chỉnh: Tạo -&gt; Xem -&gt; Xóa -&gt; Xem</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Chưa có category "Test Category".</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Test Category"}</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên "Test Category"
 2. GET /api/categories - xác nhận có
@@ -7147,17 +7154,17 @@
 4. GET /api/categories - xac nhan không còn</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Tạo thành công (POST → 201) → Xuất hiện trong danh sách (GET → 200, có category) → Xóa thành công (DELETE → 204) → Không còn trong danh sách (GET → 200, không có category).</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK; B3 DELETE: 200 OK; B4 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7167,50 +7174,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Luồng Tạo-&gt;Xem-&gt;Xóa-&gt;Xem đúng phạm vi 'Thêm/Xem/Xóa' của đặc tả</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-02</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Tạo category khi chưa đăng nhập (không có token)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Không gửi header Authorization
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories KHÔNG gửi token</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7220,50 +7227,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="84" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-03</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Tạo category với token không hợp lệ</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhung token không hợp lệ.</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;invalid_token&gt;
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với invalid_token</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7273,50 +7280,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="84" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-04</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Tạo category với token giả mạo (sai chữ ký)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã bị sửa đổi.</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;tampered_token&gt;
 Body: {"name": "Category giả"}</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tampered_token</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token không hợp lệ (sai chữ ký). Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7326,50 +7333,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="97.5" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-05</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Tạo category với token hết hạn</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Người dùng có token nhưng đã hết hạn.</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer &lt;expired_token&gt;
 Body: {"name": "Category hết hạn"}</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với expired_token</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token hết hạn. Status code: 401 Unauthorized. LƯU Ý: cần tạo token hết hạn trước khi test.</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7379,50 +7386,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả 'API có tính ảnh hưởng dữ liệu (POST/PUT/DELETE /api/categories) phải yêu cầu Token JWT hợp lệ'.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="97.5" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-06</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Tạo category với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"name": "Điện thoại"}</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với user_token</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Từ chối tạo category. Token hợp lệ nhưng role != "admin". Spec nói rõ: phải kiểm tra role = "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7432,50 +7439,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả phải kiểm tra role='admin', không chỉ kiểm tra có token.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="84" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-07</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Xóa category với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id với user_token</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Từ chối xóa category. Role != "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7485,49 +7492,49 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả phải kiểm tra role='admin', không chỉ kiểm tra có token.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="111.75" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-08</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>GET /api/categories không có token</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Người dùng CHƯA đăng nhập. Không có token.</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Không gửi header Authorization</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories KHÔNG gửi token</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Từ chối truy cập. Status code: 401 Unauthorized.</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 401 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7537,49 +7544,49 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Dù đặc tả không nói rõ, nhưng theo em GET cũng cần token + role admin. Suy ra test case AI tạo rahợp lý.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="126" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-09</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>GET /api/categories với token user bình thường (role != admin)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories với user_token</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Từ chối xem danh sách category. Role != "admin". Status code: 403 Forbidden.</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7589,50 +7596,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Dù đặc tả không nói rõ, nhưng theo em GET cũng cần token + role admin. Suy ra test case AI tạo ra hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="84" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-01</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>GET /api/categories trả về danh sách dạng mảng (array)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Token JWT hợp lệ.</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Response phải trả về một mảng (array), không phải object hay string. Mảng có thể trống hoặc có phần tử tùy dữ liệu hiện có, miễn đúng kiểu array.</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7642,50 +7649,50 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra schema cơ bản (mảng). Suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="55.5" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-02</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>GET /api/categories trả về mảng rỗng khi không có category</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Không có category nào.</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>1. GET /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Response trả về mảng rỗng chính xác là [] (không phải null, không phải object rỗng {}).</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7695,51 +7702,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Kiểm tra schema cơ bản (mảng). Suy ra test case hợp lý.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="84" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-03</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>POST /api/categories thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Category mới"}</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên hợp lệ
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Response thành công phải có status 201 Created (convention chuẩn REST cho hành động tạo mới thành công; 200 OK có thể chấp nhận nếu backend không tuân thủ chuẩn tuyệt đối).</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7749,51 +7756,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Thành công thì trả về 2xx, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="28" ht="84" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-04</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>POST /api/categories thất bại (tên trống) trả về 4xx</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên trống
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Response lỗi phải có status 400 Bad Request. Không được trả về 2xx khi dữ liệu không hợp lệ.</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7803,51 +7810,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Từ chối khi tên rỗng phải là 4xx - test case hợp lý, khớp với yêu cầu 'tên bắt buộc' của đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="111.75" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-05</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>POST /api/categories thành công có cấu trúc response hợp lệ</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Category mới"}</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories
 2. Kiểm tra response body</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Response thành công phải có cấu trúc JSON hợp lệ, tối thiểu gồm field "id" và "name" (ví dụ: {"id": 1, "name": "Category mới"}). LƯU Ý: tên field là SUY ĐOÁN, không trích từ tài liệu, cần đối chiếu response thực tế khi thực thi.</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7857,51 +7864,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Tên field cụ thể trong response không được liệt kê ở đặc tả nhưng vẫn phải test cấu trúc JSON nên test case hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="30" ht="84" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-06</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>DELETE /api/categories/:id thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần xóa.</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/:id</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Response thành công phải có status 204 No Content (đồng nhất với TC-FR14-ST-03; 200 OK cũng có thể chấp nhận nếu backend trả kèm message).</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 204 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7911,51 +7918,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Thành công thì trả về 2xx, test case hợp lý</t>
         </is>
       </c>
     </row>
     <row r="31" ht="97.5" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-07</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>DELETE /api/categories/:id thất bại (id không tồn tại) trả về 4xx</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. ID không tồn tại.</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 URL: DELETE /api/categories/99999</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/99999
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Hệ thống trả lỗi 404 Not Found.</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 404 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7965,51 +7972,51 @@
           <t>INCOMPLETE</t>
         </is>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Đặc tả không nói rõ nhưng em nghĩ hệ thống phải thông báo lỗi thay vì xác định thành công, nên em chuyển kết quả từ phân vân 2 trạng thái sang hệ thống phải trả lỗi.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="84" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-08</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Response lỗi khi thiếu field name có cấu trúc báo lỗi</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {}</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với body rỗng
 2. Kiểm tra response</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Response phải báo lỗi với status 400 Bad Request và có cấu trúc JSON hợp lệ (ví dụ: {"error": "Tên danh mục là bắt buộc"}).</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8019,51 +8026,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Cấu trúc lỗi JSON hợp lệ khi thiếu field bắt buộc khớp yêu cầu 'tên bắt buộc'.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="84" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-09</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Sửa category thành công trả về status 2xx</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa. Tên hợp lệ.</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Response thành công phải có status 200 OK.</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H33" s="20" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8073,51 +8080,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="34" ht="84" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SCHEMA-10</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Sửa category thất bại (tên trống) trả về 4xx</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần sửa.</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": ""}</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>1. PUT /api/categories/:id với tên trống
 2. Kiểm tra HTTP status code</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Response lỗi phải có status 400 Bad Request.</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8127,52 +8134,52 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả API</t>
         </is>
       </c>
     </row>
     <row r="35" ht="126" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-ST-06</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Xóa category rồi tạo lại với tên giống - không bị trùng id</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category "Temp Category".</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Temp Category"}</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>1. DELETE /api/categories/:id của "Temp Category"
 2. POST /api/categories với tên "Temp Category" mới
 3. GET /api/categories - xác nhận chỉ có 1 với id mới</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Xóa thành công. Tạo lại với id mới. Chỉ có 1 category "Temp Category". Id mới phải khác id cũ (do id thường là auto-increment hoặc UUID, không tái sử dụng id đã xóa).</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>B1 DELETE: 200 OK; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H35" s="20" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8182,51 +8189,51 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Không quy định trong đặc tả, nhưng theo suy luận của em, test case AI sinh ra hợp lý. Kiểm tra được tính unique của danh mục sẽ được xác định đúng hay không.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="111.75" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-SEC-10</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Token user bình thường (role != admin) thực thi cả POST và DELETE</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Người dùng đã đăng nhập với tài khoản user bình thường (role = "user").</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{userToken}}
 Body: {"name": "Test"}</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với user_token
 2. DELETE /api/categories/:id với user_token</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Cả POST và DELETE đều bị từ chối. Token hợp lệ nhưng role != "admin". Status code: 403 Forbidden cho cả 2 request.</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 DELETE: 200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8236,56 +8243,56 @@
           <t>VALID</t>
         </is>
       </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Dựa vào đặc tả.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="105.75" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-01</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Tạo category với field thừa không được định nghĩa</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Sách", "description": "Mô tả không nằm trong spec"}</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với body có field 'description' thừa ngoài spec</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Hệ thống bỏ qua field "description" không được định nghĩa trong spec, chỉ lưu field "name"; tạo category thành công với status 201 Created (convention phổ biến: ignore unknown fields thay vì báo lỗi 400, trừ khi hệ thống dùng strict schema validation).</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
       <c r="I37" s="12" t="n"/>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì prompt yêu cầu sinh test case theo 'domain partition trên từng parameter' được liệt kê trong đặc tả; AI chỉ suy luận trên các field đã được định nghĩa, không tự nghĩ đến trường hợp field không nằm trong đặc tả) - đây là giới hạn phạm vi suy luận của model khi bám sát input đã cho.</t>
         </is>
@@ -8293,50 +8300,50 @@
       <c r="K37" s="13" t="n"/>
     </row>
     <row r="38" ht="97.5" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-02</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Race condition - 2 admin tạo category cùng tên đồng thời</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập (2 phiên/token khác nhau nếu có thể). Chưa có category tên 'Sách'.</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body (gửi đồng thời 2 lần): {"name": "Sách"}</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>1. Gửi đồng thời 2 request POST /api/categories cùng tên 'Sách'
 2. GET /api/categories kiểm tra có bao nhiêu category tên 'Sách' được tạo</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Do tên category phải unique (theo TC-FR14-DP-07), khi 2 request đồng thời cùng tên "Sách" được gửi, chỉ 1 request thành công (201 Created), request còn lại phải bị từ chối (409 Conflict hoặc 400 Bad Request). Không được có 2 category cùng tên "Sách" sau khi chạy xong.</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H38" s="17" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
       <c r="I38" s="12" t="n"/>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì test case AI sinh ra theo luồng tuần tự (1 request - 1 response tại một thời điểm), không có khả năng/không được yêu cầu mô phỏng tình huống đồng thời. Đây là hạn chế đặc trưng của việc sinh test case từ đặc tả tĩnh: AI không tự suy luận về các vấn đề vận hành thực tế nếu prompt không yêu cầu rõ ràng.</t>
         </is>
@@ -8344,49 +8351,49 @@
       <c r="K38" s="13" t="n"/>
     </row>
     <row r="39" ht="117" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-03</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Gọi HTTP method không được hỗ trợ (PATCH)</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập. Có category cần test.</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Tên mới"}</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>1. PATCH /api/categories/:id (method không được liệt kê trong API spec - chỉ có GET/POST/PUT/DELETE)</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Hệ thống trả về 404 Not Found (phổ biến hơn 405 Method Not Allowed đối với các API đơn giản dùng framework như Express, vốn không định nghĩa route cho PATCH nên coi như route không tồn tại). Nếu hệ thống có OPTIONS/route-level method negotiation thì có thể trả 405 kèm header Allow.</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="I39" s="12" t="n"/>
-      <c r="J39" s="16" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI generate test case dựa trên các HTTP method được liệt kê tường minh trong đặc tả (GET/POST/PUT/DELETE), không tự nghĩ đến việc test các method KHÔNG được định nghĩa trong đặc tả. Đây là đặc điểm của model: thiên về mặt theo đúng đặc tả, thiếu tư duy mặt ngược lại thì như nào.</t>
         </is>
@@ -8394,50 +8401,50 @@
       <c r="K39" s="13" t="n"/>
     </row>
     <row r="40" ht="160.5" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-04</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Content-Type sai khi tạo category</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Header: Content-Type: text/plain
 Body: name=Sach</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với Content-Type sai, body không phải JSON hợp lệ</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Hệ thống nên trả về 400 Bad Request với thông báo lỗi rõ ràng (ví dụ: "Invalid JSON body" hoặc "Unsupported Content-Type"), KHÔNG được trả 500 Internal Server Error. Nếu thực thi cho ra 500 thì đây là một bug cần report.</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H40" s="17" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="I40" s="12" t="n"/>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI tập trung sinh test case validate nội dung body theo đúng domain partition được yêu cầu trong prompt, chứ không kiểm tra các thuộc tính protocol-level như HTTP header Content-Type. Đây là hạn chế do phạm vi prompt (chỉ yêu cầu domain partition/state/security/schema) không bao gồm rõ ràng validation ở tầng request header.</t>
         </is>
@@ -8445,50 +8452,50 @@
       <c r="K40" s="13" t="n"/>
     </row>
     <row r="41" ht="124.5" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-FR14-EXT-05</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Tên category chứa ký tự Unicode có dấu / emoji</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Admin đã đăng nhập.</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Header: Authorization: Bearer {{adminToken}}
 Body: {"name": "Đồ gia dụng 🏠"}</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>1. POST /api/categories với tên chứa tiếng Việt có dấu và emoji
 2. GET /api/categories kiểm tra tên lưu và trả về có đúng nguyên gốc không</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Hệ thống lưu và trả về đúng nguyên vẹn chuỗi UTF-8 (tiếng Việt có dấu và emoji), không bị lỗi encoding, không bị cắt ký tự. Status code: 201 Created khi tạo thành công.</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
       <c r="I41" s="12" t="n"/>
-      <c r="J41" s="16" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>AI bỏ sót vì AI ít khi tự sinh test case về encoding/Unicode edge case trừ khi được yêu cầu cụ thể trong prompt - đây là đặc điểm kỹ thuật của hệ thống, thường không được nêu rõ trong đặc tả chức năng, nên AI thiên về test theo đặc tả hơn là các edge case kỹ thuật/encoding.</t>
         </is>

--- a/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
+++ b/23127031_HW06_AI_API_090/testcases_testsummary.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -80,6 +80,19 @@
       <charset val="134"/>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -245,15 +258,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <color rgb="00006100"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -478,12 +489,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -514,6 +531,30 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -617,151 +658,145 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" applyAlignment="1">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -803,22 +838,39 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="38" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1342,298 +1394,254 @@
   <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="30" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15" customWidth="1" style="1" min="2" max="2"/>
-    <col width="15" customWidth="1" style="1" min="3" max="3"/>
-    <col width="15" customWidth="1" style="1" min="4" max="6"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9" customWidth="1" style="1" min="8" max="16384"/>
+    <col width="30" customWidth="1" style="26" min="1" max="1"/>
+    <col width="15" customWidth="1" style="26" min="2" max="2"/>
+    <col width="37.5454545454545" customWidth="1" style="26" min="3" max="3"/>
+    <col width="15" customWidth="1" style="26" min="4" max="6"/>
+    <col width="40" customWidth="1" style="26" min="7" max="7"/>
+    <col width="9" customWidth="1" style="26" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>HW06 API Testing - Test Summary Report</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Student ID: 23127031 | Date: 2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Number of APIs tested</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="19" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Total test cases generated</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="19" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Total requests in collection</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="19" t="n">
         <v>151</v>
       </c>
     </row>
     <row r="8" ht="14.5" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Assertions executed</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="20" t="n">
         <v>138</v>
       </c>
     </row>
     <row r="9" ht="14.5" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Assertions passed</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n">
-        <v>60</v>
+      <c r="B9" s="20" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="14.5" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Assertions failed</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n">
-        <v>78</v>
+      <c r="B10" s="20" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Pass rate</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>43.5%</t>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Bugs found</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
-        <v>13</v>
+      <c r="B12" s="19" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Critical bugs</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Major bugs</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>Critical bugs</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Major bugs</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="B15" s="20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" ht="14.5" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Minor bugs</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="20" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Detailed Results by API</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="18" ht="15" customFormat="1" customHeight="1" s="26">
+      <c r="A18" s="23" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+    </row>
+    <row r="19" ht="15.5" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>Assertions</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>Test Cases</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>Bugs Found</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Test Cases</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="n">
-        <v>7</v>
-      </c>
+      <c r="G19" s="26" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>FR-02</t>
         </is>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="19" t="n">
         <v>52</v>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="E20" s="25" t="n">
-        <v>26</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="G20" s="18" t="n">
-        <v>3</v>
-      </c>
+      <c r="E20" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="G20" s="26" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>FR-08</t>
         </is>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="19" t="n">
         <v>48</v>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="E21" s="25" t="n">
-        <v>38</v>
-      </c>
-      <c r="F21" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <v>4</v>
-      </c>
+      <c r="E21" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="26" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="28" t="inlineStr">
@@ -1655,179 +1663,177 @@
       <c r="E22" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="F22" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="G22" s="21" t="n">
+      <c r="G22" s="35" t="n"/>
+    </row>
+    <row r="23" ht="14.5" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="31" t="n">
+        <v>151</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>120</v>
+      </c>
+      <c r="E23" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="F23" s="31" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="21" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>Issue Numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>#166, #168, #169, #170, #171, #174</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>#167, #172, #173, #179, #180</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>#176, #177, #178</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="14.5" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="29" t="n">
-        <v>151</v>
-      </c>
-      <c r="D23" s="29" t="n">
+      <c r="C29" s="28" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>AI Audit Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>EXT (no label)</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="n">
         <v>120</v>
       </c>
-      <c r="E23" s="29" t="n">
-        <v>80</v>
-      </c>
-      <c r="F23" s="29" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="20" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>Issue Numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>#166, #168, #169, #170, #171, #174</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C27" s="25" t="inlineStr">
-        <is>
-          <t>#167, #172, #173, #179</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>#176, #177, #178</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B29" s="30" t="n">
-        <v>13</v>
-      </c>
-      <c r="C29" s="21" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>AI Audit Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>INVALID</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>EXT (no label)</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="n">
-        <v>120</v>
-      </c>
-      <c r="C37" s="24" t="n"/>
+      <c r="C37" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1848,13 +1854,13 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="28.0909090909091" defaultRowHeight="14"/>
   <cols>
-    <col width="15.6363636363636" customWidth="1" style="1" min="1" max="1"/>
-    <col width="28.0909090909091" customWidth="1" style="1" min="2" max="6"/>
-    <col width="37.0636363636364" customWidth="1" style="1" min="7" max="7"/>
-    <col width="35.4909090909091" customWidth="1" style="1" min="8" max="8"/>
-    <col width="28.0909090909091" customWidth="1" style="1" min="9" max="9"/>
-    <col width="35" customWidth="1" style="1" min="10" max="10"/>
-    <col width="28.0909090909091" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="15.6363636363636" customWidth="1" style="26" min="1" max="1"/>
+    <col width="28.0909090909091" customWidth="1" style="26" min="2" max="6"/>
+    <col width="37.0636363636364" customWidth="1" style="26" min="7" max="7"/>
+    <col width="35.4909090909091" customWidth="1" style="26" min="8" max="8"/>
+    <col width="28.0909090909091" customWidth="1" style="26" min="9" max="9"/>
+    <col width="35" customWidth="1" style="26" min="10" max="10"/>
+    <col width="28.0909090909091" customWidth="1" style="26" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1947,7 +1953,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2001,7 +2007,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2055,7 +2061,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2109,7 +2115,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2163,7 +2169,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2217,7 +2223,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2271,7 +2277,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2325,7 +2331,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2379,7 +2385,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2433,7 +2439,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2487,7 +2493,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2541,7 +2547,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2595,7 +2601,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2649,7 +2655,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2703,7 +2709,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2757,7 +2763,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2811,7 +2817,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2865,7 +2871,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2919,7 +2925,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2973,7 +2979,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3027,7 +3033,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3081,7 +3087,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3135,7 +3141,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3189,7 +3195,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3244,7 +3250,7 @@
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3299,7 +3305,7 @@
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3354,9 +3360,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H28" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -3409,9 +3415,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H29" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -3464,9 +3470,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H30" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -3519,9 +3525,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H31" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -3575,9 +3581,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H32" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
@@ -3631,9 +3637,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H33" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -3687,9 +3693,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H34" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
@@ -3742,9 +3748,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H35" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -3797,9 +3803,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H36" s="37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -3851,7 +3857,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3901,7 +3907,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H38" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3952,9 +3958,9 @@
           <t>B1 POST: 500 Internal Server Error; B2 GET: 401 Unauthorized</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H39" s="39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
@@ -4001,7 +4007,7 @@
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="39" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4050,7 +4056,7 @@
           <t>500 Internal Server Error - BUG: kỳ vọng 401 nhưng thực tế 500</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="39" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4077,17 +4083,17 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="21.5454545454545" customWidth="1" style="1" min="1" max="1"/>
-    <col width="30.4545454545455" customWidth="1" style="1" min="2" max="2"/>
-    <col width="40" customWidth="1" style="1" min="3" max="3"/>
-    <col width="50" customWidth="1" style="1" min="4" max="4"/>
-    <col width="45" customWidth="1" style="1" min="5" max="5"/>
-    <col width="55" customWidth="1" style="1" min="6" max="6"/>
-    <col width="18" customWidth="1" style="1" min="7" max="7"/>
-    <col width="12" customWidth="1" style="1" min="8" max="8"/>
-    <col width="18.0909090909091" customWidth="1" style="1" min="9" max="9"/>
-    <col width="29.6363636363636" customWidth="1" style="1" min="10" max="10"/>
-    <col width="8" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="21.5454545454545" customWidth="1" style="26" min="1" max="1"/>
+    <col width="30.4545454545455" customWidth="1" style="26" min="2" max="2"/>
+    <col width="40" customWidth="1" style="26" min="3" max="3"/>
+    <col width="50" customWidth="1" style="26" min="4" max="4"/>
+    <col width="45" customWidth="1" style="26" min="5" max="5"/>
+    <col width="55" customWidth="1" style="26" min="6" max="6"/>
+    <col width="18" customWidth="1" style="26" min="7" max="7"/>
+    <col width="12" customWidth="1" style="26" min="8" max="8"/>
+    <col width="18.0909090909091" customWidth="1" style="26" min="9" max="9"/>
+    <col width="29.6363636363636" customWidth="1" style="26" min="10" max="10"/>
+    <col width="8" customWidth="1" style="26" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4181,7 +4187,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4236,7 +4242,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4291,7 +4297,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4346,7 +4352,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4401,7 +4407,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4456,7 +4462,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 200 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="39" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4511,7 +4517,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4566,7 +4572,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4621,7 +4627,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4676,7 +4682,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4731,7 +4737,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4786,7 +4792,7 @@
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4841,7 +4847,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4896,7 +4902,7 @@
           <t>B1 POST: 400 Bad Request; B2 GET: 404 Not Found</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4951,7 +4957,7 @@
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5005,9 +5011,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H17" s="39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -5059,9 +5065,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H18" s="39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -5114,7 +5120,7 @@
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5169,7 +5175,7 @@
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5224,7 +5230,7 @@
           <t>B1 GET: 200 OK; B2 POST: 400 Bad Request</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5279,7 +5285,7 @@
           <t>B1 POST: 400 Bad Request; B2 GET: 404 Not Found</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5333,7 +5339,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5387,7 +5393,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5441,7 +5447,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5495,7 +5501,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5549,9 +5555,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H27" s="39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -5603,9 +5609,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H28" s="39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -5657,7 +5663,7 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5710,7 +5716,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5763,7 +5769,7 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5816,7 +5822,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5871,7 +5877,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5924,7 +5930,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5978,9 +5984,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H35" s="39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -6030,7 +6036,7 @@
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6084,7 +6090,7 @@
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6135,7 +6141,7 @@
           <t>B1 POST: 400 Bad Request; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6184,7 +6190,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6234,7 +6240,7 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6283,9 +6289,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H41" s="39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
@@ -6310,17 +6316,17 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="21.9090909090909" customWidth="1" style="1" min="1" max="1"/>
-    <col width="26.7272727272727" customWidth="1" style="1" min="2" max="2"/>
-    <col width="31" customWidth="1" style="1" min="3" max="3"/>
-    <col width="21.6363636363636" customWidth="1" style="1" min="4" max="4"/>
-    <col width="21.7272727272727" customWidth="1" style="1" min="5" max="5"/>
-    <col width="20.2727272727273" customWidth="1" style="1" min="6" max="6"/>
-    <col width="41.4090909090909" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9" customWidth="1" style="1" min="8" max="8"/>
-    <col width="22.1818181818182" customWidth="1" style="1" min="9" max="9"/>
+    <col width="21.9090909090909" customWidth="1" style="26" min="1" max="1"/>
+    <col width="26.7272727272727" customWidth="1" style="26" min="2" max="2"/>
+    <col width="31" customWidth="1" style="26" min="3" max="3"/>
+    <col width="21.6363636363636" customWidth="1" style="26" min="4" max="4"/>
+    <col width="21.7272727272727" customWidth="1" style="26" min="5" max="5"/>
+    <col width="20.2727272727273" customWidth="1" style="26" min="6" max="6"/>
+    <col width="41.4090909090909" customWidth="1" style="26" min="7" max="7"/>
+    <col width="9" customWidth="1" style="26" min="8" max="8"/>
+    <col width="22.1818181818182" customWidth="1" style="26" min="9" max="9"/>
     <col width="45.5818181818182" customWidth="1" style="2" min="10" max="10"/>
-    <col width="9" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="26" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
@@ -6413,7 +6419,7 @@
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6467,7 +6473,7 @@
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6521,7 +6527,7 @@
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6575,7 +6581,7 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6629,7 +6635,7 @@
           <t>200 OK – Hệ thống chấp nhận tên 1000 ký tự.</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6683,7 +6689,7 @@
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6736,7 +6742,7 @@
           <t>200 OK - BUG: kỳ vọng 409 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6790,7 +6796,7 @@
           <t>200 OK - BUG: kỳ vọng 400 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6842,7 +6848,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6894,7 +6900,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6948,7 +6954,7 @@
           <t>B1 DELETE: 200 OK; B2 GET: 200 OK; B3 DELETE: 200 OK - BUG: kỳ vọng 204 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7001,7 +7007,7 @@
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 404 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7055,7 +7061,7 @@
           <t>B1 PUT: 400 Bad Request; B2 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7108,7 +7114,7 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7164,7 +7170,7 @@
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK; B3 DELETE: 200 OK; B4 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7217,7 +7223,7 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7270,7 +7276,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7323,7 +7329,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7376,7 +7382,7 @@
           <t>403 Forbidden - BUG: kỳ vọng 401 nhưng thực tế 403</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7429,7 +7435,7 @@
           <t>200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7482,7 +7488,7 @@
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7534,7 +7540,7 @@
           <t>200 OK - BUG: kỳ vọng 401 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7586,7 +7592,7 @@
           <t>200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7639,7 +7645,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7692,7 +7698,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7746,7 +7752,7 @@
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7800,7 +7806,7 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7854,7 +7860,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7908,7 +7914,7 @@
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 204 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7962,7 +7968,7 @@
           <t>B1 DELETE: 200 OK; B2 DELETE: 200 OK - BUG: kỳ vọng 404 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8016,7 +8022,7 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8070,7 +8076,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8124,7 +8130,7 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8179,7 +8185,7 @@
           <t>B1 DELETE: 200 OK; B2 POST: 400 Bad Request; B3 GET: 200 OK</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8233,7 +8239,7 @@
           <t>B1 POST: 400 Bad Request; B2 DELETE: 200 OK - BUG: kỳ vọng 403 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="37" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8286,7 +8292,7 @@
           <t>200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="39" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8337,7 +8343,7 @@
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="39" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8387,7 +8393,7 @@
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8438,7 +8444,7 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8489,7 +8495,7 @@
           <t>B1 POST: 400 Bad Request; B2 GET: 200 OK - BUG: kỳ vọng 201 nhưng thực tế 200</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="39" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
